--- a/du-lieu/chinh-sua-tay.xlsx
+++ b/du-lieu/chinh-sua-tay.xlsx
@@ -431,7 +431,7 @@
         <v>OM4-DE-IS-0009</v>
       </c>
       <c r="E2" t="str">
-        <v>Y3-2</v>
+        <v>Y3-1</v>
       </c>
     </row>
   </sheetData>

--- a/du-lieu/chinh-sua-tay.xlsx
+++ b/du-lieu/chinh-sua-tay.xlsx
@@ -431,7 +431,7 @@
         <v>OM4-DE-IS-0009</v>
       </c>
       <c r="E2" t="str">
-        <v>Y3-1</v>
+        <v>Y3-2</v>
       </c>
     </row>
   </sheetData>

--- a/du-lieu/chinh-sua-tay.xlsx
+++ b/du-lieu/chinh-sua-tay.xlsx
@@ -431,7 +431,7 @@
         <v>OM4-DE-IS-0009</v>
       </c>
       <c r="E2" t="str">
-        <v>Y3-1</v>
+        <v>Y3-4</v>
       </c>
     </row>
   </sheetData>

--- a/du-lieu/chinh-sua-tay.xlsx
+++ b/du-lieu/chinh-sua-tay.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:H2"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -416,6 +416,15 @@
       <c r="E1" t="str">
         <v>Vị trí</v>
       </c>
+      <c r="F1" t="str">
+        <v>Trạng thái</v>
+      </c>
+      <c r="G1" t="str">
+        <v>Ngày xuất</v>
+      </c>
+      <c r="H1" t="str">
+        <v>Ngày cập nhật</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
@@ -431,12 +440,21 @@
         <v>OM4-DE-IS-0009</v>
       </c>
       <c r="E2" t="str">
-        <v>Y3-4</v>
+        <v>Y3-1</v>
+      </c>
+      <c r="F2" t="str">
+        <v>Trong kho</v>
+      </c>
+      <c r="G2" t="str">
+        <v/>
+      </c>
+      <c r="H2" t="str">
+        <v>18/08/2026</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H2"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/du-lieu/chinh-sua-tay.xlsx
+++ b/du-lieu/chinh-sua-tay.xlsx
@@ -440,7 +440,7 @@
         <v>OM4-DE-IS-0009</v>
       </c>
       <c r="E2" t="str">
-        <v>Y3-1</v>
+        <v>Y3-2</v>
       </c>
       <c r="F2" t="str">
         <v>Trong kho</v>

--- a/du-lieu/chinh-sua-tay.xlsx
+++ b/du-lieu/chinh-sua-tay.xlsx
@@ -440,7 +440,7 @@
         <v>OM4-DE-IS-0009</v>
       </c>
       <c r="E2" t="str">
-        <v>Y3-2</v>
+        <v>Y3-1</v>
       </c>
       <c r="F2" t="str">
         <v>Trong kho</v>

--- a/du-lieu/chinh-sua-tay.xlsx
+++ b/du-lieu/chinh-sua-tay.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H18"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -452,9 +452,425 @@
         <v>18/08/2026</v>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>28/07/2026</v>
+      </c>
+      <c r="B3" t="str">
+        <v>OM4-DE-IS-0009-001</v>
+      </c>
+      <c r="C3" t="str">
+        <v>HDG STEEL Conduit</v>
+      </c>
+      <c r="D3" t="str">
+        <v>OM4-DE-IS-0009</v>
+      </c>
+      <c r="E3" t="str">
+        <v>Y3-2</v>
+      </c>
+      <c r="F3" t="str">
+        <v>Trong kho</v>
+      </c>
+      <c r="G3" t="str">
+        <v/>
+      </c>
+      <c r="H3" t="str">
+        <v>18/08/2026</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>28/07/2026</v>
+      </c>
+      <c r="B4" t="str">
+        <v>OM4-DE-IS-0009-002</v>
+      </c>
+      <c r="C4" t="str">
+        <v>HDG STEEL Conduit</v>
+      </c>
+      <c r="D4" t="str">
+        <v>OM4-DE-IS-0009</v>
+      </c>
+      <c r="E4" t="str">
+        <v>Y3-2</v>
+      </c>
+      <c r="F4" t="str">
+        <v>Trong kho</v>
+      </c>
+      <c r="G4" t="str">
+        <v/>
+      </c>
+      <c r="H4" t="str">
+        <v>18/08/2026</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>28/07/2026</v>
+      </c>
+      <c r="B5" t="str">
+        <v>OM4-DE-IS-0009-003</v>
+      </c>
+      <c r="C5" t="str">
+        <v>CONDUIT FITTINGS</v>
+      </c>
+      <c r="D5" t="str">
+        <v>OM4-DE-IS-0009</v>
+      </c>
+      <c r="E5" t="str">
+        <v>Y3-2</v>
+      </c>
+      <c r="F5" t="str">
+        <v>Trong kho</v>
+      </c>
+      <c r="G5" t="str">
+        <v/>
+      </c>
+      <c r="H5" t="str">
+        <v>18/08/2026</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>28/07/2026</v>
+      </c>
+      <c r="B6" t="str">
+        <v>OM4-DE-IS-0009-004</v>
+      </c>
+      <c r="C6" t="str">
+        <v>CONDUIT FITTINGS (Normal Bend)</v>
+      </c>
+      <c r="D6" t="str">
+        <v>OM4-DE-IS-0009</v>
+      </c>
+      <c r="E6" t="str">
+        <v>Y3-2</v>
+      </c>
+      <c r="F6" t="str">
+        <v>Trong kho</v>
+      </c>
+      <c r="G6" t="str">
+        <v/>
+      </c>
+      <c r="H6" t="str">
+        <v>18/08/2026</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>28/07/2026</v>
+      </c>
+      <c r="B7" t="str">
+        <v>OM4-DE-IS-0009-006</v>
+      </c>
+      <c r="C7" t="str">
+        <v>CONDUIT FITTINGS (Normal Bend)</v>
+      </c>
+      <c r="D7" t="str">
+        <v>OM4-DE-IS-0009</v>
+      </c>
+      <c r="E7" t="str">
+        <v>Y3-2</v>
+      </c>
+      <c r="F7" t="str">
+        <v>Trong kho</v>
+      </c>
+      <c r="G7" t="str">
+        <v/>
+      </c>
+      <c r="H7" t="str">
+        <v>18/08/2026</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>28/07/2026</v>
+      </c>
+      <c r="B8" t="str">
+        <v>OM4-DE-IS-0009-007</v>
+      </c>
+      <c r="C8" t="str">
+        <v>CONDUIT FITTINGS (Normal Bend)</v>
+      </c>
+      <c r="D8" t="str">
+        <v>OM4-DE-IS-0009</v>
+      </c>
+      <c r="E8" t="str">
+        <v>Y3-2</v>
+      </c>
+      <c r="F8" t="str">
+        <v>Trong kho</v>
+      </c>
+      <c r="G8" t="str">
+        <v/>
+      </c>
+      <c r="H8" t="str">
+        <v>18/08/2026</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>28/07/2026</v>
+      </c>
+      <c r="B9" t="str">
+        <v>OM4-DE-IS-0009-008</v>
+      </c>
+      <c r="C9" t="str">
+        <v>CONDUIT FITTINGS (Normal Bend)</v>
+      </c>
+      <c r="D9" t="str">
+        <v>OM4-DE-IS-0009</v>
+      </c>
+      <c r="E9" t="str">
+        <v>Y3-2</v>
+      </c>
+      <c r="F9" t="str">
+        <v>Trong kho</v>
+      </c>
+      <c r="G9" t="str">
+        <v/>
+      </c>
+      <c r="H9" t="str">
+        <v>18/08/2026</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>28/07/2026</v>
+      </c>
+      <c r="B10" t="str">
+        <v>OM4-DE-IS-0009-009</v>
+      </c>
+      <c r="C10" t="str">
+        <v>CONDUIT FITTINGS (Normal Bend)</v>
+      </c>
+      <c r="D10" t="str">
+        <v>OM4-DE-IS-0009</v>
+      </c>
+      <c r="E10" t="str">
+        <v>Y3-2</v>
+      </c>
+      <c r="F10" t="str">
+        <v>Trong kho</v>
+      </c>
+      <c r="G10" t="str">
+        <v/>
+      </c>
+      <c r="H10" t="str">
+        <v>18/08/2026</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>28/07/2026</v>
+      </c>
+      <c r="B11" t="str">
+        <v>OM4-DE-IS-0009-010</v>
+      </c>
+      <c r="C11" t="str">
+        <v>CONDUIT FITTINGS</v>
+      </c>
+      <c r="D11" t="str">
+        <v>OM4-DE-IS-0009</v>
+      </c>
+      <c r="E11" t="str">
+        <v>Y3-2</v>
+      </c>
+      <c r="F11" t="str">
+        <v>Trong kho</v>
+      </c>
+      <c r="G11" t="str">
+        <v/>
+      </c>
+      <c r="H11" t="str">
+        <v>18/08/2026</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>28/07/2026</v>
+      </c>
+      <c r="B12" t="str">
+        <v>OM4-DE-IS-0009-011</v>
+      </c>
+      <c r="C12" t="str">
+        <v>Flexible Conduit</v>
+      </c>
+      <c r="D12" t="str">
+        <v>OM4-DE-IS-0009</v>
+      </c>
+      <c r="E12" t="str">
+        <v>Y3-2</v>
+      </c>
+      <c r="F12" t="str">
+        <v>Trong kho</v>
+      </c>
+      <c r="G12" t="str">
+        <v/>
+      </c>
+      <c r="H12" t="str">
+        <v>18/08/2026</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>28/07/2026</v>
+      </c>
+      <c r="B13" t="str">
+        <v>OM4-DE-IS-0009-012</v>
+      </c>
+      <c r="C13" t="str">
+        <v>CONDUIT FITTINGS</v>
+      </c>
+      <c r="D13" t="str">
+        <v>OM4-DE-IS-0009</v>
+      </c>
+      <c r="E13" t="str">
+        <v>Y3-2</v>
+      </c>
+      <c r="F13" t="str">
+        <v>Trong kho</v>
+      </c>
+      <c r="G13" t="str">
+        <v/>
+      </c>
+      <c r="H13" t="str">
+        <v>18/08/2026</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>28/07/2026</v>
+      </c>
+      <c r="B14" t="str">
+        <v>OM4-DE-IS-0009-013</v>
+      </c>
+      <c r="C14" t="str">
+        <v>PULL BOX with C-COVER</v>
+      </c>
+      <c r="D14" t="str">
+        <v>OM4-DE-IS-0009</v>
+      </c>
+      <c r="E14" t="str">
+        <v>Y3-2</v>
+      </c>
+      <c r="F14" t="str">
+        <v>Trong kho</v>
+      </c>
+      <c r="G14" t="str">
+        <v/>
+      </c>
+      <c r="H14" t="str">
+        <v>18/08/2026</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>28/07/2026</v>
+      </c>
+      <c r="B15" t="str">
+        <v>OM4-DE-IS-0009-014</v>
+      </c>
+      <c r="C15" t="str">
+        <v>Post Base single Channel</v>
+      </c>
+      <c r="D15" t="str">
+        <v>OM4-DE-IS-0009</v>
+      </c>
+      <c r="E15" t="str">
+        <v>Y3-2</v>
+      </c>
+      <c r="F15" t="str">
+        <v>Trong kho</v>
+      </c>
+      <c r="G15" t="str">
+        <v/>
+      </c>
+      <c r="H15" t="str">
+        <v>18/08/2026</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>28/07/2026</v>
+      </c>
+      <c r="B16" t="str">
+        <v>OM4-DE-IS-0009-015</v>
+      </c>
+      <c r="C16" t="str">
+        <v>Unistrut Channel Single</v>
+      </c>
+      <c r="D16" t="str">
+        <v>OM4-DE-IS-0009</v>
+      </c>
+      <c r="E16" t="str">
+        <v>Y3-2</v>
+      </c>
+      <c r="F16" t="str">
+        <v>Trong kho</v>
+      </c>
+      <c r="G16" t="str">
+        <v/>
+      </c>
+      <c r="H16" t="str">
+        <v>18/08/2026</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>28/07/2026</v>
+      </c>
+      <c r="B17" t="str">
+        <v>OM4-DE-IS-0009-016</v>
+      </c>
+      <c r="C17" t="str">
+        <v>Uni-Struct Insert channel</v>
+      </c>
+      <c r="D17" t="str">
+        <v>OM4-DE-IS-0009</v>
+      </c>
+      <c r="E17" t="str">
+        <v>Y3-2</v>
+      </c>
+      <c r="F17" t="str">
+        <v>Trong kho</v>
+      </c>
+      <c r="G17" t="str">
+        <v/>
+      </c>
+      <c r="H17" t="str">
+        <v>18/08/2026</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>28/07/2026</v>
+      </c>
+      <c r="B18" t="str">
+        <v>OM4-DE-IS-0009-017</v>
+      </c>
+      <c r="C18" t="str">
+        <v>C- Channel</v>
+      </c>
+      <c r="D18" t="str">
+        <v>OM4-DE-IS-0009</v>
+      </c>
+      <c r="E18" t="str">
+        <v>Y3-2</v>
+      </c>
+      <c r="F18" t="str">
+        <v>Trong kho</v>
+      </c>
+      <c r="G18" t="str">
+        <v/>
+      </c>
+      <c r="H18" t="str">
+        <v>18/08/2026</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H18"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/du-lieu/chinh-sua-tay.xlsx
+++ b/du-lieu/chinh-sua-tay.xlsx
@@ -440,7 +440,7 @@
         <v>OM4-DE-IS-0009</v>
       </c>
       <c r="E2" t="str">
-        <v>Y3-2</v>
+        <v>Y3-1</v>
       </c>
       <c r="F2" t="str">
         <v>Trong kho</v>
@@ -466,7 +466,7 @@
         <v>OM4-DE-IS-0009</v>
       </c>
       <c r="E3" t="str">
-        <v>Y3-2</v>
+        <v>Y3-1</v>
       </c>
       <c r="F3" t="str">
         <v>Trong kho</v>
@@ -492,7 +492,7 @@
         <v>OM4-DE-IS-0009</v>
       </c>
       <c r="E4" t="str">
-        <v>Y3-2</v>
+        <v>Y3-1</v>
       </c>
       <c r="F4" t="str">
         <v>Trong kho</v>
@@ -518,7 +518,7 @@
         <v>OM4-DE-IS-0009</v>
       </c>
       <c r="E5" t="str">
-        <v>Y3-2</v>
+        <v>Y3-1</v>
       </c>
       <c r="F5" t="str">
         <v>Trong kho</v>
@@ -544,7 +544,7 @@
         <v>OM4-DE-IS-0009</v>
       </c>
       <c r="E6" t="str">
-        <v>Y3-2</v>
+        <v>Y3-1</v>
       </c>
       <c r="F6" t="str">
         <v>Trong kho</v>
@@ -570,7 +570,7 @@
         <v>OM4-DE-IS-0009</v>
       </c>
       <c r="E7" t="str">
-        <v>Y3-2</v>
+        <v>Y3-1</v>
       </c>
       <c r="F7" t="str">
         <v>Trong kho</v>
@@ -596,7 +596,7 @@
         <v>OM4-DE-IS-0009</v>
       </c>
       <c r="E8" t="str">
-        <v>Y3-2</v>
+        <v>Y3-1</v>
       </c>
       <c r="F8" t="str">
         <v>Trong kho</v>
@@ -622,7 +622,7 @@
         <v>OM4-DE-IS-0009</v>
       </c>
       <c r="E9" t="str">
-        <v>Y3-2</v>
+        <v>Y3-1</v>
       </c>
       <c r="F9" t="str">
         <v>Trong kho</v>
@@ -648,7 +648,7 @@
         <v>OM4-DE-IS-0009</v>
       </c>
       <c r="E10" t="str">
-        <v>Y3-2</v>
+        <v>Y3-1</v>
       </c>
       <c r="F10" t="str">
         <v>Trong kho</v>
@@ -674,7 +674,7 @@
         <v>OM4-DE-IS-0009</v>
       </c>
       <c r="E11" t="str">
-        <v>Y3-2</v>
+        <v>Y3-1</v>
       </c>
       <c r="F11" t="str">
         <v>Trong kho</v>
@@ -700,7 +700,7 @@
         <v>OM4-DE-IS-0009</v>
       </c>
       <c r="E12" t="str">
-        <v>Y3-2</v>
+        <v>Y3-1</v>
       </c>
       <c r="F12" t="str">
         <v>Trong kho</v>
@@ -726,7 +726,7 @@
         <v>OM4-DE-IS-0009</v>
       </c>
       <c r="E13" t="str">
-        <v>Y3-2</v>
+        <v>Y3-1</v>
       </c>
       <c r="F13" t="str">
         <v>Trong kho</v>
@@ -752,7 +752,7 @@
         <v>OM4-DE-IS-0009</v>
       </c>
       <c r="E14" t="str">
-        <v>Y3-2</v>
+        <v>Y3-1</v>
       </c>
       <c r="F14" t="str">
         <v>Trong kho</v>
@@ -778,7 +778,7 @@
         <v>OM4-DE-IS-0009</v>
       </c>
       <c r="E15" t="str">
-        <v>Y3-2</v>
+        <v>Y3-1</v>
       </c>
       <c r="F15" t="str">
         <v>Trong kho</v>
@@ -804,7 +804,7 @@
         <v>OM4-DE-IS-0009</v>
       </c>
       <c r="E16" t="str">
-        <v>Y3-2</v>
+        <v>Y3-1</v>
       </c>
       <c r="F16" t="str">
         <v>Trong kho</v>
@@ -830,7 +830,7 @@
         <v>OM4-DE-IS-0009</v>
       </c>
       <c r="E17" t="str">
-        <v>Y3-2</v>
+        <v>Y3-1</v>
       </c>
       <c r="F17" t="str">
         <v>Trong kho</v>
@@ -856,7 +856,7 @@
         <v>OM4-DE-IS-0009</v>
       </c>
       <c r="E18" t="str">
-        <v>Y3-2</v>
+        <v>Y3-1</v>
       </c>
       <c r="F18" t="str">
         <v>Trong kho</v>

--- a/du-lieu/chinh-sua-tay.xlsx
+++ b/du-lieu/chinh-sua-tay.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H18"/>
+  <dimension ref="A1:H19"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -868,9 +868,35 @@
         <v>18/08/2026</v>
       </c>
     </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>18/08/2026</v>
+      </c>
+      <c r="B19" t="str">
+        <v>OM4-P2-LS-0002-001</v>
+      </c>
+      <c r="C19" t="str">
+        <v>Stranded Bare Copper Conductor 240 sq.mm(C-240)</v>
+      </c>
+      <c r="D19" t="str">
+        <v>OM4-P2-LS-0002</v>
+      </c>
+      <c r="E19" t="str">
+        <v>S1</v>
+      </c>
+      <c r="F19" t="str">
+        <v>Trong kho</v>
+      </c>
+      <c r="G19" t="str">
+        <v/>
+      </c>
+      <c r="H19" t="str">
+        <v>18/08/2026</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H18"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H19"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/du-lieu/chinh-sua-tay.xlsx
+++ b/du-lieu/chinh-sua-tay.xlsx
@@ -407,7 +407,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:Y46"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -434,6 +434,57 @@
       <c r="H1" t="str">
         <v>Ngày cập nhật</v>
       </c>
+      <c r="I1" t="str">
+        <v>Nhà cung cấp/SX</v>
+      </c>
+      <c r="J1" t="str">
+        <v>Xuất xứ (C/O)</v>
+      </c>
+      <c r="K1" t="str">
+        <v>Mục bảng giá</v>
+      </c>
+      <c r="L1" t="str">
+        <v>Số lượng</v>
+      </c>
+      <c r="M1" t="str">
+        <v>Đơn vị SL</v>
+      </c>
+      <c r="N1" t="str">
+        <v>Loại kiện</v>
+      </c>
+      <c r="O1" t="str">
+        <v>Dài</v>
+      </c>
+      <c r="P1" t="str">
+        <v>Rộng</v>
+      </c>
+      <c r="Q1" t="str">
+        <v>Cao</v>
+      </c>
+      <c r="R1" t="str">
+        <v>Đơn vị kích thước</v>
+      </c>
+      <c r="S1" t="str">
+        <v>Thể tích (cbm)</v>
+      </c>
+      <c r="T1" t="str">
+        <v>Net Weight (kg)</v>
+      </c>
+      <c r="U1" t="str">
+        <v>Gross Weight (kg)</v>
+      </c>
+      <c r="V1" t="str">
+        <v>Tag No./Model</v>
+      </c>
+      <c r="W1" t="str">
+        <v>Hàng nguy hiểm</v>
+      </c>
+      <c r="X1" t="str">
+        <v>Phân loại lưu kho</v>
+      </c>
+      <c r="Y1" t="str">
+        <v>Remark</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
@@ -461,9 +512,3433 @@
         <v>18/08/2026</v>
       </c>
     </row>
+    <row r="3" xml:space="preserve">
+      <c r="A3" t="str">
+        <v>18/08/2026</v>
+      </c>
+      <c r="B3" t="str">
+        <v>OM4-P2-LS-0002-001</v>
+      </c>
+      <c r="C3" t="str" xml:space="preserve">
+        <v xml:space="preserve">Stranded Bare Copper Conductor 240 sq.mm_x000d_
+(C-240)</v>
+      </c>
+      <c r="D3" t="str">
+        <v>OM4-P2-LS-0002</v>
+      </c>
+      <c r="E3" t="str">
+        <v>S1</v>
+      </c>
+      <c r="F3" t="str">
+        <v>Trong kho</v>
+      </c>
+      <c r="G3" t="str">
+        <v/>
+      </c>
+      <c r="H3" t="str">
+        <v>18/08/2026</v>
+      </c>
+      <c r="I3" t="str">
+        <v/>
+      </c>
+      <c r="J3" t="str">
+        <v/>
+      </c>
+      <c r="K3" t="str">
+        <v/>
+      </c>
+      <c r="L3" t="str">
+        <v/>
+      </c>
+      <c r="M3" t="str">
+        <v/>
+      </c>
+      <c r="N3" t="str">
+        <v/>
+      </c>
+      <c r="O3" t="str">
+        <v/>
+      </c>
+      <c r="P3" t="str">
+        <v/>
+      </c>
+      <c r="Q3" t="str">
+        <v/>
+      </c>
+      <c r="R3" t="str">
+        <v/>
+      </c>
+      <c r="S3" t="str">
+        <v/>
+      </c>
+      <c r="T3" t="str">
+        <v/>
+      </c>
+      <c r="U3" t="str">
+        <v/>
+      </c>
+      <c r="V3" t="str">
+        <v/>
+      </c>
+      <c r="W3" t="str">
+        <v/>
+      </c>
+      <c r="X3" t="str">
+        <v/>
+      </c>
+      <c r="Y3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="4" xml:space="preserve">
+      <c r="A4" t="str">
+        <v>18/08/2026</v>
+      </c>
+      <c r="B4" t="str">
+        <v>OM4-P2-LS-0002-002</v>
+      </c>
+      <c r="C4" t="str" xml:space="preserve">
+        <v xml:space="preserve">Stranded Bare Copper Conductor 240 sq.mm_x000d_
+(C-240)</v>
+      </c>
+      <c r="D4" t="str">
+        <v>OM4-P2-LS-0002</v>
+      </c>
+      <c r="E4" t="str">
+        <v>S1</v>
+      </c>
+      <c r="F4" t="str">
+        <v>Trong kho</v>
+      </c>
+      <c r="G4" t="str">
+        <v/>
+      </c>
+      <c r="H4" t="str">
+        <v>18/08/2026</v>
+      </c>
+      <c r="I4" t="str">
+        <v/>
+      </c>
+      <c r="J4" t="str">
+        <v/>
+      </c>
+      <c r="K4" t="str">
+        <v/>
+      </c>
+      <c r="L4" t="str">
+        <v/>
+      </c>
+      <c r="M4" t="str">
+        <v/>
+      </c>
+      <c r="N4" t="str">
+        <v/>
+      </c>
+      <c r="O4" t="str">
+        <v/>
+      </c>
+      <c r="P4" t="str">
+        <v/>
+      </c>
+      <c r="Q4" t="str">
+        <v/>
+      </c>
+      <c r="R4" t="str">
+        <v/>
+      </c>
+      <c r="S4" t="str">
+        <v/>
+      </c>
+      <c r="T4" t="str">
+        <v/>
+      </c>
+      <c r="U4" t="str">
+        <v/>
+      </c>
+      <c r="V4" t="str">
+        <v/>
+      </c>
+      <c r="W4" t="str">
+        <v/>
+      </c>
+      <c r="X4" t="str">
+        <v/>
+      </c>
+      <c r="Y4" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="5" xml:space="preserve">
+      <c r="A5" t="str">
+        <v>18/08/2026</v>
+      </c>
+      <c r="B5" t="str">
+        <v>OM4-P2-LS-0002-004</v>
+      </c>
+      <c r="C5" t="str" xml:space="preserve">
+        <v xml:space="preserve">Stranded Bare Copper Conductor 240 sq.mm_x000d_
+(C-240)</v>
+      </c>
+      <c r="D5" t="str">
+        <v>OM4-P2-LS-0002</v>
+      </c>
+      <c r="E5" t="str">
+        <v>S1</v>
+      </c>
+      <c r="F5" t="str">
+        <v>Trong kho</v>
+      </c>
+      <c r="G5" t="str">
+        <v/>
+      </c>
+      <c r="H5" t="str">
+        <v>18/08/2026</v>
+      </c>
+      <c r="I5" t="str">
+        <v/>
+      </c>
+      <c r="J5" t="str">
+        <v/>
+      </c>
+      <c r="K5" t="str">
+        <v/>
+      </c>
+      <c r="L5" t="str">
+        <v/>
+      </c>
+      <c r="M5" t="str">
+        <v/>
+      </c>
+      <c r="N5" t="str">
+        <v/>
+      </c>
+      <c r="O5" t="str">
+        <v/>
+      </c>
+      <c r="P5" t="str">
+        <v/>
+      </c>
+      <c r="Q5" t="str">
+        <v/>
+      </c>
+      <c r="R5" t="str">
+        <v/>
+      </c>
+      <c r="S5" t="str">
+        <v/>
+      </c>
+      <c r="T5" t="str">
+        <v/>
+      </c>
+      <c r="U5" t="str">
+        <v/>
+      </c>
+      <c r="V5" t="str">
+        <v/>
+      </c>
+      <c r="W5" t="str">
+        <v/>
+      </c>
+      <c r="X5" t="str">
+        <v/>
+      </c>
+      <c r="Y5" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="6" xml:space="preserve">
+      <c r="A6" t="str">
+        <v>18/08/2026</v>
+      </c>
+      <c r="B6" t="str">
+        <v>OM4-P2-LS-0002-005</v>
+      </c>
+      <c r="C6" t="str" xml:space="preserve">
+        <v xml:space="preserve">Stranded Bare Copper Conductor 240 sq.mm_x000d_
+(C-240)</v>
+      </c>
+      <c r="D6" t="str">
+        <v>OM4-P2-LS-0002</v>
+      </c>
+      <c r="E6" t="str">
+        <v>S1</v>
+      </c>
+      <c r="F6" t="str">
+        <v>Trong kho</v>
+      </c>
+      <c r="G6" t="str">
+        <v/>
+      </c>
+      <c r="H6" t="str">
+        <v>18/08/2026</v>
+      </c>
+      <c r="I6" t="str">
+        <v/>
+      </c>
+      <c r="J6" t="str">
+        <v/>
+      </c>
+      <c r="K6" t="str">
+        <v/>
+      </c>
+      <c r="L6" t="str">
+        <v/>
+      </c>
+      <c r="M6" t="str">
+        <v/>
+      </c>
+      <c r="N6" t="str">
+        <v/>
+      </c>
+      <c r="O6" t="str">
+        <v/>
+      </c>
+      <c r="P6" t="str">
+        <v/>
+      </c>
+      <c r="Q6" t="str">
+        <v/>
+      </c>
+      <c r="R6" t="str">
+        <v/>
+      </c>
+      <c r="S6" t="str">
+        <v/>
+      </c>
+      <c r="T6" t="str">
+        <v/>
+      </c>
+      <c r="U6" t="str">
+        <v/>
+      </c>
+      <c r="V6" t="str">
+        <v/>
+      </c>
+      <c r="W6" t="str">
+        <v/>
+      </c>
+      <c r="X6" t="str">
+        <v/>
+      </c>
+      <c r="Y6" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>18/08/2026</v>
+      </c>
+      <c r="B7" t="str">
+        <v>OM4-P2-LS-0002-006</v>
+      </c>
+      <c r="C7" t="str">
+        <v>PVC Insulated Copper Conductor (Yellow and Green) - 240 sq.mm (CV 240,  0.6/1kV)</v>
+      </c>
+      <c r="D7" t="str">
+        <v>OM4-P2-LS-0002</v>
+      </c>
+      <c r="E7" t="str">
+        <v>S1</v>
+      </c>
+      <c r="F7" t="str">
+        <v>Trong kho</v>
+      </c>
+      <c r="G7" t="str">
+        <v/>
+      </c>
+      <c r="H7" t="str">
+        <v>18/08/2026</v>
+      </c>
+      <c r="I7" t="str">
+        <v/>
+      </c>
+      <c r="J7" t="str">
+        <v/>
+      </c>
+      <c r="K7" t="str">
+        <v/>
+      </c>
+      <c r="L7" t="str">
+        <v/>
+      </c>
+      <c r="M7" t="str">
+        <v/>
+      </c>
+      <c r="N7" t="str">
+        <v/>
+      </c>
+      <c r="O7" t="str">
+        <v/>
+      </c>
+      <c r="P7" t="str">
+        <v/>
+      </c>
+      <c r="Q7" t="str">
+        <v/>
+      </c>
+      <c r="R7" t="str">
+        <v/>
+      </c>
+      <c r="S7" t="str">
+        <v/>
+      </c>
+      <c r="T7" t="str">
+        <v/>
+      </c>
+      <c r="U7" t="str">
+        <v/>
+      </c>
+      <c r="V7" t="str">
+        <v/>
+      </c>
+      <c r="W7" t="str">
+        <v/>
+      </c>
+      <c r="X7" t="str">
+        <v/>
+      </c>
+      <c r="Y7" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>18/08/2026</v>
+      </c>
+      <c r="B8" t="str">
+        <v>OM4-P2-LS-0002-007</v>
+      </c>
+      <c r="C8" t="str">
+        <v>PVC Insulated Copper Conductor (Yellow and Green) - 150 sq.mm (CV 150,  0.6/1kV)</v>
+      </c>
+      <c r="D8" t="str">
+        <v>OM4-P2-LS-0002</v>
+      </c>
+      <c r="E8" t="str">
+        <v>S1</v>
+      </c>
+      <c r="F8" t="str">
+        <v>Trong kho</v>
+      </c>
+      <c r="G8" t="str">
+        <v/>
+      </c>
+      <c r="H8" t="str">
+        <v>18/08/2026</v>
+      </c>
+      <c r="I8" t="str">
+        <v/>
+      </c>
+      <c r="J8" t="str">
+        <v/>
+      </c>
+      <c r="K8" t="str">
+        <v/>
+      </c>
+      <c r="L8" t="str">
+        <v/>
+      </c>
+      <c r="M8" t="str">
+        <v/>
+      </c>
+      <c r="N8" t="str">
+        <v/>
+      </c>
+      <c r="O8" t="str">
+        <v/>
+      </c>
+      <c r="P8" t="str">
+        <v/>
+      </c>
+      <c r="Q8" t="str">
+        <v/>
+      </c>
+      <c r="R8" t="str">
+        <v/>
+      </c>
+      <c r="S8" t="str">
+        <v/>
+      </c>
+      <c r="T8" t="str">
+        <v/>
+      </c>
+      <c r="U8" t="str">
+        <v/>
+      </c>
+      <c r="V8" t="str">
+        <v/>
+      </c>
+      <c r="W8" t="str">
+        <v/>
+      </c>
+      <c r="X8" t="str">
+        <v/>
+      </c>
+      <c r="Y8" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>18/08/2026</v>
+      </c>
+      <c r="B9" t="str">
+        <v>OM4-P2-LS-0002-008</v>
+      </c>
+      <c r="C9" t="str">
+        <v>PVC Insulated Copper Conductor (Yellow and Green) - 95 sq.mm (CV 95,  0.6/1kV)</v>
+      </c>
+      <c r="D9" t="str">
+        <v>OM4-P2-LS-0002</v>
+      </c>
+      <c r="E9" t="str">
+        <v>S1</v>
+      </c>
+      <c r="F9" t="str">
+        <v>Trong kho</v>
+      </c>
+      <c r="G9" t="str">
+        <v/>
+      </c>
+      <c r="H9" t="str">
+        <v>18/08/2026</v>
+      </c>
+      <c r="I9" t="str">
+        <v/>
+      </c>
+      <c r="J9" t="str">
+        <v/>
+      </c>
+      <c r="K9" t="str">
+        <v/>
+      </c>
+      <c r="L9" t="str">
+        <v/>
+      </c>
+      <c r="M9" t="str">
+        <v/>
+      </c>
+      <c r="N9" t="str">
+        <v/>
+      </c>
+      <c r="O9" t="str">
+        <v/>
+      </c>
+      <c r="P9" t="str">
+        <v/>
+      </c>
+      <c r="Q9" t="str">
+        <v/>
+      </c>
+      <c r="R9" t="str">
+        <v/>
+      </c>
+      <c r="S9" t="str">
+        <v/>
+      </c>
+      <c r="T9" t="str">
+        <v/>
+      </c>
+      <c r="U9" t="str">
+        <v/>
+      </c>
+      <c r="V9" t="str">
+        <v/>
+      </c>
+      <c r="W9" t="str">
+        <v/>
+      </c>
+      <c r="X9" t="str">
+        <v/>
+      </c>
+      <c r="Y9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>18/08/2026</v>
+      </c>
+      <c r="B10" t="str">
+        <v>OM4-P2-LS-0002-009</v>
+      </c>
+      <c r="C10" t="str">
+        <v>Welding mold D type (Cross connection cable 240x240 include: hand clamp, flint igniter, PVC &amp; Steel brush).</v>
+      </c>
+      <c r="D10" t="str">
+        <v>OM4-P2-LS-0002</v>
+      </c>
+      <c r="E10" t="str">
+        <v>S1</v>
+      </c>
+      <c r="F10" t="str">
+        <v>Trong kho</v>
+      </c>
+      <c r="G10" t="str">
+        <v/>
+      </c>
+      <c r="H10" t="str">
+        <v>18/08/2026</v>
+      </c>
+      <c r="I10" t="str">
+        <v/>
+      </c>
+      <c r="J10" t="str">
+        <v/>
+      </c>
+      <c r="K10" t="str">
+        <v/>
+      </c>
+      <c r="L10" t="str">
+        <v/>
+      </c>
+      <c r="M10" t="str">
+        <v/>
+      </c>
+      <c r="N10" t="str">
+        <v/>
+      </c>
+      <c r="O10" t="str">
+        <v/>
+      </c>
+      <c r="P10" t="str">
+        <v/>
+      </c>
+      <c r="Q10" t="str">
+        <v/>
+      </c>
+      <c r="R10" t="str">
+        <v/>
+      </c>
+      <c r="S10" t="str">
+        <v/>
+      </c>
+      <c r="T10" t="str">
+        <v/>
+      </c>
+      <c r="U10" t="str">
+        <v/>
+      </c>
+      <c r="V10" t="str">
+        <v/>
+      </c>
+      <c r="W10" t="str">
+        <v/>
+      </c>
+      <c r="X10" t="str">
+        <v/>
+      </c>
+      <c r="Y10" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>18/08/2026</v>
+      </c>
+      <c r="B11" t="str">
+        <v>OM4-P2-LS-0002-010</v>
+      </c>
+      <c r="C11" t="str">
+        <v>Welding mold D type (T connection cable 240 &amp; cable 150 include: hand clamp, flint igniter, PVC &amp; Steel brush).</v>
+      </c>
+      <c r="D11" t="str">
+        <v>OM4-P2-LS-0002</v>
+      </c>
+      <c r="E11" t="str">
+        <v>S1</v>
+      </c>
+      <c r="F11" t="str">
+        <v>Trong kho</v>
+      </c>
+      <c r="G11" t="str">
+        <v/>
+      </c>
+      <c r="H11" t="str">
+        <v>18/08/2026</v>
+      </c>
+      <c r="I11" t="str">
+        <v/>
+      </c>
+      <c r="J11" t="str">
+        <v/>
+      </c>
+      <c r="K11" t="str">
+        <v/>
+      </c>
+      <c r="L11" t="str">
+        <v/>
+      </c>
+      <c r="M11" t="str">
+        <v/>
+      </c>
+      <c r="N11" t="str">
+        <v/>
+      </c>
+      <c r="O11" t="str">
+        <v/>
+      </c>
+      <c r="P11" t="str">
+        <v/>
+      </c>
+      <c r="Q11" t="str">
+        <v/>
+      </c>
+      <c r="R11" t="str">
+        <v/>
+      </c>
+      <c r="S11" t="str">
+        <v/>
+      </c>
+      <c r="T11" t="str">
+        <v/>
+      </c>
+      <c r="U11" t="str">
+        <v/>
+      </c>
+      <c r="V11" t="str">
+        <v/>
+      </c>
+      <c r="W11" t="str">
+        <v/>
+      </c>
+      <c r="X11" t="str">
+        <v/>
+      </c>
+      <c r="Y11" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>18/08/2026</v>
+      </c>
+      <c r="B12" t="str">
+        <v>OM4-P2-LS-0002-011</v>
+      </c>
+      <c r="C12" t="str">
+        <v>Welding mold D type (T connection cable 240 &amp; cable 95 include: hand clamp, flint igniter, PVC &amp; Steel brush).</v>
+      </c>
+      <c r="D12" t="str">
+        <v>OM4-P2-LS-0002</v>
+      </c>
+      <c r="E12" t="str">
+        <v>S1</v>
+      </c>
+      <c r="F12" t="str">
+        <v>Trong kho</v>
+      </c>
+      <c r="G12" t="str">
+        <v/>
+      </c>
+      <c r="H12" t="str">
+        <v>18/08/2026</v>
+      </c>
+      <c r="I12" t="str">
+        <v/>
+      </c>
+      <c r="J12" t="str">
+        <v/>
+      </c>
+      <c r="K12" t="str">
+        <v/>
+      </c>
+      <c r="L12" t="str">
+        <v/>
+      </c>
+      <c r="M12" t="str">
+        <v/>
+      </c>
+      <c r="N12" t="str">
+        <v/>
+      </c>
+      <c r="O12" t="str">
+        <v/>
+      </c>
+      <c r="P12" t="str">
+        <v/>
+      </c>
+      <c r="Q12" t="str">
+        <v/>
+      </c>
+      <c r="R12" t="str">
+        <v/>
+      </c>
+      <c r="S12" t="str">
+        <v/>
+      </c>
+      <c r="T12" t="str">
+        <v/>
+      </c>
+      <c r="U12" t="str">
+        <v/>
+      </c>
+      <c r="V12" t="str">
+        <v/>
+      </c>
+      <c r="W12" t="str">
+        <v/>
+      </c>
+      <c r="X12" t="str">
+        <v/>
+      </c>
+      <c r="Y12" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>18/08/2026</v>
+      </c>
+      <c r="B13" t="str">
+        <v>OM4-P2-LS-0002-012</v>
+      </c>
+      <c r="C13" t="str">
+        <v>Welding mold C type (T connection cable 240 &amp; cable 35 include: hand clamp, flint igniter, PVC &amp; Steel brush).</v>
+      </c>
+      <c r="D13" t="str">
+        <v>OM4-P2-LS-0002</v>
+      </c>
+      <c r="E13" t="str">
+        <v>S1</v>
+      </c>
+      <c r="F13" t="str">
+        <v>Trong kho</v>
+      </c>
+      <c r="G13" t="str">
+        <v/>
+      </c>
+      <c r="H13" t="str">
+        <v>18/08/2026</v>
+      </c>
+      <c r="I13" t="str">
+        <v/>
+      </c>
+      <c r="J13" t="str">
+        <v/>
+      </c>
+      <c r="K13" t="str">
+        <v/>
+      </c>
+      <c r="L13" t="str">
+        <v/>
+      </c>
+      <c r="M13" t="str">
+        <v/>
+      </c>
+      <c r="N13" t="str">
+        <v/>
+      </c>
+      <c r="O13" t="str">
+        <v/>
+      </c>
+      <c r="P13" t="str">
+        <v/>
+      </c>
+      <c r="Q13" t="str">
+        <v/>
+      </c>
+      <c r="R13" t="str">
+        <v/>
+      </c>
+      <c r="S13" t="str">
+        <v/>
+      </c>
+      <c r="T13" t="str">
+        <v/>
+      </c>
+      <c r="U13" t="str">
+        <v/>
+      </c>
+      <c r="V13" t="str">
+        <v/>
+      </c>
+      <c r="W13" t="str">
+        <v/>
+      </c>
+      <c r="X13" t="str">
+        <v/>
+      </c>
+      <c r="Y13" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>18/08/2026</v>
+      </c>
+      <c r="B14" t="str">
+        <v>OM4-P2-LS-0002-013</v>
+      </c>
+      <c r="C14" t="str">
+        <v>Welding mold C type (T connection cable 240 &amp; cable 16 include: hand clamp, flint igniter, PVC &amp; Steel brush).</v>
+      </c>
+      <c r="D14" t="str">
+        <v>OM4-P2-LS-0002</v>
+      </c>
+      <c r="E14" t="str">
+        <v>S1</v>
+      </c>
+      <c r="F14" t="str">
+        <v>Trong kho</v>
+      </c>
+      <c r="G14" t="str">
+        <v/>
+      </c>
+      <c r="H14" t="str">
+        <v>18/08/2026</v>
+      </c>
+      <c r="I14" t="str">
+        <v/>
+      </c>
+      <c r="J14" t="str">
+        <v/>
+      </c>
+      <c r="K14" t="str">
+        <v/>
+      </c>
+      <c r="L14" t="str">
+        <v/>
+      </c>
+      <c r="M14" t="str">
+        <v/>
+      </c>
+      <c r="N14" t="str">
+        <v/>
+      </c>
+      <c r="O14" t="str">
+        <v/>
+      </c>
+      <c r="P14" t="str">
+        <v/>
+      </c>
+      <c r="Q14" t="str">
+        <v/>
+      </c>
+      <c r="R14" t="str">
+        <v/>
+      </c>
+      <c r="S14" t="str">
+        <v/>
+      </c>
+      <c r="T14" t="str">
+        <v/>
+      </c>
+      <c r="U14" t="str">
+        <v/>
+      </c>
+      <c r="V14" t="str">
+        <v/>
+      </c>
+      <c r="W14" t="str">
+        <v/>
+      </c>
+      <c r="X14" t="str">
+        <v/>
+      </c>
+      <c r="Y14" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>18/08/2026</v>
+      </c>
+      <c r="B15" t="str">
+        <v>OM4-P2-LS-0002-014</v>
+      </c>
+      <c r="C15" t="str">
+        <v>Welding mold D type (Horizontal cable 240 to rod Φ18 connection include: hand clamp, flint igniter, PVC &amp; Steel brush).</v>
+      </c>
+      <c r="D15" t="str">
+        <v>OM4-P2-LS-0002</v>
+      </c>
+      <c r="E15" t="str">
+        <v>S1</v>
+      </c>
+      <c r="F15" t="str">
+        <v>Trong kho</v>
+      </c>
+      <c r="G15" t="str">
+        <v/>
+      </c>
+      <c r="H15" t="str">
+        <v>18/08/2026</v>
+      </c>
+      <c r="I15" t="str">
+        <v/>
+      </c>
+      <c r="J15" t="str">
+        <v/>
+      </c>
+      <c r="K15" t="str">
+        <v/>
+      </c>
+      <c r="L15" t="str">
+        <v/>
+      </c>
+      <c r="M15" t="str">
+        <v/>
+      </c>
+      <c r="N15" t="str">
+        <v/>
+      </c>
+      <c r="O15" t="str">
+        <v/>
+      </c>
+      <c r="P15" t="str">
+        <v/>
+      </c>
+      <c r="Q15" t="str">
+        <v/>
+      </c>
+      <c r="R15" t="str">
+        <v/>
+      </c>
+      <c r="S15" t="str">
+        <v/>
+      </c>
+      <c r="T15" t="str">
+        <v/>
+      </c>
+      <c r="U15" t="str">
+        <v/>
+      </c>
+      <c r="V15" t="str">
+        <v/>
+      </c>
+      <c r="W15" t="str">
+        <v/>
+      </c>
+      <c r="X15" t="str">
+        <v/>
+      </c>
+      <c r="Y15" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="16" xml:space="preserve">
+      <c r="A16" t="str">
+        <v>18/08/2026</v>
+      </c>
+      <c r="B16" t="str">
+        <v>OM4-P2-LS-0002-015</v>
+      </c>
+      <c r="C16" t="str" xml:space="preserve">
+        <v xml:space="preserve">Pure copper earth rod Φ18x3m, external thread both sides, factory tolerance._x000d_
+ + Driving heads, internal thread for rod Φ18 (Black steel)._x000d_
+ + Driving tip, internal thread for rod Φ18 (Black steel).</v>
+      </c>
+      <c r="D16" t="str">
+        <v>OM4-P2-LS-0002</v>
+      </c>
+      <c r="E16" t="str">
+        <v>S1</v>
+      </c>
+      <c r="F16" t="str">
+        <v>Trong kho</v>
+      </c>
+      <c r="G16" t="str">
+        <v/>
+      </c>
+      <c r="H16" t="str">
+        <v>18/08/2026</v>
+      </c>
+      <c r="I16" t="str">
+        <v/>
+      </c>
+      <c r="J16" t="str">
+        <v/>
+      </c>
+      <c r="K16" t="str">
+        <v/>
+      </c>
+      <c r="L16" t="str">
+        <v/>
+      </c>
+      <c r="M16" t="str">
+        <v/>
+      </c>
+      <c r="N16" t="str">
+        <v/>
+      </c>
+      <c r="O16" t="str">
+        <v/>
+      </c>
+      <c r="P16" t="str">
+        <v/>
+      </c>
+      <c r="Q16" t="str">
+        <v/>
+      </c>
+      <c r="R16" t="str">
+        <v/>
+      </c>
+      <c r="S16" t="str">
+        <v/>
+      </c>
+      <c r="T16" t="str">
+        <v/>
+      </c>
+      <c r="U16" t="str">
+        <v/>
+      </c>
+      <c r="V16" t="str">
+        <v/>
+      </c>
+      <c r="W16" t="str">
+        <v/>
+      </c>
+      <c r="X16" t="str">
+        <v/>
+      </c>
+      <c r="Y16" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="17" xml:space="preserve">
+      <c r="A17" t="str">
+        <v>18/08/2026</v>
+      </c>
+      <c r="B17" t="str">
+        <v>OM4-P2-LS-0002-016</v>
+      </c>
+      <c r="C17" t="str" xml:space="preserve">
+        <v xml:space="preserve">Concrete eath pit (Dim: 310x310x170mm)_x000d_
+ + Copper earth bar 5 connection points Φ12, Dim: 50x5x300 c/w: SS304 bolds, nuts, spring &amp; flat washers M12x40.</v>
+      </c>
+      <c r="D17" t="str">
+        <v>OM4-P2-LS-0002</v>
+      </c>
+      <c r="E17" t="str">
+        <v>S1</v>
+      </c>
+      <c r="F17" t="str">
+        <v>Trong kho</v>
+      </c>
+      <c r="G17" t="str">
+        <v/>
+      </c>
+      <c r="H17" t="str">
+        <v>18/08/2026</v>
+      </c>
+      <c r="I17" t="str">
+        <v/>
+      </c>
+      <c r="J17" t="str">
+        <v/>
+      </c>
+      <c r="K17" t="str">
+        <v/>
+      </c>
+      <c r="L17" t="str">
+        <v/>
+      </c>
+      <c r="M17" t="str">
+        <v/>
+      </c>
+      <c r="N17" t="str">
+        <v/>
+      </c>
+      <c r="O17" t="str">
+        <v/>
+      </c>
+      <c r="P17" t="str">
+        <v/>
+      </c>
+      <c r="Q17" t="str">
+        <v/>
+      </c>
+      <c r="R17" t="str">
+        <v/>
+      </c>
+      <c r="S17" t="str">
+        <v/>
+      </c>
+      <c r="T17" t="str">
+        <v/>
+      </c>
+      <c r="U17" t="str">
+        <v/>
+      </c>
+      <c r="V17" t="str">
+        <v/>
+      </c>
+      <c r="W17" t="str">
+        <v/>
+      </c>
+      <c r="X17" t="str">
+        <v/>
+      </c>
+      <c r="Y17" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="18" xml:space="preserve">
+      <c r="A18" t="str">
+        <v>18/08/2026</v>
+      </c>
+      <c r="B18" t="str">
+        <v>OM4-P2-LS-0002-017</v>
+      </c>
+      <c r="C18" t="str" xml:space="preserve">
+        <v xml:space="preserve">Concrete eath pit (Dim: 310x310x170mm)_x000d_
+ + Copper earth bar 5 connection points Φ12, Dim: 50x5x300 c/w: SS304 bolds, nuts, spring &amp; flat washers M12x40.</v>
+      </c>
+      <c r="D18" t="str">
+        <v>OM4-P2-LS-0002</v>
+      </c>
+      <c r="E18" t="str">
+        <v>S1</v>
+      </c>
+      <c r="F18" t="str">
+        <v>Trong kho</v>
+      </c>
+      <c r="G18" t="str">
+        <v/>
+      </c>
+      <c r="H18" t="str">
+        <v>18/08/2026</v>
+      </c>
+      <c r="I18" t="str">
+        <v/>
+      </c>
+      <c r="J18" t="str">
+        <v/>
+      </c>
+      <c r="K18" t="str">
+        <v/>
+      </c>
+      <c r="L18" t="str">
+        <v/>
+      </c>
+      <c r="M18" t="str">
+        <v/>
+      </c>
+      <c r="N18" t="str">
+        <v/>
+      </c>
+      <c r="O18" t="str">
+        <v/>
+      </c>
+      <c r="P18" t="str">
+        <v/>
+      </c>
+      <c r="Q18" t="str">
+        <v/>
+      </c>
+      <c r="R18" t="str">
+        <v/>
+      </c>
+      <c r="S18" t="str">
+        <v/>
+      </c>
+      <c r="T18" t="str">
+        <v/>
+      </c>
+      <c r="U18" t="str">
+        <v/>
+      </c>
+      <c r="V18" t="str">
+        <v/>
+      </c>
+      <c r="W18" t="str">
+        <v/>
+      </c>
+      <c r="X18" t="str">
+        <v/>
+      </c>
+      <c r="Y18" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="19" xml:space="preserve">
+      <c r="A19" t="str">
+        <v>18/08/2026</v>
+      </c>
+      <c r="B19" t="str">
+        <v>OM4-P2-LS-0002-018</v>
+      </c>
+      <c r="C19" t="str" xml:space="preserve">
+        <v xml:space="preserve">Concrete eath pit (Dim: 310x310x170mm)_x000d_
+ + Copper earth bar 5 connection points Φ12, Dim: 50x5x300 c/w: SS304 bolds, nuts, spring &amp; flat washers M12x40.</v>
+      </c>
+      <c r="D19" t="str">
+        <v>OM4-P2-LS-0002</v>
+      </c>
+      <c r="E19" t="str">
+        <v>S1</v>
+      </c>
+      <c r="F19" t="str">
+        <v>Trong kho</v>
+      </c>
+      <c r="G19" t="str">
+        <v/>
+      </c>
+      <c r="H19" t="str">
+        <v>18/08/2026</v>
+      </c>
+      <c r="I19" t="str">
+        <v/>
+      </c>
+      <c r="J19" t="str">
+        <v/>
+      </c>
+      <c r="K19" t="str">
+        <v/>
+      </c>
+      <c r="L19" t="str">
+        <v/>
+      </c>
+      <c r="M19" t="str">
+        <v/>
+      </c>
+      <c r="N19" t="str">
+        <v/>
+      </c>
+      <c r="O19" t="str">
+        <v/>
+      </c>
+      <c r="P19" t="str">
+        <v/>
+      </c>
+      <c r="Q19" t="str">
+        <v/>
+      </c>
+      <c r="R19" t="str">
+        <v/>
+      </c>
+      <c r="S19" t="str">
+        <v/>
+      </c>
+      <c r="T19" t="str">
+        <v/>
+      </c>
+      <c r="U19" t="str">
+        <v/>
+      </c>
+      <c r="V19" t="str">
+        <v/>
+      </c>
+      <c r="W19" t="str">
+        <v/>
+      </c>
+      <c r="X19" t="str">
+        <v/>
+      </c>
+      <c r="Y19" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="20" xml:space="preserve">
+      <c r="A20" t="str">
+        <v>18/08/2026</v>
+      </c>
+      <c r="B20" t="str">
+        <v>OM4-P2-LS-0002-019</v>
+      </c>
+      <c r="C20" t="str" xml:space="preserve">
+        <v xml:space="preserve">Concrete eath pit (Dim: 310x310x170mm)_x000d_
+ + Copper earth bar 5 connection points Φ12, Dim: 50x5x300 c/w: SS304 bolds, nuts, spring &amp; flat washers M12x40.</v>
+      </c>
+      <c r="D20" t="str">
+        <v>OM4-P2-LS-0002</v>
+      </c>
+      <c r="E20" t="str">
+        <v>S1</v>
+      </c>
+      <c r="F20" t="str">
+        <v>Trong kho</v>
+      </c>
+      <c r="G20" t="str">
+        <v/>
+      </c>
+      <c r="H20" t="str">
+        <v>18/08/2026</v>
+      </c>
+      <c r="I20" t="str">
+        <v/>
+      </c>
+      <c r="J20" t="str">
+        <v/>
+      </c>
+      <c r="K20" t="str">
+        <v/>
+      </c>
+      <c r="L20" t="str">
+        <v/>
+      </c>
+      <c r="M20" t="str">
+        <v/>
+      </c>
+      <c r="N20" t="str">
+        <v/>
+      </c>
+      <c r="O20" t="str">
+        <v/>
+      </c>
+      <c r="P20" t="str">
+        <v/>
+      </c>
+      <c r="Q20" t="str">
+        <v/>
+      </c>
+      <c r="R20" t="str">
+        <v/>
+      </c>
+      <c r="S20" t="str">
+        <v/>
+      </c>
+      <c r="T20" t="str">
+        <v/>
+      </c>
+      <c r="U20" t="str">
+        <v/>
+      </c>
+      <c r="V20" t="str">
+        <v/>
+      </c>
+      <c r="W20" t="str">
+        <v/>
+      </c>
+      <c r="X20" t="str">
+        <v/>
+      </c>
+      <c r="Y20" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="21" xml:space="preserve">
+      <c r="A21" t="str">
+        <v>18/08/2026</v>
+      </c>
+      <c r="B21" t="str">
+        <v>OM4-P2-LS-0002-020</v>
+      </c>
+      <c r="C21" t="str" xml:space="preserve">
+        <v xml:space="preserve">Concrete eath pit (Dim: 310x310x170mm)_x000d_
+ + Copper earth bar 5 connection points Φ12, Dim: 50x5x300 c/w: SS304 bolds, nuts, spring &amp; flat washers M12x40.</v>
+      </c>
+      <c r="D21" t="str">
+        <v>OM4-P2-LS-0002</v>
+      </c>
+      <c r="E21" t="str">
+        <v>S1</v>
+      </c>
+      <c r="F21" t="str">
+        <v>Trong kho</v>
+      </c>
+      <c r="G21" t="str">
+        <v/>
+      </c>
+      <c r="H21" t="str">
+        <v>18/08/2026</v>
+      </c>
+      <c r="I21" t="str">
+        <v/>
+      </c>
+      <c r="J21" t="str">
+        <v/>
+      </c>
+      <c r="K21" t="str">
+        <v/>
+      </c>
+      <c r="L21" t="str">
+        <v/>
+      </c>
+      <c r="M21" t="str">
+        <v/>
+      </c>
+      <c r="N21" t="str">
+        <v/>
+      </c>
+      <c r="O21" t="str">
+        <v/>
+      </c>
+      <c r="P21" t="str">
+        <v/>
+      </c>
+      <c r="Q21" t="str">
+        <v/>
+      </c>
+      <c r="R21" t="str">
+        <v/>
+      </c>
+      <c r="S21" t="str">
+        <v/>
+      </c>
+      <c r="T21" t="str">
+        <v/>
+      </c>
+      <c r="U21" t="str">
+        <v/>
+      </c>
+      <c r="V21" t="str">
+        <v/>
+      </c>
+      <c r="W21" t="str">
+        <v/>
+      </c>
+      <c r="X21" t="str">
+        <v/>
+      </c>
+      <c r="Y21" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="22" xml:space="preserve">
+      <c r="A22" t="str">
+        <v>18/08/2026</v>
+      </c>
+      <c r="B22" t="str">
+        <v>OM4-P2-LS-0002-021</v>
+      </c>
+      <c r="C22" t="str" xml:space="preserve">
+        <v xml:space="preserve">Concrete eath pit (Dim: 310x310x170mm)_x000d_
+ + Copper earth bar 5 connection points Φ12, Dim: 50x5x300 c/w: SS304 bolds, nuts, spring &amp; flat washers M12x40.</v>
+      </c>
+      <c r="D22" t="str">
+        <v>OM4-P2-LS-0002</v>
+      </c>
+      <c r="E22" t="str">
+        <v>S1</v>
+      </c>
+      <c r="F22" t="str">
+        <v>Trong kho</v>
+      </c>
+      <c r="G22" t="str">
+        <v/>
+      </c>
+      <c r="H22" t="str">
+        <v>18/08/2026</v>
+      </c>
+      <c r="I22" t="str">
+        <v/>
+      </c>
+      <c r="J22" t="str">
+        <v/>
+      </c>
+      <c r="K22" t="str">
+        <v/>
+      </c>
+      <c r="L22" t="str">
+        <v/>
+      </c>
+      <c r="M22" t="str">
+        <v/>
+      </c>
+      <c r="N22" t="str">
+        <v/>
+      </c>
+      <c r="O22" t="str">
+        <v/>
+      </c>
+      <c r="P22" t="str">
+        <v/>
+      </c>
+      <c r="Q22" t="str">
+        <v/>
+      </c>
+      <c r="R22" t="str">
+        <v/>
+      </c>
+      <c r="S22" t="str">
+        <v/>
+      </c>
+      <c r="T22" t="str">
+        <v/>
+      </c>
+      <c r="U22" t="str">
+        <v/>
+      </c>
+      <c r="V22" t="str">
+        <v/>
+      </c>
+      <c r="W22" t="str">
+        <v/>
+      </c>
+      <c r="X22" t="str">
+        <v/>
+      </c>
+      <c r="Y22" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="23" xml:space="preserve">
+      <c r="A23" t="str">
+        <v>18/08/2026</v>
+      </c>
+      <c r="B23" t="str">
+        <v>OM4-P2-LS-0002-022</v>
+      </c>
+      <c r="C23" t="str" xml:space="preserve">
+        <v xml:space="preserve">Concrete eath pit (Dim: 310x310x170mm)_x000d_
+ + Copper earth bar 5 connection points Φ12, Dim: 50x5x300 c/w: SS304 bolds, nuts, spring &amp; flat washers M12x40.</v>
+      </c>
+      <c r="D23" t="str">
+        <v>OM4-P2-LS-0002</v>
+      </c>
+      <c r="E23" t="str">
+        <v>S1</v>
+      </c>
+      <c r="F23" t="str">
+        <v>Trong kho</v>
+      </c>
+      <c r="G23" t="str">
+        <v/>
+      </c>
+      <c r="H23" t="str">
+        <v>18/08/2026</v>
+      </c>
+      <c r="I23" t="str">
+        <v/>
+      </c>
+      <c r="J23" t="str">
+        <v/>
+      </c>
+      <c r="K23" t="str">
+        <v/>
+      </c>
+      <c r="L23" t="str">
+        <v/>
+      </c>
+      <c r="M23" t="str">
+        <v/>
+      </c>
+      <c r="N23" t="str">
+        <v/>
+      </c>
+      <c r="O23" t="str">
+        <v/>
+      </c>
+      <c r="P23" t="str">
+        <v/>
+      </c>
+      <c r="Q23" t="str">
+        <v/>
+      </c>
+      <c r="R23" t="str">
+        <v/>
+      </c>
+      <c r="S23" t="str">
+        <v/>
+      </c>
+      <c r="T23" t="str">
+        <v/>
+      </c>
+      <c r="U23" t="str">
+        <v/>
+      </c>
+      <c r="V23" t="str">
+        <v/>
+      </c>
+      <c r="W23" t="str">
+        <v/>
+      </c>
+      <c r="X23" t="str">
+        <v/>
+      </c>
+      <c r="Y23" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="24" xml:space="preserve">
+      <c r="A24" t="str">
+        <v>18/08/2026</v>
+      </c>
+      <c r="B24" t="str">
+        <v>OM4-P2-LS-0002-023</v>
+      </c>
+      <c r="C24" t="str" xml:space="preserve">
+        <v xml:space="preserve">Concrete eath pit (Dim: 310x310x170mm)_x000d_
+ + Copper earth bar 5 connection points Φ12, Dim: 50x5x300 c/w: SS304 bolds, nuts, spring &amp; flat washers M12x40.</v>
+      </c>
+      <c r="D24" t="str">
+        <v>OM4-P2-LS-0002</v>
+      </c>
+      <c r="E24" t="str">
+        <v>S1</v>
+      </c>
+      <c r="F24" t="str">
+        <v>Trong kho</v>
+      </c>
+      <c r="G24" t="str">
+        <v/>
+      </c>
+      <c r="H24" t="str">
+        <v>18/08/2026</v>
+      </c>
+      <c r="I24" t="str">
+        <v/>
+      </c>
+      <c r="J24" t="str">
+        <v/>
+      </c>
+      <c r="K24" t="str">
+        <v/>
+      </c>
+      <c r="L24" t="str">
+        <v/>
+      </c>
+      <c r="M24" t="str">
+        <v/>
+      </c>
+      <c r="N24" t="str">
+        <v/>
+      </c>
+      <c r="O24" t="str">
+        <v/>
+      </c>
+      <c r="P24" t="str">
+        <v/>
+      </c>
+      <c r="Q24" t="str">
+        <v/>
+      </c>
+      <c r="R24" t="str">
+        <v/>
+      </c>
+      <c r="S24" t="str">
+        <v/>
+      </c>
+      <c r="T24" t="str">
+        <v/>
+      </c>
+      <c r="U24" t="str">
+        <v/>
+      </c>
+      <c r="V24" t="str">
+        <v/>
+      </c>
+      <c r="W24" t="str">
+        <v/>
+      </c>
+      <c r="X24" t="str">
+        <v/>
+      </c>
+      <c r="Y24" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="25" xml:space="preserve">
+      <c r="A25" t="str">
+        <v>18/08/2026</v>
+      </c>
+      <c r="B25" t="str">
+        <v>OM4-P2-LS-0002-024</v>
+      </c>
+      <c r="C25" t="str" xml:space="preserve">
+        <v xml:space="preserve">Concrete eath pit (Dim: 310x310x170mm)_x000d_
+ + Copper earth bar 5 connection points Φ12, Dim: 50x5x300 c/w: SS304 bolds, nuts, spring &amp; flat washers M12x40.</v>
+      </c>
+      <c r="D25" t="str">
+        <v>OM4-P2-LS-0002</v>
+      </c>
+      <c r="E25" t="str">
+        <v>S1</v>
+      </c>
+      <c r="F25" t="str">
+        <v>Trong kho</v>
+      </c>
+      <c r="G25" t="str">
+        <v/>
+      </c>
+      <c r="H25" t="str">
+        <v>18/08/2026</v>
+      </c>
+      <c r="I25" t="str">
+        <v/>
+      </c>
+      <c r="J25" t="str">
+        <v/>
+      </c>
+      <c r="K25" t="str">
+        <v/>
+      </c>
+      <c r="L25" t="str">
+        <v/>
+      </c>
+      <c r="M25" t="str">
+        <v/>
+      </c>
+      <c r="N25" t="str">
+        <v/>
+      </c>
+      <c r="O25" t="str">
+        <v/>
+      </c>
+      <c r="P25" t="str">
+        <v/>
+      </c>
+      <c r="Q25" t="str">
+        <v/>
+      </c>
+      <c r="R25" t="str">
+        <v/>
+      </c>
+      <c r="S25" t="str">
+        <v/>
+      </c>
+      <c r="T25" t="str">
+        <v/>
+      </c>
+      <c r="U25" t="str">
+        <v/>
+      </c>
+      <c r="V25" t="str">
+        <v/>
+      </c>
+      <c r="W25" t="str">
+        <v/>
+      </c>
+      <c r="X25" t="str">
+        <v/>
+      </c>
+      <c r="Y25" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="26" xml:space="preserve">
+      <c r="A26" t="str">
+        <v>18/08/2026</v>
+      </c>
+      <c r="B26" t="str">
+        <v>OM4-P2-LS-0002-025</v>
+      </c>
+      <c r="C26" t="str" xml:space="preserve">
+        <v xml:space="preserve">Concrete eath pit (Dim: 310x310x170mm)_x000d_
+ + Copper earth bar 5 connection points Φ12, Dim: 50x5x300 c/w: SS304 bolds, nuts, spring &amp; flat washers M12x40.</v>
+      </c>
+      <c r="D26" t="str">
+        <v>OM4-P2-LS-0002</v>
+      </c>
+      <c r="E26" t="str">
+        <v>S1</v>
+      </c>
+      <c r="F26" t="str">
+        <v>Trong kho</v>
+      </c>
+      <c r="G26" t="str">
+        <v/>
+      </c>
+      <c r="H26" t="str">
+        <v>18/08/2026</v>
+      </c>
+      <c r="I26" t="str">
+        <v/>
+      </c>
+      <c r="J26" t="str">
+        <v/>
+      </c>
+      <c r="K26" t="str">
+        <v/>
+      </c>
+      <c r="L26" t="str">
+        <v/>
+      </c>
+      <c r="M26" t="str">
+        <v/>
+      </c>
+      <c r="N26" t="str">
+        <v/>
+      </c>
+      <c r="O26" t="str">
+        <v/>
+      </c>
+      <c r="P26" t="str">
+        <v/>
+      </c>
+      <c r="Q26" t="str">
+        <v/>
+      </c>
+      <c r="R26" t="str">
+        <v/>
+      </c>
+      <c r="S26" t="str">
+        <v/>
+      </c>
+      <c r="T26" t="str">
+        <v/>
+      </c>
+      <c r="U26" t="str">
+        <v/>
+      </c>
+      <c r="V26" t="str">
+        <v/>
+      </c>
+      <c r="W26" t="str">
+        <v/>
+      </c>
+      <c r="X26" t="str">
+        <v/>
+      </c>
+      <c r="Y26" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="27" xml:space="preserve">
+      <c r="A27" t="str">
+        <v>18/08/2026</v>
+      </c>
+      <c r="B27" t="str">
+        <v>OM4-P2-LS-0002-026</v>
+      </c>
+      <c r="C27" t="str" xml:space="preserve">
+        <v xml:space="preserve">Concrete eath pit (Dim: 310x310x170mm)_x000d_
+ + Copper earth bar 5 connection points Φ12, Dim: 50x5x300 c/w: SS304 bolds, nuts, spring &amp; flat washers M12x40.</v>
+      </c>
+      <c r="D27" t="str">
+        <v>OM4-P2-LS-0002</v>
+      </c>
+      <c r="E27" t="str">
+        <v>S1</v>
+      </c>
+      <c r="F27" t="str">
+        <v>Trong kho</v>
+      </c>
+      <c r="G27" t="str">
+        <v/>
+      </c>
+      <c r="H27" t="str">
+        <v>18/08/2026</v>
+      </c>
+      <c r="I27" t="str">
+        <v/>
+      </c>
+      <c r="J27" t="str">
+        <v/>
+      </c>
+      <c r="K27" t="str">
+        <v/>
+      </c>
+      <c r="L27" t="str">
+        <v/>
+      </c>
+      <c r="M27" t="str">
+        <v/>
+      </c>
+      <c r="N27" t="str">
+        <v/>
+      </c>
+      <c r="O27" t="str">
+        <v/>
+      </c>
+      <c r="P27" t="str">
+        <v/>
+      </c>
+      <c r="Q27" t="str">
+        <v/>
+      </c>
+      <c r="R27" t="str">
+        <v/>
+      </c>
+      <c r="S27" t="str">
+        <v/>
+      </c>
+      <c r="T27" t="str">
+        <v/>
+      </c>
+      <c r="U27" t="str">
+        <v/>
+      </c>
+      <c r="V27" t="str">
+        <v/>
+      </c>
+      <c r="W27" t="str">
+        <v/>
+      </c>
+      <c r="X27" t="str">
+        <v/>
+      </c>
+      <c r="Y27" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="28" xml:space="preserve">
+      <c r="A28" t="str">
+        <v>18/08/2026</v>
+      </c>
+      <c r="B28" t="str">
+        <v>OM4-P2-LS-0002-027</v>
+      </c>
+      <c r="C28" t="str" xml:space="preserve">
+        <v xml:space="preserve">Concrete eath pit (Dim: 310x310x170mm)_x000d_
+ + Copper earth bar 5 connection points Φ12, Dim: 50x5x300 c/w: SS304 bolds, nuts, spring &amp; flat washers M12x40.</v>
+      </c>
+      <c r="D28" t="str">
+        <v>OM4-P2-LS-0002</v>
+      </c>
+      <c r="E28" t="str">
+        <v>S1</v>
+      </c>
+      <c r="F28" t="str">
+        <v>Trong kho</v>
+      </c>
+      <c r="G28" t="str">
+        <v/>
+      </c>
+      <c r="H28" t="str">
+        <v>18/08/2026</v>
+      </c>
+      <c r="I28" t="str">
+        <v/>
+      </c>
+      <c r="J28" t="str">
+        <v/>
+      </c>
+      <c r="K28" t="str">
+        <v/>
+      </c>
+      <c r="L28" t="str">
+        <v/>
+      </c>
+      <c r="M28" t="str">
+        <v/>
+      </c>
+      <c r="N28" t="str">
+        <v/>
+      </c>
+      <c r="O28" t="str">
+        <v/>
+      </c>
+      <c r="P28" t="str">
+        <v/>
+      </c>
+      <c r="Q28" t="str">
+        <v/>
+      </c>
+      <c r="R28" t="str">
+        <v/>
+      </c>
+      <c r="S28" t="str">
+        <v/>
+      </c>
+      <c r="T28" t="str">
+        <v/>
+      </c>
+      <c r="U28" t="str">
+        <v/>
+      </c>
+      <c r="V28" t="str">
+        <v/>
+      </c>
+      <c r="W28" t="str">
+        <v/>
+      </c>
+      <c r="X28" t="str">
+        <v/>
+      </c>
+      <c r="Y28" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="29" xml:space="preserve">
+      <c r="A29" t="str">
+        <v>18/08/2026</v>
+      </c>
+      <c r="B29" t="str">
+        <v>OM4-P2-LS-0002-028</v>
+      </c>
+      <c r="C29" t="str" xml:space="preserve">
+        <v xml:space="preserve">Concrete eath pit (Dim: 310x310x170mm)_x000d_
+ + Copper earth bar 5 connection points Φ12, Dim: 50x5x300 c/w: SS304 bolds, nuts, spring &amp; flat washers M12x40.</v>
+      </c>
+      <c r="D29" t="str">
+        <v>OM4-P2-LS-0002</v>
+      </c>
+      <c r="E29" t="str">
+        <v>S1</v>
+      </c>
+      <c r="F29" t="str">
+        <v>Trong kho</v>
+      </c>
+      <c r="G29" t="str">
+        <v/>
+      </c>
+      <c r="H29" t="str">
+        <v>18/08/2026</v>
+      </c>
+      <c r="I29" t="str">
+        <v/>
+      </c>
+      <c r="J29" t="str">
+        <v/>
+      </c>
+      <c r="K29" t="str">
+        <v/>
+      </c>
+      <c r="L29" t="str">
+        <v/>
+      </c>
+      <c r="M29" t="str">
+        <v/>
+      </c>
+      <c r="N29" t="str">
+        <v/>
+      </c>
+      <c r="O29" t="str">
+        <v/>
+      </c>
+      <c r="P29" t="str">
+        <v/>
+      </c>
+      <c r="Q29" t="str">
+        <v/>
+      </c>
+      <c r="R29" t="str">
+        <v/>
+      </c>
+      <c r="S29" t="str">
+        <v/>
+      </c>
+      <c r="T29" t="str">
+        <v/>
+      </c>
+      <c r="U29" t="str">
+        <v/>
+      </c>
+      <c r="V29" t="str">
+        <v/>
+      </c>
+      <c r="W29" t="str">
+        <v/>
+      </c>
+      <c r="X29" t="str">
+        <v/>
+      </c>
+      <c r="Y29" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="30" xml:space="preserve">
+      <c r="A30" t="str">
+        <v>18/08/2026</v>
+      </c>
+      <c r="B30" t="str">
+        <v>OM4-P2-LS-0002-029</v>
+      </c>
+      <c r="C30" t="str" xml:space="preserve">
+        <v xml:space="preserve">Concrete eath pit (Dim: 310x310x170mm)_x000d_
+ + Copper earth bar 5 connection points Φ12, Dim: 50x5x300 c/w: SS304 bolds, nuts, spring &amp; flat washers M12x40.</v>
+      </c>
+      <c r="D30" t="str">
+        <v>OM4-P2-LS-0002</v>
+      </c>
+      <c r="E30" t="str">
+        <v>S1</v>
+      </c>
+      <c r="F30" t="str">
+        <v>Trong kho</v>
+      </c>
+      <c r="G30" t="str">
+        <v/>
+      </c>
+      <c r="H30" t="str">
+        <v>18/08/2026</v>
+      </c>
+      <c r="I30" t="str">
+        <v/>
+      </c>
+      <c r="J30" t="str">
+        <v/>
+      </c>
+      <c r="K30" t="str">
+        <v/>
+      </c>
+      <c r="L30" t="str">
+        <v/>
+      </c>
+      <c r="M30" t="str">
+        <v/>
+      </c>
+      <c r="N30" t="str">
+        <v/>
+      </c>
+      <c r="O30" t="str">
+        <v/>
+      </c>
+      <c r="P30" t="str">
+        <v/>
+      </c>
+      <c r="Q30" t="str">
+        <v/>
+      </c>
+      <c r="R30" t="str">
+        <v/>
+      </c>
+      <c r="S30" t="str">
+        <v/>
+      </c>
+      <c r="T30" t="str">
+        <v/>
+      </c>
+      <c r="U30" t="str">
+        <v/>
+      </c>
+      <c r="V30" t="str">
+        <v/>
+      </c>
+      <c r="W30" t="str">
+        <v/>
+      </c>
+      <c r="X30" t="str">
+        <v/>
+      </c>
+      <c r="Y30" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="31" xml:space="preserve">
+      <c r="A31" t="str">
+        <v>18/08/2026</v>
+      </c>
+      <c r="B31" t="str">
+        <v>OM4-P2-LS-0002-030</v>
+      </c>
+      <c r="C31" t="str" xml:space="preserve">
+        <v xml:space="preserve">Concrete eath pit (Dim: 310x310x170mm)_x000d_
+ + Copper earth bar 5 connection points Φ12, Dim: 50x5x300 c/w: SS304 bolds, nuts, spring &amp; flat washers M12x40.</v>
+      </c>
+      <c r="D31" t="str">
+        <v>OM4-P2-LS-0002</v>
+      </c>
+      <c r="E31" t="str">
+        <v>S1</v>
+      </c>
+      <c r="F31" t="str">
+        <v>Trong kho</v>
+      </c>
+      <c r="G31" t="str">
+        <v/>
+      </c>
+      <c r="H31" t="str">
+        <v>18/08/2026</v>
+      </c>
+      <c r="I31" t="str">
+        <v/>
+      </c>
+      <c r="J31" t="str">
+        <v/>
+      </c>
+      <c r="K31" t="str">
+        <v/>
+      </c>
+      <c r="L31" t="str">
+        <v/>
+      </c>
+      <c r="M31" t="str">
+        <v/>
+      </c>
+      <c r="N31" t="str">
+        <v/>
+      </c>
+      <c r="O31" t="str">
+        <v/>
+      </c>
+      <c r="P31" t="str">
+        <v/>
+      </c>
+      <c r="Q31" t="str">
+        <v/>
+      </c>
+      <c r="R31" t="str">
+        <v/>
+      </c>
+      <c r="S31" t="str">
+        <v/>
+      </c>
+      <c r="T31" t="str">
+        <v/>
+      </c>
+      <c r="U31" t="str">
+        <v/>
+      </c>
+      <c r="V31" t="str">
+        <v/>
+      </c>
+      <c r="W31" t="str">
+        <v/>
+      </c>
+      <c r="X31" t="str">
+        <v/>
+      </c>
+      <c r="Y31" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="32" xml:space="preserve">
+      <c r="A32" t="str">
+        <v>18/08/2026</v>
+      </c>
+      <c r="B32" t="str">
+        <v>OM4-P2-LS-0002-031</v>
+      </c>
+      <c r="C32" t="str" xml:space="preserve">
+        <v xml:space="preserve">Concrete eath pit (Dim: 310x310x170mm)_x000d_
+ + Copper earth bar 5 connection points Φ12, Dim: 50x5x300 c/w: SS304 bolds, nuts, spring &amp; flat washers M12x40.</v>
+      </c>
+      <c r="D32" t="str">
+        <v>OM4-P2-LS-0002</v>
+      </c>
+      <c r="E32" t="str">
+        <v>S1</v>
+      </c>
+      <c r="F32" t="str">
+        <v>Trong kho</v>
+      </c>
+      <c r="G32" t="str">
+        <v/>
+      </c>
+      <c r="H32" t="str">
+        <v>18/08/2026</v>
+      </c>
+      <c r="I32" t="str">
+        <v/>
+      </c>
+      <c r="J32" t="str">
+        <v/>
+      </c>
+      <c r="K32" t="str">
+        <v/>
+      </c>
+      <c r="L32" t="str">
+        <v/>
+      </c>
+      <c r="M32" t="str">
+        <v/>
+      </c>
+      <c r="N32" t="str">
+        <v/>
+      </c>
+      <c r="O32" t="str">
+        <v/>
+      </c>
+      <c r="P32" t="str">
+        <v/>
+      </c>
+      <c r="Q32" t="str">
+        <v/>
+      </c>
+      <c r="R32" t="str">
+        <v/>
+      </c>
+      <c r="S32" t="str">
+        <v/>
+      </c>
+      <c r="T32" t="str">
+        <v/>
+      </c>
+      <c r="U32" t="str">
+        <v/>
+      </c>
+      <c r="V32" t="str">
+        <v/>
+      </c>
+      <c r="W32" t="str">
+        <v/>
+      </c>
+      <c r="X32" t="str">
+        <v/>
+      </c>
+      <c r="Y32" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="33" xml:space="preserve">
+      <c r="A33" t="str">
+        <v>18/08/2026</v>
+      </c>
+      <c r="B33" t="str">
+        <v>OM4-P2-LS-0002-032</v>
+      </c>
+      <c r="C33" t="str" xml:space="preserve">
+        <v xml:space="preserve">Concrete eath pit (Dim: 310x310x170mm)_x000d_
+ + Copper earth bar 5 connection points Φ12, Dim: 50x5x300 c/w: SS304 bolds, nuts, spring &amp; flat washers M12x40.</v>
+      </c>
+      <c r="D33" t="str">
+        <v>OM4-P2-LS-0002</v>
+      </c>
+      <c r="E33" t="str">
+        <v>S1</v>
+      </c>
+      <c r="F33" t="str">
+        <v>Trong kho</v>
+      </c>
+      <c r="G33" t="str">
+        <v/>
+      </c>
+      <c r="H33" t="str">
+        <v>18/08/2026</v>
+      </c>
+      <c r="I33" t="str">
+        <v/>
+      </c>
+      <c r="J33" t="str">
+        <v/>
+      </c>
+      <c r="K33" t="str">
+        <v/>
+      </c>
+      <c r="L33" t="str">
+        <v/>
+      </c>
+      <c r="M33" t="str">
+        <v/>
+      </c>
+      <c r="N33" t="str">
+        <v/>
+      </c>
+      <c r="O33" t="str">
+        <v/>
+      </c>
+      <c r="P33" t="str">
+        <v/>
+      </c>
+      <c r="Q33" t="str">
+        <v/>
+      </c>
+      <c r="R33" t="str">
+        <v/>
+      </c>
+      <c r="S33" t="str">
+        <v/>
+      </c>
+      <c r="T33" t="str">
+        <v/>
+      </c>
+      <c r="U33" t="str">
+        <v/>
+      </c>
+      <c r="V33" t="str">
+        <v/>
+      </c>
+      <c r="W33" t="str">
+        <v/>
+      </c>
+      <c r="X33" t="str">
+        <v/>
+      </c>
+      <c r="Y33" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="34" xml:space="preserve">
+      <c r="A34" t="str">
+        <v>18/08/2026</v>
+      </c>
+      <c r="B34" t="str">
+        <v>OM4-P2-LS-0002-033</v>
+      </c>
+      <c r="C34" t="str" xml:space="preserve">
+        <v xml:space="preserve">Concrete eath pit (Dim: 310x310x170mm)_x000d_
+ + Copper earth bar 5 connection points Φ12, Dim: 50x5x300 c/w: SS304 bolds, nuts, spring &amp; flat washers M12x40.</v>
+      </c>
+      <c r="D34" t="str">
+        <v>OM4-P2-LS-0002</v>
+      </c>
+      <c r="E34" t="str">
+        <v>S1</v>
+      </c>
+      <c r="F34" t="str">
+        <v>Trong kho</v>
+      </c>
+      <c r="G34" t="str">
+        <v/>
+      </c>
+      <c r="H34" t="str">
+        <v>18/08/2026</v>
+      </c>
+      <c r="I34" t="str">
+        <v/>
+      </c>
+      <c r="J34" t="str">
+        <v/>
+      </c>
+      <c r="K34" t="str">
+        <v/>
+      </c>
+      <c r="L34" t="str">
+        <v/>
+      </c>
+      <c r="M34" t="str">
+        <v/>
+      </c>
+      <c r="N34" t="str">
+        <v/>
+      </c>
+      <c r="O34" t="str">
+        <v/>
+      </c>
+      <c r="P34" t="str">
+        <v/>
+      </c>
+      <c r="Q34" t="str">
+        <v/>
+      </c>
+      <c r="R34" t="str">
+        <v/>
+      </c>
+      <c r="S34" t="str">
+        <v/>
+      </c>
+      <c r="T34" t="str">
+        <v/>
+      </c>
+      <c r="U34" t="str">
+        <v/>
+      </c>
+      <c r="V34" t="str">
+        <v/>
+      </c>
+      <c r="W34" t="str">
+        <v/>
+      </c>
+      <c r="X34" t="str">
+        <v/>
+      </c>
+      <c r="Y34" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="35" xml:space="preserve">
+      <c r="A35" t="str">
+        <v>18/08/2026</v>
+      </c>
+      <c r="B35" t="str">
+        <v>OM4-P2-LS-0002-034</v>
+      </c>
+      <c r="C35" t="str" xml:space="preserve">
+        <v xml:space="preserve">Concrete eath pit (Dim: 310x310x170mm)_x000d_
+ + Copper earth bar 5 connection points Φ12, Dim: 50x5x300 c/w: SS304 bolds, nuts, spring &amp; flat washers M12x40.</v>
+      </c>
+      <c r="D35" t="str">
+        <v>OM4-P2-LS-0002</v>
+      </c>
+      <c r="E35" t="str">
+        <v>S1</v>
+      </c>
+      <c r="F35" t="str">
+        <v>Trong kho</v>
+      </c>
+      <c r="G35" t="str">
+        <v/>
+      </c>
+      <c r="H35" t="str">
+        <v>18/08/2026</v>
+      </c>
+      <c r="I35" t="str">
+        <v/>
+      </c>
+      <c r="J35" t="str">
+        <v/>
+      </c>
+      <c r="K35" t="str">
+        <v/>
+      </c>
+      <c r="L35" t="str">
+        <v/>
+      </c>
+      <c r="M35" t="str">
+        <v/>
+      </c>
+      <c r="N35" t="str">
+        <v/>
+      </c>
+      <c r="O35" t="str">
+        <v/>
+      </c>
+      <c r="P35" t="str">
+        <v/>
+      </c>
+      <c r="Q35" t="str">
+        <v/>
+      </c>
+      <c r="R35" t="str">
+        <v/>
+      </c>
+      <c r="S35" t="str">
+        <v/>
+      </c>
+      <c r="T35" t="str">
+        <v/>
+      </c>
+      <c r="U35" t="str">
+        <v/>
+      </c>
+      <c r="V35" t="str">
+        <v/>
+      </c>
+      <c r="W35" t="str">
+        <v/>
+      </c>
+      <c r="X35" t="str">
+        <v/>
+      </c>
+      <c r="Y35" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="36" xml:space="preserve">
+      <c r="A36" t="str">
+        <v>18/08/2026</v>
+      </c>
+      <c r="B36" t="str">
+        <v>OM4-P2-LS-0002-035</v>
+      </c>
+      <c r="C36" t="str" xml:space="preserve">
+        <v xml:space="preserve">Concrete eath pit (Dim: 310x310x170mm)_x000d_
+ + Copper earth bar 5 connection points Φ12, Dim: 50x5x300 c/w: SS304 bolds, nuts, spring &amp; flat washers M12x40.</v>
+      </c>
+      <c r="D36" t="str">
+        <v>OM4-P2-LS-0002</v>
+      </c>
+      <c r="E36" t="str">
+        <v>S1</v>
+      </c>
+      <c r="F36" t="str">
+        <v>Trong kho</v>
+      </c>
+      <c r="G36" t="str">
+        <v/>
+      </c>
+      <c r="H36" t="str">
+        <v>18/08/2026</v>
+      </c>
+      <c r="I36" t="str">
+        <v/>
+      </c>
+      <c r="J36" t="str">
+        <v/>
+      </c>
+      <c r="K36" t="str">
+        <v/>
+      </c>
+      <c r="L36" t="str">
+        <v/>
+      </c>
+      <c r="M36" t="str">
+        <v/>
+      </c>
+      <c r="N36" t="str">
+        <v/>
+      </c>
+      <c r="O36" t="str">
+        <v/>
+      </c>
+      <c r="P36" t="str">
+        <v/>
+      </c>
+      <c r="Q36" t="str">
+        <v/>
+      </c>
+      <c r="R36" t="str">
+        <v/>
+      </c>
+      <c r="S36" t="str">
+        <v/>
+      </c>
+      <c r="T36" t="str">
+        <v/>
+      </c>
+      <c r="U36" t="str">
+        <v/>
+      </c>
+      <c r="V36" t="str">
+        <v/>
+      </c>
+      <c r="W36" t="str">
+        <v/>
+      </c>
+      <c r="X36" t="str">
+        <v/>
+      </c>
+      <c r="Y36" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="37" xml:space="preserve">
+      <c r="A37" t="str">
+        <v>18/08/2026</v>
+      </c>
+      <c r="B37" t="str">
+        <v>OM4-P2-LS-0002-036</v>
+      </c>
+      <c r="C37" t="str" xml:space="preserve">
+        <v xml:space="preserve">Concrete eath pit (Dim: 310x310x170mm)_x000d_
+ + Copper earth bar 5 connection points Φ12, Dim: 50x5x300 c/w: SS304 bolds, nuts, spring &amp; flat washers M12x40.</v>
+      </c>
+      <c r="D37" t="str">
+        <v>OM4-P2-LS-0002</v>
+      </c>
+      <c r="E37" t="str">
+        <v>S1</v>
+      </c>
+      <c r="F37" t="str">
+        <v>Trong kho</v>
+      </c>
+      <c r="G37" t="str">
+        <v/>
+      </c>
+      <c r="H37" t="str">
+        <v>18/08/2026</v>
+      </c>
+      <c r="I37" t="str">
+        <v/>
+      </c>
+      <c r="J37" t="str">
+        <v/>
+      </c>
+      <c r="K37" t="str">
+        <v/>
+      </c>
+      <c r="L37" t="str">
+        <v/>
+      </c>
+      <c r="M37" t="str">
+        <v/>
+      </c>
+      <c r="N37" t="str">
+        <v/>
+      </c>
+      <c r="O37" t="str">
+        <v/>
+      </c>
+      <c r="P37" t="str">
+        <v/>
+      </c>
+      <c r="Q37" t="str">
+        <v/>
+      </c>
+      <c r="R37" t="str">
+        <v/>
+      </c>
+      <c r="S37" t="str">
+        <v/>
+      </c>
+      <c r="T37" t="str">
+        <v/>
+      </c>
+      <c r="U37" t="str">
+        <v/>
+      </c>
+      <c r="V37" t="str">
+        <v/>
+      </c>
+      <c r="W37" t="str">
+        <v/>
+      </c>
+      <c r="X37" t="str">
+        <v/>
+      </c>
+      <c r="Y37" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="38" xml:space="preserve">
+      <c r="A38" t="str">
+        <v>18/08/2026</v>
+      </c>
+      <c r="B38" t="str">
+        <v>OM4-P2-LS-0002-037</v>
+      </c>
+      <c r="C38" t="str" xml:space="preserve">
+        <v xml:space="preserve">Concrete eath pit (Dim: 310x310x170mm)_x000d_
+ + Copper earth bar 5 connection points Φ12, Dim: 50x5x300 c/w: SS304 bolds, nuts, spring &amp; flat washers M12x40.</v>
+      </c>
+      <c r="D38" t="str">
+        <v>OM4-P2-LS-0002</v>
+      </c>
+      <c r="E38" t="str">
+        <v>S1</v>
+      </c>
+      <c r="F38" t="str">
+        <v>Trong kho</v>
+      </c>
+      <c r="G38" t="str">
+        <v/>
+      </c>
+      <c r="H38" t="str">
+        <v>18/08/2026</v>
+      </c>
+      <c r="I38" t="str">
+        <v/>
+      </c>
+      <c r="J38" t="str">
+        <v/>
+      </c>
+      <c r="K38" t="str">
+        <v/>
+      </c>
+      <c r="L38" t="str">
+        <v/>
+      </c>
+      <c r="M38" t="str">
+        <v/>
+      </c>
+      <c r="N38" t="str">
+        <v/>
+      </c>
+      <c r="O38" t="str">
+        <v/>
+      </c>
+      <c r="P38" t="str">
+        <v/>
+      </c>
+      <c r="Q38" t="str">
+        <v/>
+      </c>
+      <c r="R38" t="str">
+        <v/>
+      </c>
+      <c r="S38" t="str">
+        <v/>
+      </c>
+      <c r="T38" t="str">
+        <v/>
+      </c>
+      <c r="U38" t="str">
+        <v/>
+      </c>
+      <c r="V38" t="str">
+        <v/>
+      </c>
+      <c r="W38" t="str">
+        <v/>
+      </c>
+      <c r="X38" t="str">
+        <v/>
+      </c>
+      <c r="Y38" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="39" xml:space="preserve">
+      <c r="A39" t="str">
+        <v>18/08/2026</v>
+      </c>
+      <c r="B39" t="str">
+        <v>OM4-P2-LS-0002-038</v>
+      </c>
+      <c r="C39" t="str" xml:space="preserve">
+        <v xml:space="preserve">Concrete eath pit (Dim: 310x310x170mm)_x000d_
+ + Copper earth bar 5 connection points Φ12, Dim: 50x5x300 c/w: SS304 bolds, nuts, spring &amp; flat washers M12x40.</v>
+      </c>
+      <c r="D39" t="str">
+        <v>OM4-P2-LS-0002</v>
+      </c>
+      <c r="E39" t="str">
+        <v>S1</v>
+      </c>
+      <c r="F39" t="str">
+        <v>Trong kho</v>
+      </c>
+      <c r="G39" t="str">
+        <v/>
+      </c>
+      <c r="H39" t="str">
+        <v>18/08/2026</v>
+      </c>
+      <c r="I39" t="str">
+        <v/>
+      </c>
+      <c r="J39" t="str">
+        <v/>
+      </c>
+      <c r="K39" t="str">
+        <v/>
+      </c>
+      <c r="L39" t="str">
+        <v/>
+      </c>
+      <c r="M39" t="str">
+        <v/>
+      </c>
+      <c r="N39" t="str">
+        <v/>
+      </c>
+      <c r="O39" t="str">
+        <v/>
+      </c>
+      <c r="P39" t="str">
+        <v/>
+      </c>
+      <c r="Q39" t="str">
+        <v/>
+      </c>
+      <c r="R39" t="str">
+        <v/>
+      </c>
+      <c r="S39" t="str">
+        <v/>
+      </c>
+      <c r="T39" t="str">
+        <v/>
+      </c>
+      <c r="U39" t="str">
+        <v/>
+      </c>
+      <c r="V39" t="str">
+        <v/>
+      </c>
+      <c r="W39" t="str">
+        <v/>
+      </c>
+      <c r="X39" t="str">
+        <v/>
+      </c>
+      <c r="Y39" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="40" xml:space="preserve">
+      <c r="A40" t="str">
+        <v>18/08/2026</v>
+      </c>
+      <c r="B40" t="str">
+        <v>OM4-P2-LS-0002-039</v>
+      </c>
+      <c r="C40" t="str" xml:space="preserve">
+        <v xml:space="preserve">Concrete eath pit (Dim: 310x310x170mm)_x000d_
+ + Copper earth bar 5 connection points Φ12, Dim: 50x5x300 c/w: SS304 bolds, nuts, spring &amp; flat washers M12x40.</v>
+      </c>
+      <c r="D40" t="str">
+        <v>OM4-P2-LS-0002</v>
+      </c>
+      <c r="E40" t="str">
+        <v>S1</v>
+      </c>
+      <c r="F40" t="str">
+        <v>Trong kho</v>
+      </c>
+      <c r="G40" t="str">
+        <v/>
+      </c>
+      <c r="H40" t="str">
+        <v>18/08/2026</v>
+      </c>
+      <c r="I40" t="str">
+        <v/>
+      </c>
+      <c r="J40" t="str">
+        <v/>
+      </c>
+      <c r="K40" t="str">
+        <v/>
+      </c>
+      <c r="L40" t="str">
+        <v/>
+      </c>
+      <c r="M40" t="str">
+        <v/>
+      </c>
+      <c r="N40" t="str">
+        <v/>
+      </c>
+      <c r="O40" t="str">
+        <v/>
+      </c>
+      <c r="P40" t="str">
+        <v/>
+      </c>
+      <c r="Q40" t="str">
+        <v/>
+      </c>
+      <c r="R40" t="str">
+        <v/>
+      </c>
+      <c r="S40" t="str">
+        <v/>
+      </c>
+      <c r="T40" t="str">
+        <v/>
+      </c>
+      <c r="U40" t="str">
+        <v/>
+      </c>
+      <c r="V40" t="str">
+        <v/>
+      </c>
+      <c r="W40" t="str">
+        <v/>
+      </c>
+      <c r="X40" t="str">
+        <v/>
+      </c>
+      <c r="Y40" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="41" xml:space="preserve">
+      <c r="A41" t="str">
+        <v>18/08/2026</v>
+      </c>
+      <c r="B41" t="str">
+        <v>OM4-P2-LS-0002-040</v>
+      </c>
+      <c r="C41" t="str" xml:space="preserve">
+        <v xml:space="preserve">Concrete eath pit (Dim: 310x310x170mm)_x000d_
+ + Copper earth bar 5 connection points Φ12, Dim: 50x5x300 c/w: SS304 bolds, nuts, spring &amp; flat washers M12x40.</v>
+      </c>
+      <c r="D41" t="str">
+        <v>OM4-P2-LS-0002</v>
+      </c>
+      <c r="E41" t="str">
+        <v>S1</v>
+      </c>
+      <c r="F41" t="str">
+        <v>Trong kho</v>
+      </c>
+      <c r="G41" t="str">
+        <v/>
+      </c>
+      <c r="H41" t="str">
+        <v>18/08/2026</v>
+      </c>
+      <c r="I41" t="str">
+        <v/>
+      </c>
+      <c r="J41" t="str">
+        <v/>
+      </c>
+      <c r="K41" t="str">
+        <v/>
+      </c>
+      <c r="L41" t="str">
+        <v/>
+      </c>
+      <c r="M41" t="str">
+        <v/>
+      </c>
+      <c r="N41" t="str">
+        <v/>
+      </c>
+      <c r="O41" t="str">
+        <v/>
+      </c>
+      <c r="P41" t="str">
+        <v/>
+      </c>
+      <c r="Q41" t="str">
+        <v/>
+      </c>
+      <c r="R41" t="str">
+        <v/>
+      </c>
+      <c r="S41" t="str">
+        <v/>
+      </c>
+      <c r="T41" t="str">
+        <v/>
+      </c>
+      <c r="U41" t="str">
+        <v/>
+      </c>
+      <c r="V41" t="str">
+        <v/>
+      </c>
+      <c r="W41" t="str">
+        <v/>
+      </c>
+      <c r="X41" t="str">
+        <v/>
+      </c>
+      <c r="Y41" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="42" xml:space="preserve">
+      <c r="A42" t="str">
+        <v>18/08/2026</v>
+      </c>
+      <c r="B42" t="str">
+        <v>OM4-P2-LS-0002-041</v>
+      </c>
+      <c r="C42" t="str" xml:space="preserve">
+        <v xml:space="preserve">Concrete eath pit (Dim: 310x310x170mm)_x000d_
+ + Copper earth bar 5 connection points Φ12, Dim: 50x5x300 c/w: SS304 bolds, nuts, spring &amp; flat washers M12x40.</v>
+      </c>
+      <c r="D42" t="str">
+        <v>OM4-P2-LS-0002</v>
+      </c>
+      <c r="E42" t="str">
+        <v>S1</v>
+      </c>
+      <c r="F42" t="str">
+        <v>Trong kho</v>
+      </c>
+      <c r="G42" t="str">
+        <v/>
+      </c>
+      <c r="H42" t="str">
+        <v>18/08/2026</v>
+      </c>
+      <c r="I42" t="str">
+        <v/>
+      </c>
+      <c r="J42" t="str">
+        <v/>
+      </c>
+      <c r="K42" t="str">
+        <v/>
+      </c>
+      <c r="L42" t="str">
+        <v/>
+      </c>
+      <c r="M42" t="str">
+        <v/>
+      </c>
+      <c r="N42" t="str">
+        <v/>
+      </c>
+      <c r="O42" t="str">
+        <v/>
+      </c>
+      <c r="P42" t="str">
+        <v/>
+      </c>
+      <c r="Q42" t="str">
+        <v/>
+      </c>
+      <c r="R42" t="str">
+        <v/>
+      </c>
+      <c r="S42" t="str">
+        <v/>
+      </c>
+      <c r="T42" t="str">
+        <v/>
+      </c>
+      <c r="U42" t="str">
+        <v/>
+      </c>
+      <c r="V42" t="str">
+        <v/>
+      </c>
+      <c r="W42" t="str">
+        <v/>
+      </c>
+      <c r="X42" t="str">
+        <v/>
+      </c>
+      <c r="Y42" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="43" xml:space="preserve">
+      <c r="A43" t="str">
+        <v>18/08/2026</v>
+      </c>
+      <c r="B43" t="str">
+        <v>OM4-P2-LS-0002-042</v>
+      </c>
+      <c r="C43" t="str" xml:space="preserve">
+        <v xml:space="preserve">Concrete eath pit (Dim: 310x310x170mm)_x000d_
+ + Copper earth bar 5 connection points Φ12, Dim: 50x5x300 c/w: SS304 bolds, nuts, spring &amp; flat washers M12x40.</v>
+      </c>
+      <c r="D43" t="str">
+        <v>OM4-P2-LS-0002</v>
+      </c>
+      <c r="E43" t="str">
+        <v>S1</v>
+      </c>
+      <c r="F43" t="str">
+        <v>Trong kho</v>
+      </c>
+      <c r="G43" t="str">
+        <v/>
+      </c>
+      <c r="H43" t="str">
+        <v>18/08/2026</v>
+      </c>
+      <c r="I43" t="str">
+        <v/>
+      </c>
+      <c r="J43" t="str">
+        <v/>
+      </c>
+      <c r="K43" t="str">
+        <v/>
+      </c>
+      <c r="L43" t="str">
+        <v/>
+      </c>
+      <c r="M43" t="str">
+        <v/>
+      </c>
+      <c r="N43" t="str">
+        <v/>
+      </c>
+      <c r="O43" t="str">
+        <v/>
+      </c>
+      <c r="P43" t="str">
+        <v/>
+      </c>
+      <c r="Q43" t="str">
+        <v/>
+      </c>
+      <c r="R43" t="str">
+        <v/>
+      </c>
+      <c r="S43" t="str">
+        <v/>
+      </c>
+      <c r="T43" t="str">
+        <v/>
+      </c>
+      <c r="U43" t="str">
+        <v/>
+      </c>
+      <c r="V43" t="str">
+        <v/>
+      </c>
+      <c r="W43" t="str">
+        <v/>
+      </c>
+      <c r="X43" t="str">
+        <v/>
+      </c>
+      <c r="Y43" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="44" xml:space="preserve">
+      <c r="A44" t="str">
+        <v>18/08/2026</v>
+      </c>
+      <c r="B44" t="str">
+        <v>OM4-P2-LS-0002-043</v>
+      </c>
+      <c r="C44" t="str" xml:space="preserve">
+        <v xml:space="preserve">Concrete eath pit (Dim: 310x310x170mm)_x000d_
+ + Copper earth bar 5 connection points Φ12, Dim: 50x5x300 c/w: SS304 bolds, nuts, spring &amp; flat washers M12x40.</v>
+      </c>
+      <c r="D44" t="str">
+        <v>OM4-P2-LS-0002</v>
+      </c>
+      <c r="E44" t="str">
+        <v>S1</v>
+      </c>
+      <c r="F44" t="str">
+        <v>Trong kho</v>
+      </c>
+      <c r="G44" t="str">
+        <v/>
+      </c>
+      <c r="H44" t="str">
+        <v>18/08/2026</v>
+      </c>
+      <c r="I44" t="str">
+        <v/>
+      </c>
+      <c r="J44" t="str">
+        <v/>
+      </c>
+      <c r="K44" t="str">
+        <v/>
+      </c>
+      <c r="L44" t="str">
+        <v/>
+      </c>
+      <c r="M44" t="str">
+        <v/>
+      </c>
+      <c r="N44" t="str">
+        <v/>
+      </c>
+      <c r="O44" t="str">
+        <v/>
+      </c>
+      <c r="P44" t="str">
+        <v/>
+      </c>
+      <c r="Q44" t="str">
+        <v/>
+      </c>
+      <c r="R44" t="str">
+        <v/>
+      </c>
+      <c r="S44" t="str">
+        <v/>
+      </c>
+      <c r="T44" t="str">
+        <v/>
+      </c>
+      <c r="U44" t="str">
+        <v/>
+      </c>
+      <c r="V44" t="str">
+        <v/>
+      </c>
+      <c r="W44" t="str">
+        <v/>
+      </c>
+      <c r="X44" t="str">
+        <v/>
+      </c>
+      <c r="Y44" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="45" xml:space="preserve">
+      <c r="A45" t="str">
+        <v>18/08/2026</v>
+      </c>
+      <c r="B45" t="str">
+        <v>OM4-P2-LS-0002-044</v>
+      </c>
+      <c r="C45" t="str" xml:space="preserve">
+        <v xml:space="preserve">Concrete eath pit (Dim: 310x310x170mm)_x000d_
+ + Copper earth bar 5 connection points Φ12, Dim: 50x5x300 c/w: SS304 bolds, nuts, spring &amp; flat washers M12x40.</v>
+      </c>
+      <c r="D45" t="str">
+        <v>OM4-P2-LS-0002</v>
+      </c>
+      <c r="E45" t="str">
+        <v>S1</v>
+      </c>
+      <c r="F45" t="str">
+        <v>Trong kho</v>
+      </c>
+      <c r="G45" t="str">
+        <v/>
+      </c>
+      <c r="H45" t="str">
+        <v>18/08/2026</v>
+      </c>
+      <c r="I45" t="str">
+        <v/>
+      </c>
+      <c r="J45" t="str">
+        <v/>
+      </c>
+      <c r="K45" t="str">
+        <v/>
+      </c>
+      <c r="L45" t="str">
+        <v/>
+      </c>
+      <c r="M45" t="str">
+        <v/>
+      </c>
+      <c r="N45" t="str">
+        <v/>
+      </c>
+      <c r="O45" t="str">
+        <v/>
+      </c>
+      <c r="P45" t="str">
+        <v/>
+      </c>
+      <c r="Q45" t="str">
+        <v/>
+      </c>
+      <c r="R45" t="str">
+        <v/>
+      </c>
+      <c r="S45" t="str">
+        <v/>
+      </c>
+      <c r="T45" t="str">
+        <v/>
+      </c>
+      <c r="U45" t="str">
+        <v/>
+      </c>
+      <c r="V45" t="str">
+        <v/>
+      </c>
+      <c r="W45" t="str">
+        <v/>
+      </c>
+      <c r="X45" t="str">
+        <v/>
+      </c>
+      <c r="Y45" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="46" xml:space="preserve">
+      <c r="A46" t="str">
+        <v>18/08/2026</v>
+      </c>
+      <c r="B46" t="str">
+        <v>OM4-P2-LS-0002-045</v>
+      </c>
+      <c r="C46" t="str" xml:space="preserve">
+        <v xml:space="preserve">Concrete eath pit (Dim: 310x310x170mm)_x000d_
+ + Copper earth bar 5 connection points Φ12, Dim: 50x5x300 c/w: SS304 bolds, nuts, spring &amp; flat washers M12x40.</v>
+      </c>
+      <c r="D46" t="str">
+        <v>OM4-P2-LS-0002</v>
+      </c>
+      <c r="E46" t="str">
+        <v>S1</v>
+      </c>
+      <c r="F46" t="str">
+        <v>Trong kho</v>
+      </c>
+      <c r="G46" t="str">
+        <v/>
+      </c>
+      <c r="H46" t="str">
+        <v>18/08/2026</v>
+      </c>
+      <c r="I46" t="str">
+        <v/>
+      </c>
+      <c r="J46" t="str">
+        <v/>
+      </c>
+      <c r="K46" t="str">
+        <v/>
+      </c>
+      <c r="L46" t="str">
+        <v/>
+      </c>
+      <c r="M46" t="str">
+        <v/>
+      </c>
+      <c r="N46" t="str">
+        <v/>
+      </c>
+      <c r="O46" t="str">
+        <v/>
+      </c>
+      <c r="P46" t="str">
+        <v/>
+      </c>
+      <c r="Q46" t="str">
+        <v/>
+      </c>
+      <c r="R46" t="str">
+        <v/>
+      </c>
+      <c r="S46" t="str">
+        <v/>
+      </c>
+      <c r="T46" t="str">
+        <v/>
+      </c>
+      <c r="U46" t="str">
+        <v/>
+      </c>
+      <c r="V46" t="str">
+        <v/>
+      </c>
+      <c r="W46" t="str">
+        <v/>
+      </c>
+      <c r="X46" t="str">
+        <v/>
+      </c>
+      <c r="Y46" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:Y46"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/du-lieu/chinh-sua-tay.xlsx
+++ b/du-lieu/chinh-sua-tay.xlsx
@@ -572,7 +572,7 @@
         <v/>
       </c>
       <c r="Z2" t="str">
-        <v>[{"name":"HRSG Embeded Material (Template)","qty":1,"unit":"PKG","remaining":0,"log":[{"time":"21:59:33 18/8/2026","change":-1,"after":0}]},{"name":"TEMPLATE(TP-1)_10T*374*374","qty":20,"unit":"EA","remaining":20,"log":[]},{"name":"TEMPLATE(TP-2)_10T*450*900","qty":40,"unit":"EA","remaining":40,"log":[]},{"name":"TEMPLATE(TP-3)_10T*270*320","qty":8,"unit":"EA","remaining":8,"log":[]},{"name":"TEMPLATE(STP-1)_15T*250*3801","qty":6,"unit":"EA","remaining":6,"log":[]},{"name":"TEMPLATE(STP-2)_10T*60*250","qty":6,"unit":"EA","remaining":6,"log":[]},{"name":"TEMPLATE(STP-3)_15T*250*3801","qty":6,"unit":"EA","remaining":6,"log":[]},{"name":"TEMPLATE(STP-4)_10T*60*250","qty":6,"unit":"EA","remaining":6,"log":[]}]</v>
+        <v>[{"name":"HRSG Embeded Material (Template)","qty":1,"unit":"PKG","remaining":1,"log":[{"time":"21:59:36 18/8/2026","change":1,"after":1},{"time":"21:59:33 18/8/2026","change":-1,"after":0}]},{"name":"TEMPLATE(TP-1)_10T*374*374","qty":20,"unit":"EA","remaining":20,"log":[]},{"name":"TEMPLATE(TP-2)_10T*450*900","qty":40,"unit":"EA","remaining":40,"log":[]},{"name":"TEMPLATE(TP-3)_10T*270*320","qty":8,"unit":"EA","remaining":8,"log":[]},{"name":"TEMPLATE(STP-1)_15T*250*3801","qty":6,"unit":"EA","remaining":6,"log":[]},{"name":"TEMPLATE(STP-2)_10T*60*250","qty":6,"unit":"EA","remaining":6,"log":[]},{"name":"TEMPLATE(STP-3)_15T*250*3801","qty":6,"unit":"EA","remaining":6,"log":[]},{"name":"TEMPLATE(STP-4)_10T*60*250","qty":6,"unit":"EA","remaining":6,"log":[]}]</v>
       </c>
     </row>
   </sheetData>

--- a/du-lieu/chinh-sua-tay.xlsx
+++ b/du-lieu/chinh-sua-tay.xlsx
@@ -572,7 +572,7 @@
         <v/>
       </c>
       <c r="Z2" t="str">
-        <v>[{"name":"HRSG Embeded Material (Template)","qty":1,"unit":"PKG","remaining":1,"log":[{"time":"21:59:36 18/8/2026","change":1,"after":1},{"time":"21:59:33 18/8/2026","change":-1,"after":0}]},{"name":"TEMPLATE(TP-1)_10T*374*374","qty":20,"unit":"EA","remaining":20,"log":[]},{"name":"TEMPLATE(TP-2)_10T*450*900","qty":40,"unit":"EA","remaining":40,"log":[]},{"name":"TEMPLATE(TP-3)_10T*270*320","qty":8,"unit":"EA","remaining":8,"log":[]},{"name":"TEMPLATE(STP-1)_15T*250*3801","qty":6,"unit":"EA","remaining":6,"log":[]},{"name":"TEMPLATE(STP-2)_10T*60*250","qty":6,"unit":"EA","remaining":6,"log":[]},{"name":"TEMPLATE(STP-3)_15T*250*3801","qty":6,"unit":"EA","remaining":6,"log":[]},{"name":"TEMPLATE(STP-4)_10T*60*250","qty":6,"unit":"EA","remaining":6,"log":[]}]</v>
+        <v>[{"name":"HRSG Embeded Material (Template)","qty":1,"unit":"PKG","remaining":1,"log":[{"time":"21:59:36 18/8/2026","change":1,"after":1},{"time":"21:59:33 18/8/2026","change":-1,"after":0}]},{"name":"TEMPLATE(TP-1)_10T*374*374","qty":20,"unit":"EA","remaining":19,"log":[{"time":"22:00:37 18/8/2026","change":-1,"after":19}]},{"name":"TEMPLATE(TP-2)_10T*450*900","qty":40,"unit":"EA","remaining":40,"log":[]},{"name":"TEMPLATE(TP-3)_10T*270*320","qty":8,"unit":"EA","remaining":8,"log":[]},{"name":"TEMPLATE(STP-1)_15T*250*3801","qty":6,"unit":"EA","remaining":6,"log":[]},{"name":"TEMPLATE(STP-2)_10T*60*250","qty":6,"unit":"EA","remaining":6,"log":[]},{"name":"TEMPLATE(STP-3)_15T*250*3801","qty":6,"unit":"EA","remaining":6,"log":[]},{"name":"TEMPLATE(STP-4)_10T*60*250","qty":6,"unit":"EA","remaining":6,"log":[]}]</v>
       </c>
     </row>
   </sheetData>

--- a/du-lieu/chinh-sua-tay.xlsx
+++ b/du-lieu/chinh-sua-tay.xlsx
@@ -572,7 +572,7 @@
         <v/>
       </c>
       <c r="Z2" t="str">
-        <v>[{"name":"HRSG Embeded Material (Template)","qty":1,"unit":"PKG","remaining":1,"log":[{"time":"21:59:36 18/8/2026","change":1,"after":1},{"time":"21:59:33 18/8/2026","change":-1,"after":0}]},{"name":"TEMPLATE(TP-1)_10T*374*374","qty":20,"unit":"EA","remaining":19,"log":[{"time":"22:00:37 18/8/2026","change":-1,"after":19}]},{"name":"TEMPLATE(TP-2)_10T*450*900","qty":40,"unit":"EA","remaining":40,"log":[]},{"name":"TEMPLATE(TP-3)_10T*270*320","qty":8,"unit":"EA","remaining":8,"log":[]},{"name":"TEMPLATE(STP-1)_15T*250*3801","qty":6,"unit":"EA","remaining":6,"log":[]},{"name":"TEMPLATE(STP-2)_10T*60*250","qty":6,"unit":"EA","remaining":6,"log":[]},{"name":"TEMPLATE(STP-3)_15T*250*3801","qty":6,"unit":"EA","remaining":6,"log":[]},{"name":"TEMPLATE(STP-4)_10T*60*250","qty":6,"unit":"EA","remaining":6,"log":[]}]</v>
+        <v>[{"name":"HRSG Embeded Material (Template)","qty":1,"unit":"PKG","remaining":1,"log":[{"time":"21:59:36 18/8/2026","change":1,"after":1},{"time":"21:59:33 18/8/2026","change":-1,"after":0}]},{"name":"TEMPLATE(TP-1)_10T*374*374","qty":20,"unit":"EA","remaining":18,"log":[{"time":"22:05:53 18/8/2026","change":-1,"after":18},{"time":"22:00:37 18/8/2026","change":-1,"after":19}]},{"name":"TEMPLATE(TP-2)_10T*450*900","qty":40,"unit":"EA","remaining":40,"log":[]},{"name":"TEMPLATE(TP-3)_10T*270*320","qty":8,"unit":"EA","remaining":8,"log":[]},{"name":"TEMPLATE(STP-1)_15T*250*3801","qty":6,"unit":"EA","remaining":6,"log":[]},{"name":"TEMPLATE(STP-2)_10T*60*250","qty":6,"unit":"EA","remaining":6,"log":[]},{"name":"TEMPLATE(STP-3)_15T*250*3801","qty":6,"unit":"EA","remaining":6,"log":[]},{"name":"TEMPLATE(STP-4)_10T*60*250","qty":6,"unit":"EA","remaining":6,"log":[]}]</v>
       </c>
     </row>
   </sheetData>

--- a/du-lieu/chinh-sua-tay.xlsx
+++ b/du-lieu/chinh-sua-tay.xlsx
@@ -413,7 +413,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z2"/>
+  <dimension ref="A1:Z3"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -572,12 +572,92 @@
         <v/>
       </c>
       <c r="Z2" t="str">
-        <v>[{"name":"HRSG Embeded Material (Template)","qty":1,"unit":"PKG","remaining":1,"log":[{"time":"21:59:36 18/8/2026","change":1,"after":1},{"time":"21:59:33 18/8/2026","change":-1,"after":0}]},{"name":"TEMPLATE(TP-1)_10T*374*374","qty":20,"unit":"EA","remaining":18,"log":[{"time":"22:05:53 18/8/2026","change":-1,"after":18},{"time":"22:00:37 18/8/2026","change":-1,"after":19}]},{"name":"TEMPLATE(TP-2)_10T*450*900","qty":40,"unit":"EA","remaining":40,"log":[]},{"name":"TEMPLATE(TP-3)_10T*270*320","qty":8,"unit":"EA","remaining":8,"log":[]},{"name":"TEMPLATE(STP-1)_15T*250*3801","qty":6,"unit":"EA","remaining":6,"log":[]},{"name":"TEMPLATE(STP-2)_10T*60*250","qty":6,"unit":"EA","remaining":6,"log":[]},{"name":"TEMPLATE(STP-3)_15T*250*3801","qty":6,"unit":"EA","remaining":6,"log":[]},{"name":"TEMPLATE(STP-4)_10T*60*250","qty":6,"unit":"EA","remaining":6,"log":[]}]</v>
+        <v>[{"name":"HRSG Embeded Material (Template)","qty":1,"unit":"PKG","remaining":1,"log":[{"time":"21:59:36 18/8/2026","change":1,"after":1},{"time":"21:59:33 18/8/2026","change":-1,"after":0}]},{"name":"TEMPLATE(TP-1)_10T*374*374","qty":20,"unit":"EA","remaining":19,"log":[{"time":"22:00:37 18/8/2026","change":-1,"after":19}]},{"name":"TEMPLATE(TP-2)_10T*450*900","qty":40,"unit":"EA","remaining":40,"log":[]},{"name":"TEMPLATE(TP-3)_10T*270*320","qty":8,"unit":"EA","remaining":8,"log":[]},{"name":"TEMPLATE(STP-1)_15T*250*3801","qty":6,"unit":"EA","remaining":6,"log":[]},{"name":"TEMPLATE(STP-2)_10T*60*250","qty":6,"unit":"EA","remaining":6,"log":[]},{"name":"TEMPLATE(STP-3)_15T*250*3801","qty":6,"unit":"EA","remaining":6,"log":[]},{"name":"TEMPLATE(STP-4)_10T*60*250","qty":6,"unit":"EA","remaining":6,"log":[]}]</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>18/08/2026</v>
+      </c>
+      <c r="B3" t="str">
+        <v>OM4-DE-IS-0002-002</v>
+      </c>
+      <c r="C3" t="str">
+        <v/>
+      </c>
+      <c r="D3" t="str">
+        <v/>
+      </c>
+      <c r="E3" t="str">
+        <v/>
+      </c>
+      <c r="F3" t="str">
+        <v>Trong kho</v>
+      </c>
+      <c r="G3" t="str">
+        <v/>
+      </c>
+      <c r="H3" t="str">
+        <v>18/08/2026</v>
+      </c>
+      <c r="I3" t="str">
+        <v/>
+      </c>
+      <c r="J3" t="str">
+        <v/>
+      </c>
+      <c r="K3" t="str">
+        <v/>
+      </c>
+      <c r="L3" t="str">
+        <v/>
+      </c>
+      <c r="M3" t="str">
+        <v/>
+      </c>
+      <c r="N3" t="str">
+        <v/>
+      </c>
+      <c r="O3" t="str">
+        <v/>
+      </c>
+      <c r="P3" t="str">
+        <v/>
+      </c>
+      <c r="Q3" t="str">
+        <v/>
+      </c>
+      <c r="R3" t="str">
+        <v/>
+      </c>
+      <c r="S3" t="str">
+        <v/>
+      </c>
+      <c r="T3" t="str">
+        <v/>
+      </c>
+      <c r="U3" t="str">
+        <v/>
+      </c>
+      <c r="V3" t="str">
+        <v/>
+      </c>
+      <c r="W3" t="str">
+        <v/>
+      </c>
+      <c r="X3" t="str">
+        <v/>
+      </c>
+      <c r="Y3" t="str">
+        <v/>
+      </c>
+      <c r="Z3" t="str">
+        <v>[{"name":"HRSG Embeded Material","qty":1,"unit":"PKG","remaining":0,"log":[{"time":"22:07:45 18/8/2026","change":-1,"after":0}]},{"name":"Anchor Bolt M56X1,515L","qty":40,"unit":"EA","remaining":40,"log":[]},{"name":"Nut M56","qty":160,"unit":"EA","remaining":160,"log":[]},{"name":"Anchor Bolt M42X1,110L","qty":16,"unit":"EA","remaining":16,"log":[]},{"name":"Nut M42","qty":64,"unit":"EA","remaining":64,"log":[]}]</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:Z2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:Z3"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/du-lieu/chinh-sua-tay.xlsx
+++ b/du-lieu/chinh-sua-tay.xlsx
@@ -413,7 +413,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z3"/>
+  <dimension ref="A1:Z2"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -572,92 +572,12 @@
         <v/>
       </c>
       <c r="Z2" t="str">
-        <v>[{"name":"HRSG Embeded Material (Template)","qty":1,"unit":"PKG","remaining":1,"log":[{"time":"21:59:36 18/8/2026","change":1,"after":1},{"time":"21:59:33 18/8/2026","change":-1,"after":0}]},{"name":"TEMPLATE(TP-1)_10T*374*374","qty":20,"unit":"EA","remaining":19,"log":[{"time":"22:00:37 18/8/2026","change":-1,"after":19}]},{"name":"TEMPLATE(TP-2)_10T*450*900","qty":40,"unit":"EA","remaining":40,"log":[]},{"name":"TEMPLATE(TP-3)_10T*270*320","qty":8,"unit":"EA","remaining":8,"log":[]},{"name":"TEMPLATE(STP-1)_15T*250*3801","qty":6,"unit":"EA","remaining":6,"log":[]},{"name":"TEMPLATE(STP-2)_10T*60*250","qty":6,"unit":"EA","remaining":6,"log":[]},{"name":"TEMPLATE(STP-3)_15T*250*3801","qty":6,"unit":"EA","remaining":6,"log":[]},{"name":"TEMPLATE(STP-4)_10T*60*250","qty":6,"unit":"EA","remaining":6,"log":[]}]</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>18/08/2026</v>
-      </c>
-      <c r="B3" t="str">
-        <v>OM4-DE-IS-0002-002</v>
-      </c>
-      <c r="C3" t="str">
-        <v/>
-      </c>
-      <c r="D3" t="str">
-        <v/>
-      </c>
-      <c r="E3" t="str">
-        <v/>
-      </c>
-      <c r="F3" t="str">
-        <v>Trong kho</v>
-      </c>
-      <c r="G3" t="str">
-        <v/>
-      </c>
-      <c r="H3" t="str">
-        <v>18/08/2026</v>
-      </c>
-      <c r="I3" t="str">
-        <v/>
-      </c>
-      <c r="J3" t="str">
-        <v/>
-      </c>
-      <c r="K3" t="str">
-        <v/>
-      </c>
-      <c r="L3" t="str">
-        <v/>
-      </c>
-      <c r="M3" t="str">
-        <v/>
-      </c>
-      <c r="N3" t="str">
-        <v/>
-      </c>
-      <c r="O3" t="str">
-        <v/>
-      </c>
-      <c r="P3" t="str">
-        <v/>
-      </c>
-      <c r="Q3" t="str">
-        <v/>
-      </c>
-      <c r="R3" t="str">
-        <v/>
-      </c>
-      <c r="S3" t="str">
-        <v/>
-      </c>
-      <c r="T3" t="str">
-        <v/>
-      </c>
-      <c r="U3" t="str">
-        <v/>
-      </c>
-      <c r="V3" t="str">
-        <v/>
-      </c>
-      <c r="W3" t="str">
-        <v/>
-      </c>
-      <c r="X3" t="str">
-        <v/>
-      </c>
-      <c r="Y3" t="str">
-        <v/>
-      </c>
-      <c r="Z3" t="str">
-        <v>[{"name":"HRSG Embeded Material","qty":1,"unit":"PKG","remaining":0,"log":[{"time":"22:07:45 18/8/2026","change":-1,"after":0}]},{"name":"Anchor Bolt M56X1,515L","qty":40,"unit":"EA","remaining":40,"log":[]},{"name":"Nut M56","qty":160,"unit":"EA","remaining":160,"log":[]},{"name":"Anchor Bolt M42X1,110L","qty":16,"unit":"EA","remaining":16,"log":[]},{"name":"Nut M42","qty":64,"unit":"EA","remaining":64,"log":[]}]</v>
+        <v>[{"name":"HRSG Embeded Material (Template)","qty":1,"unit":"PKG","remaining":1,"log":[{"time":"21:59:36 18/8/2026","change":1,"after":1},{"time":"21:59:33 18/8/2026","change":-1,"after":0}]},{"name":"TEMPLATE(TP-1)_10T*374*374","qty":20,"unit":"EA","remaining":20,"log":[{"time":"22:09:54 18/8/2026","change":1,"after":20},{"time":"22:00:37 18/8/2026","change":-1,"after":19}]},{"name":"TEMPLATE(TP-2)_10T*450*900","qty":40,"unit":"EA","remaining":40,"log":[]},{"name":"TEMPLATE(TP-3)_10T*270*320","qty":8,"unit":"EA","remaining":8,"log":[]},{"name":"TEMPLATE(STP-1)_15T*250*3801","qty":6,"unit":"EA","remaining":6,"log":[]},{"name":"TEMPLATE(STP-2)_10T*60*250","qty":6,"unit":"EA","remaining":6,"log":[]},{"name":"TEMPLATE(STP-3)_15T*250*3801","qty":6,"unit":"EA","remaining":6,"log":[]},{"name":"TEMPLATE(STP-4)_10T*60*250","qty":6,"unit":"EA","remaining":6,"log":[]}]</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:Z3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:Z2"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/du-lieu/chinh-sua-tay.xlsx
+++ b/du-lieu/chinh-sua-tay.xlsx
@@ -413,7 +413,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z2"/>
+  <dimension ref="A1:Z3"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -575,9 +575,89 @@
         <v>[{"name":"HRSG Embeded Material (Template)","qty":1,"unit":"PKG","remaining":1,"log":[{"time":"21:59:36 18/8/2026","change":1,"after":1},{"time":"21:59:33 18/8/2026","change":-1,"after":0}]},{"name":"TEMPLATE(TP-1)_10T*374*374","qty":20,"unit":"EA","remaining":20,"log":[{"time":"22:09:54 18/8/2026","change":1,"after":20},{"time":"22:00:37 18/8/2026","change":-1,"after":19}]},{"name":"TEMPLATE(TP-2)_10T*450*900","qty":40,"unit":"EA","remaining":40,"log":[]},{"name":"TEMPLATE(TP-3)_10T*270*320","qty":8,"unit":"EA","remaining":8,"log":[]},{"name":"TEMPLATE(STP-1)_15T*250*3801","qty":6,"unit":"EA","remaining":6,"log":[]},{"name":"TEMPLATE(STP-2)_10T*60*250","qty":6,"unit":"EA","remaining":6,"log":[]},{"name":"TEMPLATE(STP-3)_15T*250*3801","qty":6,"unit":"EA","remaining":6,"log":[]},{"name":"TEMPLATE(STP-4)_10T*60*250","qty":6,"unit":"EA","remaining":6,"log":[]}]</v>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>18/08/2026</v>
+      </c>
+      <c r="B3" t="str">
+        <v>OM4-DE-IS-0001-002</v>
+      </c>
+      <c r="C3" t="str">
+        <v/>
+      </c>
+      <c r="D3" t="str">
+        <v/>
+      </c>
+      <c r="E3" t="str">
+        <v/>
+      </c>
+      <c r="F3" t="str">
+        <v>Trong kho</v>
+      </c>
+      <c r="G3" t="str">
+        <v/>
+      </c>
+      <c r="H3" t="str">
+        <v>18/08/2026</v>
+      </c>
+      <c r="I3" t="str">
+        <v/>
+      </c>
+      <c r="J3" t="str">
+        <v/>
+      </c>
+      <c r="K3" t="str">
+        <v/>
+      </c>
+      <c r="L3" t="str">
+        <v/>
+      </c>
+      <c r="M3" t="str">
+        <v/>
+      </c>
+      <c r="N3" t="str">
+        <v/>
+      </c>
+      <c r="O3" t="str">
+        <v/>
+      </c>
+      <c r="P3" t="str">
+        <v/>
+      </c>
+      <c r="Q3" t="str">
+        <v/>
+      </c>
+      <c r="R3" t="str">
+        <v/>
+      </c>
+      <c r="S3" t="str">
+        <v/>
+      </c>
+      <c r="T3" t="str">
+        <v/>
+      </c>
+      <c r="U3" t="str">
+        <v/>
+      </c>
+      <c r="V3" t="str">
+        <v/>
+      </c>
+      <c r="W3" t="str">
+        <v/>
+      </c>
+      <c r="X3" t="str">
+        <v/>
+      </c>
+      <c r="Y3" t="str">
+        <v/>
+      </c>
+      <c r="Z3" t="str">
+        <v>[{"name":"HRSG Embeded Material (Anchor Bolt/Nut/Washer)","qty":1,"unit":"PKG","remaining":0,"log":[{"time":"22:18:37 18/8/2026","change":-1,"after":0}]},{"name":"Anchor Bolt","qty":40,"unit":"EA","remaining":40,"log":[]},{"name":"Nut M56","qty":160,"unit":"EA","remaining":160,"log":[]},{"name":"Anchor Bolt","qty":16,"unit":"EA","remaining":16,"log":[]},{"name":"Nut M42","qty":64,"unit":"EA","remaining":64,"log":[]}]</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:Z2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:Z3"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/du-lieu/chinh-sua-tay.xlsx
+++ b/du-lieu/chinh-sua-tay.xlsx
@@ -652,7 +652,7 @@
         <v/>
       </c>
       <c r="Z3" t="str">
-        <v>[{"name":"HRSG Embeded Material (Anchor Bolt/Nut/Washer)","qty":1,"unit":"PKG","remaining":0,"log":[{"time":"22:18:37 18/8/2026","change":-1,"after":0}]},{"name":"Anchor Bolt","qty":40,"unit":"EA","remaining":40,"log":[]},{"name":"Nut M56","qty":160,"unit":"EA","remaining":160,"log":[]},{"name":"Anchor Bolt","qty":16,"unit":"EA","remaining":16,"log":[]},{"name":"Nut M42","qty":64,"unit":"EA","remaining":64,"log":[]}]</v>
+        <v>[{"name":"HRSG Embeded Material (Anchor Bolt/Nut/Washer)","qty":1,"unit":"PKG","remaining":1,"log":[{"time":"22:18:42 18/8/2026","change":1,"after":1},{"time":"22:18:37 18/8/2026","change":-1,"after":0}]},{"name":"Anchor Bolt","qty":40,"unit":"EA","remaining":40,"log":[]},{"name":"Nut M56","qty":160,"unit":"EA","remaining":160,"log":[]},{"name":"Anchor Bolt","qty":16,"unit":"EA","remaining":16,"log":[]},{"name":"Nut M42","qty":64,"unit":"EA","remaining":64,"log":[]}]</v>
       </c>
     </row>
   </sheetData>

--- a/du-lieu/chinh-sua-tay.xlsx
+++ b/du-lieu/chinh-sua-tay.xlsx
@@ -652,7 +652,7 @@
         <v/>
       </c>
       <c r="Z3" t="str">
-        <v>[{"name":"HRSG Embeded Material (Anchor Bolt/Nut/Washer)","qty":1,"unit":"PKG","remaining":1,"log":[{"time":"22:18:42 18/8/2026","change":1,"after":1},{"time":"22:18:37 18/8/2026","change":-1,"after":0}]},{"name":"Anchor Bolt","qty":40,"unit":"EA","remaining":40,"log":[]},{"name":"Nut M56","qty":160,"unit":"EA","remaining":160,"log":[]},{"name":"Anchor Bolt","qty":16,"unit":"EA","remaining":16,"log":[]},{"name":"Nut M42","qty":64,"unit":"EA","remaining":64,"log":[]}]</v>
+        <v>[{"name":"HRSG Embeded Material (Anchor Bolt/Nut/Washer)","qty":1,"unit":"PKG","remaining":1,"log":[{"time":"22:18:42 18/8/2026","change":1,"after":1},{"time":"22:18:37 18/8/2026","change":-1,"after":0}]},{"name":"Anchor Bolt","qty":40,"unit":"EA","remaining":39,"log":[{"time":"22:18:44 18/8/2026","change":-1,"after":39}]},{"name":"Nut M56","qty":160,"unit":"EA","remaining":160,"log":[]},{"name":"Anchor Bolt","qty":16,"unit":"EA","remaining":16,"log":[]},{"name":"Nut M42","qty":64,"unit":"EA","remaining":64,"log":[]}]</v>
       </c>
     </row>
   </sheetData>

--- a/du-lieu/chinh-sua-tay.xlsx
+++ b/du-lieu/chinh-sua-tay.xlsx
@@ -652,7 +652,7 @@
         <v/>
       </c>
       <c r="Z3" t="str">
-        <v>[{"name":"HRSG Embeded Material (Anchor Bolt/Nut/Washer)","qty":1,"unit":"PKG","remaining":1,"log":[{"time":"22:18:42 18/8/2026","change":1,"after":1},{"time":"22:18:37 18/8/2026","change":-1,"after":0}]},{"name":"Anchor Bolt","qty":40,"unit":"EA","remaining":39,"log":[{"time":"22:18:44 18/8/2026","change":-1,"after":39}]},{"name":"Nut M56","qty":160,"unit":"EA","remaining":160,"log":[]},{"name":"Anchor Bolt","qty":16,"unit":"EA","remaining":16,"log":[]},{"name":"Nut M42","qty":64,"unit":"EA","remaining":64,"log":[]}]</v>
+        <v>[{"name":"HRSG Embeded Material (Anchor Bolt/Nut/Washer)","qty":1,"unit":"PKG","remaining":1,"log":[{"time":"22:18:42 18/8/2026","change":1,"after":1},{"time":"22:18:37 18/8/2026","change":-1,"after":0}]},{"name":"Anchor Bolt","qty":40,"unit":"EA","remaining":40,"log":[{"time":"22:18:56 18/8/2026","change":1,"after":40},{"time":"22:18:44 18/8/2026","change":-1,"after":39}]},{"name":"Nut M56","qty":160,"unit":"EA","remaining":160,"log":[]},{"name":"Anchor Bolt","qty":16,"unit":"EA","remaining":16,"log":[]},{"name":"Nut M42","qty":64,"unit":"EA","remaining":64,"log":[]}]</v>
       </c>
     </row>
   </sheetData>

--- a/du-lieu/chinh-sua-tay.xlsx
+++ b/du-lieu/chinh-sua-tay.xlsx
@@ -580,7 +580,7 @@
         <v>18/08/2026</v>
       </c>
       <c r="B3" t="str">
-        <v>OM4-DE-IS-0001-002</v>
+        <v>OM4-DE-IS-0001-007</v>
       </c>
       <c r="C3" t="str">
         <v/>
@@ -652,7 +652,7 @@
         <v/>
       </c>
       <c r="Z3" t="str">
-        <v>[{"name":"HRSG Embeded Material (Anchor Bolt/Nut/Washer)","qty":1,"unit":"PKG","remaining":1,"log":[{"time":"22:18:42 18/8/2026","change":1,"after":1},{"time":"22:18:37 18/8/2026","change":-1,"after":0}]},{"name":"Anchor Bolt","qty":40,"unit":"EA","remaining":40,"log":[{"time":"22:18:56 18/8/2026","change":1,"after":40},{"time":"22:18:44 18/8/2026","change":-1,"after":39}]},{"name":"Nut M56","qty":160,"unit":"EA","remaining":160,"log":[]},{"name":"Anchor Bolt","qty":16,"unit":"EA","remaining":16,"log":[]},{"name":"Nut M42","qty":64,"unit":"EA","remaining":64,"log":[]}]</v>
+        <v>[{"name":"HRSG Embeded Material (Anchor Bolt/Nut/Washer)","qty":1,"unit":"PKG","remaining":1,"log":[]},{"name":"Square Washer 130X160X20T","qty":40,"unit":"EA","remaining":40,"log":[]},{"name":"Square Washer 130X130X20T","qty":160,"unit":"EA","remaining":160,"log":[]},{"name":"Square Washer 100X100X15T","qty":16,"unit":"EA","remaining":16,"log":[]},{"name":"Square Washer 120X120X16T","qty":72,"unit":"EA","remaining":72,"log":[]},{"name":"Anchor Plate 130X130X20T","qty":40,"unit":"EA","remaining":40,"log":[]},{"name":"Anchor Plate 130X130X20T","qty":160,"unit":"EA","remaining":160,"log":[]},{"name":"Anchor Plate 100X100X12T","qty":16,"unit":"EA","remaining":16,"log":[]},{"name":"Anchor Plate 120X120X16T","qty":72,"unit":"EA","remaining":72,"log":[]},{"name":"Bot. Plate 100X100X10T","qty":40,"unit":"EA","remaining":40,"log":[]},{"name":"Bot. Plate 100X100X10T","qty":160,"unit":"EA","remaining":160,"log":[]},{"name":"Bot. Plate 100X100X10T","qty":16,"unit":"EA","remaining":15,"log":[{"time":"22:19:49 18/8/2026","change":-1,"after":15}]}]</v>
       </c>
     </row>
   </sheetData>

--- a/du-lieu/chinh-sua-tay.xlsx
+++ b/du-lieu/chinh-sua-tay.xlsx
@@ -652,7 +652,7 @@
         <v/>
       </c>
       <c r="Z3" t="str">
-        <v>[{"name":"HRSG Embeded Material (Anchor Bolt/Nut/Washer)","qty":1,"unit":"PKG","remaining":1,"log":[]},{"name":"Square Washer 130X160X20T","qty":40,"unit":"EA","remaining":40,"log":[]},{"name":"Square Washer 130X130X20T","qty":160,"unit":"EA","remaining":160,"log":[]},{"name":"Square Washer 100X100X15T","qty":16,"unit":"EA","remaining":16,"log":[]},{"name":"Square Washer 120X120X16T","qty":72,"unit":"EA","remaining":72,"log":[]},{"name":"Anchor Plate 130X130X20T","qty":40,"unit":"EA","remaining":40,"log":[]},{"name":"Anchor Plate 130X130X20T","qty":160,"unit":"EA","remaining":160,"log":[]},{"name":"Anchor Plate 100X100X12T","qty":16,"unit":"EA","remaining":16,"log":[]},{"name":"Anchor Plate 120X120X16T","qty":72,"unit":"EA","remaining":72,"log":[]},{"name":"Bot. Plate 100X100X10T","qty":40,"unit":"EA","remaining":40,"log":[]},{"name":"Bot. Plate 100X100X10T","qty":160,"unit":"EA","remaining":160,"log":[]},{"name":"Bot. Plate 100X100X10T","qty":16,"unit":"EA","remaining":15,"log":[{"time":"22:19:49 18/8/2026","change":-1,"after":15}]}]</v>
+        <v>[{"name":"HRSG Embeded Material (Anchor Bolt/Nut/Washer)","qty":1,"unit":"PKG","remaining":1,"log":[]},{"name":"Square Washer 130X160X20T","qty":40,"unit":"EA","remaining":40,"log":[]},{"name":"Square Washer 130X130X20T","qty":160,"unit":"EA","remaining":160,"log":[]},{"name":"Square Washer 100X100X15T","qty":16,"unit":"EA","remaining":16,"log":[]},{"name":"Square Washer 120X120X16T","qty":72,"unit":"EA","remaining":72,"log":[]},{"name":"Anchor Plate 130X130X20T","qty":40,"unit":"EA","remaining":40,"log":[]},{"name":"Anchor Plate 130X130X20T","qty":160,"unit":"EA","remaining":160,"log":[]},{"name":"Anchor Plate 100X100X12T","qty":16,"unit":"EA","remaining":16,"log":[]},{"name":"Anchor Plate 120X120X16T","qty":72,"unit":"EA","remaining":72,"log":[]},{"name":"Bot. Plate 100X100X10T","qty":40,"unit":"EA","remaining":40,"log":[]},{"name":"Bot. Plate 100X100X10T","qty":160,"unit":"EA","remaining":160,"log":[]},{"name":"Bot. Plate 100X100X10T","qty":16,"unit":"EA","remaining":16,"log":[{"time":"22:19:52 18/8/2026","change":1,"after":16},{"time":"22:19:49 18/8/2026","change":-1,"after":15}]}]</v>
       </c>
     </row>
   </sheetData>

--- a/du-lieu/chinh-sua-tay.xlsx
+++ b/du-lieu/chinh-sua-tay.xlsx
@@ -413,7 +413,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z3"/>
+  <dimension ref="A1:Z4"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -655,9 +655,89 @@
         <v>[{"name":"HRSG Embeded Material (Anchor Bolt/Nut/Washer)","qty":1,"unit":"PKG","remaining":1,"log":[]},{"name":"Square Washer 130X160X20T","qty":40,"unit":"EA","remaining":40,"log":[]},{"name":"Square Washer 130X130X20T","qty":160,"unit":"EA","remaining":160,"log":[]},{"name":"Square Washer 100X100X15T","qty":16,"unit":"EA","remaining":16,"log":[]},{"name":"Square Washer 120X120X16T","qty":72,"unit":"EA","remaining":72,"log":[]},{"name":"Anchor Plate 130X130X20T","qty":40,"unit":"EA","remaining":40,"log":[]},{"name":"Anchor Plate 130X130X20T","qty":160,"unit":"EA","remaining":160,"log":[]},{"name":"Anchor Plate 100X100X12T","qty":16,"unit":"EA","remaining":16,"log":[]},{"name":"Anchor Plate 120X120X16T","qty":72,"unit":"EA","remaining":72,"log":[]},{"name":"Bot. Plate 100X100X10T","qty":40,"unit":"EA","remaining":40,"log":[]},{"name":"Bot. Plate 100X100X10T","qty":160,"unit":"EA","remaining":160,"log":[]},{"name":"Bot. Plate 100X100X10T","qty":16,"unit":"EA","remaining":16,"log":[{"time":"22:19:52 18/8/2026","change":1,"after":16},{"time":"22:19:49 18/8/2026","change":-1,"after":15}]}]</v>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>18/08/2026</v>
+      </c>
+      <c r="B4" t="str">
+        <v>OM4-DE-IS-0009-010</v>
+      </c>
+      <c r="C4" t="str">
+        <v/>
+      </c>
+      <c r="D4" t="str">
+        <v/>
+      </c>
+      <c r="E4" t="str">
+        <v/>
+      </c>
+      <c r="F4" t="str">
+        <v>Trong kho</v>
+      </c>
+      <c r="G4" t="str">
+        <v/>
+      </c>
+      <c r="H4" t="str">
+        <v>18/08/2026</v>
+      </c>
+      <c r="I4" t="str">
+        <v/>
+      </c>
+      <c r="J4" t="str">
+        <v/>
+      </c>
+      <c r="K4" t="str">
+        <v/>
+      </c>
+      <c r="L4" t="str">
+        <v/>
+      </c>
+      <c r="M4" t="str">
+        <v/>
+      </c>
+      <c r="N4" t="str">
+        <v/>
+      </c>
+      <c r="O4" t="str">
+        <v/>
+      </c>
+      <c r="P4" t="str">
+        <v/>
+      </c>
+      <c r="Q4" t="str">
+        <v/>
+      </c>
+      <c r="R4" t="str">
+        <v/>
+      </c>
+      <c r="S4" t="str">
+        <v/>
+      </c>
+      <c r="T4" t="str">
+        <v/>
+      </c>
+      <c r="U4" t="str">
+        <v/>
+      </c>
+      <c r="V4" t="str">
+        <v/>
+      </c>
+      <c r="W4" t="str">
+        <v/>
+      </c>
+      <c r="X4" t="str">
+        <v/>
+      </c>
+      <c r="Y4" t="str">
+        <v/>
+      </c>
+      <c r="Z4" t="str">
+        <v>[{"name":"Condulet (\"LT\" Type) 28mm (1\")","qty":30,"unit":"EA","remaining":29,"log":[{"time":"22:30:41 18/8/2026","change":-1,"after":29}]},{"name":"Condulet (\"LT\" Type) 36mm (1-1/4\")","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"Condulet (\"LT\" Type) 42mm (1-1/2\")","qty":10,"unit":"EA","remaining":10,"log":[]},{"name":"Condulet (\"LT\" Type) 54mm (2\")","qty":15,"unit":"EA","remaining":15,"log":[]},{"name":"Condulet (\"LT\" Type) 82mm (3\")","qty":15,"unit":"EA","remaining":15,"log":[]},{"name":"Condulet (\"LT\" Type) 104mm (4\")","qty":10,"unit":"EA","remaining":10,"log":[]},{"name":"Flexible Conduit Connector (Male Type) 28mm (1\")","qty":420,"unit":"EA","remaining":420,"log":[]},{"name":"Flexible Conduit Connector (Male Type) 36mm (1-1/4\")","qty":150,"unit":"EA","remaining":150,"log":[]},{"name":"Flexible Conduit Connector (Male Type) 42mm (1-1/2\")","qty":50,"unit":"EA","remaining":50,"log":[]},{"name":"Flexible Conduit Connector (Male Type) 54mm (2\")","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"Flexible Conduit Connector (Male Type) 82mm (3\")","qty":80,"unit":"EA","remaining":80,"log":[]},{"name":"Flexible Conduit Connector (Male Type) 104mm (4\")","qty":50,"unit":"EA","remaining":50,"log":[]},{"name":"Flexible Conduit Connector (Female Type) 28mm (1\")","qty":420,"unit":"EA","remaining":420,"log":[]},{"name":"Flexible Conduit Connector (Female Type) 36mm (1-1/4\")","qty":150,"unit":"EA","remaining":150,"log":[]},{"name":"Flexible Conduit Connector (Female Type) 42mm (1-1/2\")","qty":50,"unit":"EA","remaining":50,"log":[]},{"name":"Flexible Conduit Connector (Female Type) 54mm (2\")","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"Flexible Conduit Connector (Female Type) 82mm (3\")","qty":80,"unit":"EA","remaining":80,"log":[]},{"name":"Flexible Conduit Connector (Female Type) 104mm (4\")","qty":50,"unit":"EA","remaining":50,"log":[]},{"name":"Union Coupling (Male Type) 28mm (1\")","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"Union Coupling (Male Type) 36mm (1-1/4\")","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"Union Coupling (Male Type) 42mm (1-1/2\")","qty":10,"unit":"EA","remaining":10,"log":[]},{"name":"Union Coupling (Male Type) 54mm (2\")","qty":10,"unit":"EA","remaining":10,"log":[]},{"name":"Union Coupling (Male Type) 82mm (3\")","qty":10,"unit":"EA","remaining":10,"log":[]},{"name":"Nipple(EXPLOSION TYPE, NPT to PF) 28mm (1\")","qty":10,"unit":"EA","remaining":10,"log":[]},{"name":"Nipple(EXPLOSION TYPE, NPT to PF) 36mm (1-1/4\")","qty":5,"unit":"EA","remaining":5,"log":[]},{"name":"Nipple(EXPLOSION TYPE, NPT to PF) 42mm (1-1/2\")","qty":5,"unit":"EA","remaining":5,"log":[]},{"name":"Nipple(EXPLOSION TYPE, NPT to PF) 54mm (2\")","qty":5,"unit":"EA","remaining":5,"log":[]},{"name":"SEALING COMPOUND Plaster FOR SEALING FITTING 1KG/CAN","qty":50,"unit":"EA","remaining":50,"log":[]},{"name":"REDUCER(ADAPTER TYPE) 36mm Male - 28mm Female","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"REDUCER(ADAPTER TYPE) 36mm Male - 28mm Female","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"REDUCER(ADAPTER TYPE) 42mm Male - 28mm Female","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"REDUCER(ADAPTER TYPE) 54mm Male - 28mm Female","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"REDUCER(ADAPTER TYPE) 54mm Male - 42mm Female","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"REDUCER(ADAPTER TYPE) 28mm Male - 42mm Female","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"REDUCER(ADAPTER TYPE) 36mm Male - 28mm Female","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"REDUCER(ADAPTER TYPE) 42mm Male - 36mm Female","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"Lock Nut 28mm (1\")","qty":800,"unit":"EA","remaining":800,"log":[]},{"name":"Lock Nut 36mm (1-1/4\")","qty":200,"unit":"EA","remaining":200,"log":[]},{"name":"Lock Nut 42mm (1-1/2\")","qty":100,"unit":"EA","remaining":100,"log":[]},{"name":"Lock Nut 54mm (2\")","qty":50,"unit":"EA","remaining":50,"log":[]},{"name":"Lock Nut 82mm (3\")","qty":160,"unit":"EA","remaining":160,"log":[]},{"name":"Lock Nut 104mm (4\")","qty":100,"unit":"EA","remaining":100,"log":[]},{"name":"Lock Nut 125mm (5\")","qty":120,"unit":"EA","remaining":120,"log":[]},{"name":"Flexible Conduit (Water proof type) 36mm (1-1/4\")","qty":330,"unit":"M","remaining":330,"log":[]}]</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:Z3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:Z4"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/du-lieu/chinh-sua-tay.xlsx
+++ b/du-lieu/chinh-sua-tay.xlsx
@@ -732,7 +732,7 @@
         <v/>
       </c>
       <c r="Z4" t="str">
-        <v>[{"name":"Condulet (\"LT\" Type) 28mm (1\")","qty":30,"unit":"EA","remaining":29,"log":[{"time":"22:30:41 18/8/2026","change":-1,"after":29}]},{"name":"Condulet (\"LT\" Type) 36mm (1-1/4\")","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"Condulet (\"LT\" Type) 42mm (1-1/2\")","qty":10,"unit":"EA","remaining":10,"log":[]},{"name":"Condulet (\"LT\" Type) 54mm (2\")","qty":15,"unit":"EA","remaining":15,"log":[]},{"name":"Condulet (\"LT\" Type) 82mm (3\")","qty":15,"unit":"EA","remaining":15,"log":[]},{"name":"Condulet (\"LT\" Type) 104mm (4\")","qty":10,"unit":"EA","remaining":10,"log":[]},{"name":"Flexible Conduit Connector (Male Type) 28mm (1\")","qty":420,"unit":"EA","remaining":420,"log":[]},{"name":"Flexible Conduit Connector (Male Type) 36mm (1-1/4\")","qty":150,"unit":"EA","remaining":150,"log":[]},{"name":"Flexible Conduit Connector (Male Type) 42mm (1-1/2\")","qty":50,"unit":"EA","remaining":50,"log":[]},{"name":"Flexible Conduit Connector (Male Type) 54mm (2\")","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"Flexible Conduit Connector (Male Type) 82mm (3\")","qty":80,"unit":"EA","remaining":80,"log":[]},{"name":"Flexible Conduit Connector (Male Type) 104mm (4\")","qty":50,"unit":"EA","remaining":50,"log":[]},{"name":"Flexible Conduit Connector (Female Type) 28mm (1\")","qty":420,"unit":"EA","remaining":420,"log":[]},{"name":"Flexible Conduit Connector (Female Type) 36mm (1-1/4\")","qty":150,"unit":"EA","remaining":150,"log":[]},{"name":"Flexible Conduit Connector (Female Type) 42mm (1-1/2\")","qty":50,"unit":"EA","remaining":50,"log":[]},{"name":"Flexible Conduit Connector (Female Type) 54mm (2\")","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"Flexible Conduit Connector (Female Type) 82mm (3\")","qty":80,"unit":"EA","remaining":80,"log":[]},{"name":"Flexible Conduit Connector (Female Type) 104mm (4\")","qty":50,"unit":"EA","remaining":50,"log":[]},{"name":"Union Coupling (Male Type) 28mm (1\")","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"Union Coupling (Male Type) 36mm (1-1/4\")","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"Union Coupling (Male Type) 42mm (1-1/2\")","qty":10,"unit":"EA","remaining":10,"log":[]},{"name":"Union Coupling (Male Type) 54mm (2\")","qty":10,"unit":"EA","remaining":10,"log":[]},{"name":"Union Coupling (Male Type) 82mm (3\")","qty":10,"unit":"EA","remaining":10,"log":[]},{"name":"Nipple(EXPLOSION TYPE, NPT to PF) 28mm (1\")","qty":10,"unit":"EA","remaining":10,"log":[]},{"name":"Nipple(EXPLOSION TYPE, NPT to PF) 36mm (1-1/4\")","qty":5,"unit":"EA","remaining":5,"log":[]},{"name":"Nipple(EXPLOSION TYPE, NPT to PF) 42mm (1-1/2\")","qty":5,"unit":"EA","remaining":5,"log":[]},{"name":"Nipple(EXPLOSION TYPE, NPT to PF) 54mm (2\")","qty":5,"unit":"EA","remaining":5,"log":[]},{"name":"SEALING COMPOUND Plaster FOR SEALING FITTING 1KG/CAN","qty":50,"unit":"EA","remaining":50,"log":[]},{"name":"REDUCER(ADAPTER TYPE) 36mm Male - 28mm Female","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"REDUCER(ADAPTER TYPE) 36mm Male - 28mm Female","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"REDUCER(ADAPTER TYPE) 42mm Male - 28mm Female","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"REDUCER(ADAPTER TYPE) 54mm Male - 28mm Female","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"REDUCER(ADAPTER TYPE) 54mm Male - 42mm Female","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"REDUCER(ADAPTER TYPE) 28mm Male - 42mm Female","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"REDUCER(ADAPTER TYPE) 36mm Male - 28mm Female","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"REDUCER(ADAPTER TYPE) 42mm Male - 36mm Female","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"Lock Nut 28mm (1\")","qty":800,"unit":"EA","remaining":800,"log":[]},{"name":"Lock Nut 36mm (1-1/4\")","qty":200,"unit":"EA","remaining":200,"log":[]},{"name":"Lock Nut 42mm (1-1/2\")","qty":100,"unit":"EA","remaining":100,"log":[]},{"name":"Lock Nut 54mm (2\")","qty":50,"unit":"EA","remaining":50,"log":[]},{"name":"Lock Nut 82mm (3\")","qty":160,"unit":"EA","remaining":160,"log":[]},{"name":"Lock Nut 104mm (4\")","qty":100,"unit":"EA","remaining":100,"log":[]},{"name":"Lock Nut 125mm (5\")","qty":120,"unit":"EA","remaining":120,"log":[]},{"name":"Flexible Conduit (Water proof type) 36mm (1-1/4\")","qty":330,"unit":"M","remaining":330,"log":[]}]</v>
+        <v>[{"name":"Condulet (\"LT\" Type) 28mm (1\")","qty":30,"unit":"EA","remaining":28,"log":[{"time":"22:30:47 18/8/2026","change":-1,"after":28},{"time":"22:30:41 18/8/2026","change":-1,"after":29}]},{"name":"Condulet (\"LT\" Type) 36mm (1-1/4\")","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"Condulet (\"LT\" Type) 42mm (1-1/2\")","qty":10,"unit":"EA","remaining":10,"log":[]},{"name":"Condulet (\"LT\" Type) 54mm (2\")","qty":15,"unit":"EA","remaining":15,"log":[]},{"name":"Condulet (\"LT\" Type) 82mm (3\")","qty":15,"unit":"EA","remaining":15,"log":[]},{"name":"Condulet (\"LT\" Type) 104mm (4\")","qty":10,"unit":"EA","remaining":10,"log":[]},{"name":"Flexible Conduit Connector (Male Type) 28mm (1\")","qty":420,"unit":"EA","remaining":420,"log":[]},{"name":"Flexible Conduit Connector (Male Type) 36mm (1-1/4\")","qty":150,"unit":"EA","remaining":150,"log":[]},{"name":"Flexible Conduit Connector (Male Type) 42mm (1-1/2\")","qty":50,"unit":"EA","remaining":50,"log":[]},{"name":"Flexible Conduit Connector (Male Type) 54mm (2\")","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"Flexible Conduit Connector (Male Type) 82mm (3\")","qty":80,"unit":"EA","remaining":80,"log":[]},{"name":"Flexible Conduit Connector (Male Type) 104mm (4\")","qty":50,"unit":"EA","remaining":50,"log":[]},{"name":"Flexible Conduit Connector (Female Type) 28mm (1\")","qty":420,"unit":"EA","remaining":420,"log":[]},{"name":"Flexible Conduit Connector (Female Type) 36mm (1-1/4\")","qty":150,"unit":"EA","remaining":150,"log":[]},{"name":"Flexible Conduit Connector (Female Type) 42mm (1-1/2\")","qty":50,"unit":"EA","remaining":50,"log":[]},{"name":"Flexible Conduit Connector (Female Type) 54mm (2\")","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"Flexible Conduit Connector (Female Type) 82mm (3\")","qty":80,"unit":"EA","remaining":80,"log":[]},{"name":"Flexible Conduit Connector (Female Type) 104mm (4\")","qty":50,"unit":"EA","remaining":50,"log":[]},{"name":"Union Coupling (Male Type) 28mm (1\")","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"Union Coupling (Male Type) 36mm (1-1/4\")","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"Union Coupling (Male Type) 42mm (1-1/2\")","qty":10,"unit":"EA","remaining":10,"log":[]},{"name":"Union Coupling (Male Type) 54mm (2\")","qty":10,"unit":"EA","remaining":10,"log":[]},{"name":"Union Coupling (Male Type) 82mm (3\")","qty":10,"unit":"EA","remaining":10,"log":[]},{"name":"Nipple(EXPLOSION TYPE, NPT to PF) 28mm (1\")","qty":10,"unit":"EA","remaining":10,"log":[]},{"name":"Nipple(EXPLOSION TYPE, NPT to PF) 36mm (1-1/4\")","qty":5,"unit":"EA","remaining":5,"log":[]},{"name":"Nipple(EXPLOSION TYPE, NPT to PF) 42mm (1-1/2\")","qty":5,"unit":"EA","remaining":5,"log":[]},{"name":"Nipple(EXPLOSION TYPE, NPT to PF) 54mm (2\")","qty":5,"unit":"EA","remaining":5,"log":[]},{"name":"SEALING COMPOUND Plaster FOR SEALING FITTING 1KG/CAN","qty":50,"unit":"EA","remaining":50,"log":[]},{"name":"REDUCER(ADAPTER TYPE) 36mm Male - 28mm Female","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"REDUCER(ADAPTER TYPE) 36mm Male - 28mm Female","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"REDUCER(ADAPTER TYPE) 42mm Male - 28mm Female","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"REDUCER(ADAPTER TYPE) 54mm Male - 28mm Female","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"REDUCER(ADAPTER TYPE) 54mm Male - 42mm Female","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"REDUCER(ADAPTER TYPE) 28mm Male - 42mm Female","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"REDUCER(ADAPTER TYPE) 36mm Male - 28mm Female","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"REDUCER(ADAPTER TYPE) 42mm Male - 36mm Female","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"Lock Nut 28mm (1\")","qty":800,"unit":"EA","remaining":800,"log":[]},{"name":"Lock Nut 36mm (1-1/4\")","qty":200,"unit":"EA","remaining":200,"log":[]},{"name":"Lock Nut 42mm (1-1/2\")","qty":100,"unit":"EA","remaining":100,"log":[]},{"name":"Lock Nut 54mm (2\")","qty":50,"unit":"EA","remaining":50,"log":[]},{"name":"Lock Nut 82mm (3\")","qty":160,"unit":"EA","remaining":160,"log":[]},{"name":"Lock Nut 104mm (4\")","qty":100,"unit":"EA","remaining":100,"log":[]},{"name":"Lock Nut 125mm (5\")","qty":120,"unit":"EA","remaining":120,"log":[]},{"name":"Flexible Conduit (Water proof type) 36mm (1-1/4\")","qty":330,"unit":"M","remaining":330,"log":[]}]</v>
       </c>
     </row>
   </sheetData>

--- a/du-lieu/chinh-sua-tay.xlsx
+++ b/du-lieu/chinh-sua-tay.xlsx
@@ -732,7 +732,7 @@
         <v/>
       </c>
       <c r="Z4" t="str">
-        <v>[{"name":"Condulet (\"LT\" Type) 28mm (1\")","qty":30,"unit":"EA","remaining":28,"log":[{"time":"22:30:47 18/8/2026","change":-1,"after":28},{"time":"22:30:41 18/8/2026","change":-1,"after":29}]},{"name":"Condulet (\"LT\" Type) 36mm (1-1/4\")","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"Condulet (\"LT\" Type) 42mm (1-1/2\")","qty":10,"unit":"EA","remaining":10,"log":[]},{"name":"Condulet (\"LT\" Type) 54mm (2\")","qty":15,"unit":"EA","remaining":15,"log":[]},{"name":"Condulet (\"LT\" Type) 82mm (3\")","qty":15,"unit":"EA","remaining":15,"log":[]},{"name":"Condulet (\"LT\" Type) 104mm (4\")","qty":10,"unit":"EA","remaining":10,"log":[]},{"name":"Flexible Conduit Connector (Male Type) 28mm (1\")","qty":420,"unit":"EA","remaining":420,"log":[]},{"name":"Flexible Conduit Connector (Male Type) 36mm (1-1/4\")","qty":150,"unit":"EA","remaining":150,"log":[]},{"name":"Flexible Conduit Connector (Male Type) 42mm (1-1/2\")","qty":50,"unit":"EA","remaining":50,"log":[]},{"name":"Flexible Conduit Connector (Male Type) 54mm (2\")","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"Flexible Conduit Connector (Male Type) 82mm (3\")","qty":80,"unit":"EA","remaining":80,"log":[]},{"name":"Flexible Conduit Connector (Male Type) 104mm (4\")","qty":50,"unit":"EA","remaining":50,"log":[]},{"name":"Flexible Conduit Connector (Female Type) 28mm (1\")","qty":420,"unit":"EA","remaining":420,"log":[]},{"name":"Flexible Conduit Connector (Female Type) 36mm (1-1/4\")","qty":150,"unit":"EA","remaining":150,"log":[]},{"name":"Flexible Conduit Connector (Female Type) 42mm (1-1/2\")","qty":50,"unit":"EA","remaining":50,"log":[]},{"name":"Flexible Conduit Connector (Female Type) 54mm (2\")","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"Flexible Conduit Connector (Female Type) 82mm (3\")","qty":80,"unit":"EA","remaining":80,"log":[]},{"name":"Flexible Conduit Connector (Female Type) 104mm (4\")","qty":50,"unit":"EA","remaining":50,"log":[]},{"name":"Union Coupling (Male Type) 28mm (1\")","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"Union Coupling (Male Type) 36mm (1-1/4\")","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"Union Coupling (Male Type) 42mm (1-1/2\")","qty":10,"unit":"EA","remaining":10,"log":[]},{"name":"Union Coupling (Male Type) 54mm (2\")","qty":10,"unit":"EA","remaining":10,"log":[]},{"name":"Union Coupling (Male Type) 82mm (3\")","qty":10,"unit":"EA","remaining":10,"log":[]},{"name":"Nipple(EXPLOSION TYPE, NPT to PF) 28mm (1\")","qty":10,"unit":"EA","remaining":10,"log":[]},{"name":"Nipple(EXPLOSION TYPE, NPT to PF) 36mm (1-1/4\")","qty":5,"unit":"EA","remaining":5,"log":[]},{"name":"Nipple(EXPLOSION TYPE, NPT to PF) 42mm (1-1/2\")","qty":5,"unit":"EA","remaining":5,"log":[]},{"name":"Nipple(EXPLOSION TYPE, NPT to PF) 54mm (2\")","qty":5,"unit":"EA","remaining":5,"log":[]},{"name":"SEALING COMPOUND Plaster FOR SEALING FITTING 1KG/CAN","qty":50,"unit":"EA","remaining":50,"log":[]},{"name":"REDUCER(ADAPTER TYPE) 36mm Male - 28mm Female","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"REDUCER(ADAPTER TYPE) 36mm Male - 28mm Female","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"REDUCER(ADAPTER TYPE) 42mm Male - 28mm Female","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"REDUCER(ADAPTER TYPE) 54mm Male - 28mm Female","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"REDUCER(ADAPTER TYPE) 54mm Male - 42mm Female","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"REDUCER(ADAPTER TYPE) 28mm Male - 42mm Female","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"REDUCER(ADAPTER TYPE) 36mm Male - 28mm Female","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"REDUCER(ADAPTER TYPE) 42mm Male - 36mm Female","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"Lock Nut 28mm (1\")","qty":800,"unit":"EA","remaining":800,"log":[]},{"name":"Lock Nut 36mm (1-1/4\")","qty":200,"unit":"EA","remaining":200,"log":[]},{"name":"Lock Nut 42mm (1-1/2\")","qty":100,"unit":"EA","remaining":100,"log":[]},{"name":"Lock Nut 54mm (2\")","qty":50,"unit":"EA","remaining":50,"log":[]},{"name":"Lock Nut 82mm (3\")","qty":160,"unit":"EA","remaining":160,"log":[]},{"name":"Lock Nut 104mm (4\")","qty":100,"unit":"EA","remaining":100,"log":[]},{"name":"Lock Nut 125mm (5\")","qty":120,"unit":"EA","remaining":120,"log":[]},{"name":"Flexible Conduit (Water proof type) 36mm (1-1/4\")","qty":330,"unit":"M","remaining":330,"log":[]}]</v>
+        <v>[{"name":"Condulet (\"LT\" Type) 28mm (1\")","qty":30,"unit":"EA","remaining":27,"log":[{"time":"22:31:00 18/8/2026","change":-1,"after":27},{"time":"22:30:47 18/8/2026","change":-1,"after":28},{"time":"22:30:41 18/8/2026","change":-1,"after":29}]},{"name":"Condulet (\"LT\" Type) 36mm (1-1/4\")","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"Condulet (\"LT\" Type) 42mm (1-1/2\")","qty":10,"unit":"EA","remaining":10,"log":[]},{"name":"Condulet (\"LT\" Type) 54mm (2\")","qty":15,"unit":"EA","remaining":15,"log":[]},{"name":"Condulet (\"LT\" Type) 82mm (3\")","qty":15,"unit":"EA","remaining":15,"log":[]},{"name":"Condulet (\"LT\" Type) 104mm (4\")","qty":10,"unit":"EA","remaining":10,"log":[]},{"name":"Flexible Conduit Connector (Male Type) 28mm (1\")","qty":420,"unit":"EA","remaining":420,"log":[]},{"name":"Flexible Conduit Connector (Male Type) 36mm (1-1/4\")","qty":150,"unit":"EA","remaining":150,"log":[]},{"name":"Flexible Conduit Connector (Male Type) 42mm (1-1/2\")","qty":50,"unit":"EA","remaining":50,"log":[]},{"name":"Flexible Conduit Connector (Male Type) 54mm (2\")","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"Flexible Conduit Connector (Male Type) 82mm (3\")","qty":80,"unit":"EA","remaining":80,"log":[]},{"name":"Flexible Conduit Connector (Male Type) 104mm (4\")","qty":50,"unit":"EA","remaining":50,"log":[]},{"name":"Flexible Conduit Connector (Female Type) 28mm (1\")","qty":420,"unit":"EA","remaining":420,"log":[]},{"name":"Flexible Conduit Connector (Female Type) 36mm (1-1/4\")","qty":150,"unit":"EA","remaining":150,"log":[]},{"name":"Flexible Conduit Connector (Female Type) 42mm (1-1/2\")","qty":50,"unit":"EA","remaining":50,"log":[]},{"name":"Flexible Conduit Connector (Female Type) 54mm (2\")","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"Flexible Conduit Connector (Female Type) 82mm (3\")","qty":80,"unit":"EA","remaining":80,"log":[]},{"name":"Flexible Conduit Connector (Female Type) 104mm (4\")","qty":50,"unit":"EA","remaining":50,"log":[]},{"name":"Union Coupling (Male Type) 28mm (1\")","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"Union Coupling (Male Type) 36mm (1-1/4\")","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"Union Coupling (Male Type) 42mm (1-1/2\")","qty":10,"unit":"EA","remaining":10,"log":[]},{"name":"Union Coupling (Male Type) 54mm (2\")","qty":10,"unit":"EA","remaining":10,"log":[]},{"name":"Union Coupling (Male Type) 82mm (3\")","qty":10,"unit":"EA","remaining":10,"log":[]},{"name":"Nipple(EXPLOSION TYPE, NPT to PF) 28mm (1\")","qty":10,"unit":"EA","remaining":10,"log":[]},{"name":"Nipple(EXPLOSION TYPE, NPT to PF) 36mm (1-1/4\")","qty":5,"unit":"EA","remaining":5,"log":[]},{"name":"Nipple(EXPLOSION TYPE, NPT to PF) 42mm (1-1/2\")","qty":5,"unit":"EA","remaining":5,"log":[]},{"name":"Nipple(EXPLOSION TYPE, NPT to PF) 54mm (2\")","qty":5,"unit":"EA","remaining":5,"log":[]},{"name":"SEALING COMPOUND Plaster FOR SEALING FITTING 1KG/CAN","qty":50,"unit":"EA","remaining":50,"log":[]},{"name":"REDUCER(ADAPTER TYPE) 36mm Male - 28mm Female","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"REDUCER(ADAPTER TYPE) 36mm Male - 28mm Female","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"REDUCER(ADAPTER TYPE) 42mm Male - 28mm Female","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"REDUCER(ADAPTER TYPE) 54mm Male - 28mm Female","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"REDUCER(ADAPTER TYPE) 54mm Male - 42mm Female","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"REDUCER(ADAPTER TYPE) 28mm Male - 42mm Female","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"REDUCER(ADAPTER TYPE) 36mm Male - 28mm Female","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"REDUCER(ADAPTER TYPE) 42mm Male - 36mm Female","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"Lock Nut 28mm (1\")","qty":800,"unit":"EA","remaining":800,"log":[]},{"name":"Lock Nut 36mm (1-1/4\")","qty":200,"unit":"EA","remaining":200,"log":[]},{"name":"Lock Nut 42mm (1-1/2\")","qty":100,"unit":"EA","remaining":100,"log":[]},{"name":"Lock Nut 54mm (2\")","qty":50,"unit":"EA","remaining":50,"log":[]},{"name":"Lock Nut 82mm (3\")","qty":160,"unit":"EA","remaining":160,"log":[]},{"name":"Lock Nut 104mm (4\")","qty":100,"unit":"EA","remaining":100,"log":[]},{"name":"Lock Nut 125mm (5\")","qty":120,"unit":"EA","remaining":120,"log":[]},{"name":"Flexible Conduit (Water proof type) 36mm (1-1/4\")","qty":330,"unit":"M","remaining":330,"log":[]}]</v>
       </c>
     </row>
   </sheetData>

--- a/du-lieu/chinh-sua-tay.xlsx
+++ b/du-lieu/chinh-sua-tay.xlsx
@@ -732,7 +732,7 @@
         <v/>
       </c>
       <c r="Z4" t="str">
-        <v>[{"name":"Condulet (\"LT\" Type) 28mm (1\")","qty":30,"unit":"EA","remaining":27,"log":[{"time":"22:31:00 18/8/2026","change":-1,"after":27},{"time":"22:30:47 18/8/2026","change":-1,"after":28},{"time":"22:30:41 18/8/2026","change":-1,"after":29}]},{"name":"Condulet (\"LT\" Type) 36mm (1-1/4\")","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"Condulet (\"LT\" Type) 42mm (1-1/2\")","qty":10,"unit":"EA","remaining":10,"log":[]},{"name":"Condulet (\"LT\" Type) 54mm (2\")","qty":15,"unit":"EA","remaining":15,"log":[]},{"name":"Condulet (\"LT\" Type) 82mm (3\")","qty":15,"unit":"EA","remaining":15,"log":[]},{"name":"Condulet (\"LT\" Type) 104mm (4\")","qty":10,"unit":"EA","remaining":10,"log":[]},{"name":"Flexible Conduit Connector (Male Type) 28mm (1\")","qty":420,"unit":"EA","remaining":420,"log":[]},{"name":"Flexible Conduit Connector (Male Type) 36mm (1-1/4\")","qty":150,"unit":"EA","remaining":150,"log":[]},{"name":"Flexible Conduit Connector (Male Type) 42mm (1-1/2\")","qty":50,"unit":"EA","remaining":50,"log":[]},{"name":"Flexible Conduit Connector (Male Type) 54mm (2\")","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"Flexible Conduit Connector (Male Type) 82mm (3\")","qty":80,"unit":"EA","remaining":80,"log":[]},{"name":"Flexible Conduit Connector (Male Type) 104mm (4\")","qty":50,"unit":"EA","remaining":50,"log":[]},{"name":"Flexible Conduit Connector (Female Type) 28mm (1\")","qty":420,"unit":"EA","remaining":420,"log":[]},{"name":"Flexible Conduit Connector (Female Type) 36mm (1-1/4\")","qty":150,"unit":"EA","remaining":150,"log":[]},{"name":"Flexible Conduit Connector (Female Type) 42mm (1-1/2\")","qty":50,"unit":"EA","remaining":50,"log":[]},{"name":"Flexible Conduit Connector (Female Type) 54mm (2\")","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"Flexible Conduit Connector (Female Type) 82mm (3\")","qty":80,"unit":"EA","remaining":80,"log":[]},{"name":"Flexible Conduit Connector (Female Type) 104mm (4\")","qty":50,"unit":"EA","remaining":50,"log":[]},{"name":"Union Coupling (Male Type) 28mm (1\")","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"Union Coupling (Male Type) 36mm (1-1/4\")","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"Union Coupling (Male Type) 42mm (1-1/2\")","qty":10,"unit":"EA","remaining":10,"log":[]},{"name":"Union Coupling (Male Type) 54mm (2\")","qty":10,"unit":"EA","remaining":10,"log":[]},{"name":"Union Coupling (Male Type) 82mm (3\")","qty":10,"unit":"EA","remaining":10,"log":[]},{"name":"Nipple(EXPLOSION TYPE, NPT to PF) 28mm (1\")","qty":10,"unit":"EA","remaining":10,"log":[]},{"name":"Nipple(EXPLOSION TYPE, NPT to PF) 36mm (1-1/4\")","qty":5,"unit":"EA","remaining":5,"log":[]},{"name":"Nipple(EXPLOSION TYPE, NPT to PF) 42mm (1-1/2\")","qty":5,"unit":"EA","remaining":5,"log":[]},{"name":"Nipple(EXPLOSION TYPE, NPT to PF) 54mm (2\")","qty":5,"unit":"EA","remaining":5,"log":[]},{"name":"SEALING COMPOUND Plaster FOR SEALING FITTING 1KG/CAN","qty":50,"unit":"EA","remaining":50,"log":[]},{"name":"REDUCER(ADAPTER TYPE) 36mm Male - 28mm Female","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"REDUCER(ADAPTER TYPE) 36mm Male - 28mm Female","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"REDUCER(ADAPTER TYPE) 42mm Male - 28mm Female","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"REDUCER(ADAPTER TYPE) 54mm Male - 28mm Female","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"REDUCER(ADAPTER TYPE) 54mm Male - 42mm Female","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"REDUCER(ADAPTER TYPE) 28mm Male - 42mm Female","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"REDUCER(ADAPTER TYPE) 36mm Male - 28mm Female","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"REDUCER(ADAPTER TYPE) 42mm Male - 36mm Female","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"Lock Nut 28mm (1\")","qty":800,"unit":"EA","remaining":800,"log":[]},{"name":"Lock Nut 36mm (1-1/4\")","qty":200,"unit":"EA","remaining":200,"log":[]},{"name":"Lock Nut 42mm (1-1/2\")","qty":100,"unit":"EA","remaining":100,"log":[]},{"name":"Lock Nut 54mm (2\")","qty":50,"unit":"EA","remaining":50,"log":[]},{"name":"Lock Nut 82mm (3\")","qty":160,"unit":"EA","remaining":160,"log":[]},{"name":"Lock Nut 104mm (4\")","qty":100,"unit":"EA","remaining":100,"log":[]},{"name":"Lock Nut 125mm (5\")","qty":120,"unit":"EA","remaining":120,"log":[]},{"name":"Flexible Conduit (Water proof type) 36mm (1-1/4\")","qty":330,"unit":"M","remaining":330,"log":[]}]</v>
+        <v>[{"name":"Condulet (\"LT\" Type) 28mm (1\")","qty":30,"unit":"EA","remaining":26,"log":[{"time":"22:31:05 18/8/2026","change":-1,"after":26},{"time":"22:31:00 18/8/2026","change":-1,"after":27},{"time":"22:30:47 18/8/2026","change":-1,"after":28},{"time":"22:30:41 18/8/2026","change":-1,"after":29}]},{"name":"Condulet (\"LT\" Type) 36mm (1-1/4\")","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"Condulet (\"LT\" Type) 42mm (1-1/2\")","qty":10,"unit":"EA","remaining":10,"log":[]},{"name":"Condulet (\"LT\" Type) 54mm (2\")","qty":15,"unit":"EA","remaining":15,"log":[]},{"name":"Condulet (\"LT\" Type) 82mm (3\")","qty":15,"unit":"EA","remaining":15,"log":[]},{"name":"Condulet (\"LT\" Type) 104mm (4\")","qty":10,"unit":"EA","remaining":10,"log":[]},{"name":"Flexible Conduit Connector (Male Type) 28mm (1\")","qty":420,"unit":"EA","remaining":420,"log":[]},{"name":"Flexible Conduit Connector (Male Type) 36mm (1-1/4\")","qty":150,"unit":"EA","remaining":150,"log":[]},{"name":"Flexible Conduit Connector (Male Type) 42mm (1-1/2\")","qty":50,"unit":"EA","remaining":50,"log":[]},{"name":"Flexible Conduit Connector (Male Type) 54mm (2\")","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"Flexible Conduit Connector (Male Type) 82mm (3\")","qty":80,"unit":"EA","remaining":80,"log":[]},{"name":"Flexible Conduit Connector (Male Type) 104mm (4\")","qty":50,"unit":"EA","remaining":50,"log":[]},{"name":"Flexible Conduit Connector (Female Type) 28mm (1\")","qty":420,"unit":"EA","remaining":420,"log":[]},{"name":"Flexible Conduit Connector (Female Type) 36mm (1-1/4\")","qty":150,"unit":"EA","remaining":150,"log":[]},{"name":"Flexible Conduit Connector (Female Type) 42mm (1-1/2\")","qty":50,"unit":"EA","remaining":50,"log":[]},{"name":"Flexible Conduit Connector (Female Type) 54mm (2\")","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"Flexible Conduit Connector (Female Type) 82mm (3\")","qty":80,"unit":"EA","remaining":80,"log":[]},{"name":"Flexible Conduit Connector (Female Type) 104mm (4\")","qty":50,"unit":"EA","remaining":50,"log":[]},{"name":"Union Coupling (Male Type) 28mm (1\")","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"Union Coupling (Male Type) 36mm (1-1/4\")","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"Union Coupling (Male Type) 42mm (1-1/2\")","qty":10,"unit":"EA","remaining":10,"log":[]},{"name":"Union Coupling (Male Type) 54mm (2\")","qty":10,"unit":"EA","remaining":10,"log":[]},{"name":"Union Coupling (Male Type) 82mm (3\")","qty":10,"unit":"EA","remaining":10,"log":[]},{"name":"Nipple(EXPLOSION TYPE, NPT to PF) 28mm (1\")","qty":10,"unit":"EA","remaining":10,"log":[]},{"name":"Nipple(EXPLOSION TYPE, NPT to PF) 36mm (1-1/4\")","qty":5,"unit":"EA","remaining":5,"log":[]},{"name":"Nipple(EXPLOSION TYPE, NPT to PF) 42mm (1-1/2\")","qty":5,"unit":"EA","remaining":5,"log":[]},{"name":"Nipple(EXPLOSION TYPE, NPT to PF) 54mm (2\")","qty":5,"unit":"EA","remaining":5,"log":[]},{"name":"SEALING COMPOUND Plaster FOR SEALING FITTING 1KG/CAN","qty":50,"unit":"EA","remaining":50,"log":[]},{"name":"REDUCER(ADAPTER TYPE) 36mm Male - 28mm Female","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"REDUCER(ADAPTER TYPE) 36mm Male - 28mm Female","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"REDUCER(ADAPTER TYPE) 42mm Male - 28mm Female","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"REDUCER(ADAPTER TYPE) 54mm Male - 28mm Female","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"REDUCER(ADAPTER TYPE) 54mm Male - 42mm Female","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"REDUCER(ADAPTER TYPE) 28mm Male - 42mm Female","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"REDUCER(ADAPTER TYPE) 36mm Male - 28mm Female","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"REDUCER(ADAPTER TYPE) 42mm Male - 36mm Female","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"Lock Nut 28mm (1\")","qty":800,"unit":"EA","remaining":800,"log":[]},{"name":"Lock Nut 36mm (1-1/4\")","qty":200,"unit":"EA","remaining":200,"log":[]},{"name":"Lock Nut 42mm (1-1/2\")","qty":100,"unit":"EA","remaining":100,"log":[]},{"name":"Lock Nut 54mm (2\")","qty":50,"unit":"EA","remaining":50,"log":[]},{"name":"Lock Nut 82mm (3\")","qty":160,"unit":"EA","remaining":160,"log":[]},{"name":"Lock Nut 104mm (4\")","qty":100,"unit":"EA","remaining":100,"log":[]},{"name":"Lock Nut 125mm (5\")","qty":120,"unit":"EA","remaining":120,"log":[]},{"name":"Flexible Conduit (Water proof type) 36mm (1-1/4\")","qty":330,"unit":"M","remaining":330,"log":[]}]</v>
       </c>
     </row>
   </sheetData>

--- a/du-lieu/chinh-sua-tay.xlsx
+++ b/du-lieu/chinh-sua-tay.xlsx
@@ -732,7 +732,7 @@
         <v/>
       </c>
       <c r="Z4" t="str">
-        <v>[{"name":"Condulet (\"LT\" Type) 28mm (1\")","qty":30,"unit":"EA","remaining":26,"log":[{"time":"22:31:05 18/8/2026","change":-1,"after":26},{"time":"22:31:00 18/8/2026","change":-1,"after":27},{"time":"22:30:47 18/8/2026","change":-1,"after":28},{"time":"22:30:41 18/8/2026","change":-1,"after":29}]},{"name":"Condulet (\"LT\" Type) 36mm (1-1/4\")","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"Condulet (\"LT\" Type) 42mm (1-1/2\")","qty":10,"unit":"EA","remaining":10,"log":[]},{"name":"Condulet (\"LT\" Type) 54mm (2\")","qty":15,"unit":"EA","remaining":15,"log":[]},{"name":"Condulet (\"LT\" Type) 82mm (3\")","qty":15,"unit":"EA","remaining":15,"log":[]},{"name":"Condulet (\"LT\" Type) 104mm (4\")","qty":10,"unit":"EA","remaining":10,"log":[]},{"name":"Flexible Conduit Connector (Male Type) 28mm (1\")","qty":420,"unit":"EA","remaining":420,"log":[]},{"name":"Flexible Conduit Connector (Male Type) 36mm (1-1/4\")","qty":150,"unit":"EA","remaining":150,"log":[]},{"name":"Flexible Conduit Connector (Male Type) 42mm (1-1/2\")","qty":50,"unit":"EA","remaining":50,"log":[]},{"name":"Flexible Conduit Connector (Male Type) 54mm (2\")","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"Flexible Conduit Connector (Male Type) 82mm (3\")","qty":80,"unit":"EA","remaining":80,"log":[]},{"name":"Flexible Conduit Connector (Male Type) 104mm (4\")","qty":50,"unit":"EA","remaining":50,"log":[]},{"name":"Flexible Conduit Connector (Female Type) 28mm (1\")","qty":420,"unit":"EA","remaining":420,"log":[]},{"name":"Flexible Conduit Connector (Female Type) 36mm (1-1/4\")","qty":150,"unit":"EA","remaining":150,"log":[]},{"name":"Flexible Conduit Connector (Female Type) 42mm (1-1/2\")","qty":50,"unit":"EA","remaining":50,"log":[]},{"name":"Flexible Conduit Connector (Female Type) 54mm (2\")","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"Flexible Conduit Connector (Female Type) 82mm (3\")","qty":80,"unit":"EA","remaining":80,"log":[]},{"name":"Flexible Conduit Connector (Female Type) 104mm (4\")","qty":50,"unit":"EA","remaining":50,"log":[]},{"name":"Union Coupling (Male Type) 28mm (1\")","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"Union Coupling (Male Type) 36mm (1-1/4\")","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"Union Coupling (Male Type) 42mm (1-1/2\")","qty":10,"unit":"EA","remaining":10,"log":[]},{"name":"Union Coupling (Male Type) 54mm (2\")","qty":10,"unit":"EA","remaining":10,"log":[]},{"name":"Union Coupling (Male Type) 82mm (3\")","qty":10,"unit":"EA","remaining":10,"log":[]},{"name":"Nipple(EXPLOSION TYPE, NPT to PF) 28mm (1\")","qty":10,"unit":"EA","remaining":10,"log":[]},{"name":"Nipple(EXPLOSION TYPE, NPT to PF) 36mm (1-1/4\")","qty":5,"unit":"EA","remaining":5,"log":[]},{"name":"Nipple(EXPLOSION TYPE, NPT to PF) 42mm (1-1/2\")","qty":5,"unit":"EA","remaining":5,"log":[]},{"name":"Nipple(EXPLOSION TYPE, NPT to PF) 54mm (2\")","qty":5,"unit":"EA","remaining":5,"log":[]},{"name":"SEALING COMPOUND Plaster FOR SEALING FITTING 1KG/CAN","qty":50,"unit":"EA","remaining":50,"log":[]},{"name":"REDUCER(ADAPTER TYPE) 36mm Male - 28mm Female","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"REDUCER(ADAPTER TYPE) 36mm Male - 28mm Female","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"REDUCER(ADAPTER TYPE) 42mm Male - 28mm Female","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"REDUCER(ADAPTER TYPE) 54mm Male - 28mm Female","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"REDUCER(ADAPTER TYPE) 54mm Male - 42mm Female","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"REDUCER(ADAPTER TYPE) 28mm Male - 42mm Female","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"REDUCER(ADAPTER TYPE) 36mm Male - 28mm Female","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"REDUCER(ADAPTER TYPE) 42mm Male - 36mm Female","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"Lock Nut 28mm (1\")","qty":800,"unit":"EA","remaining":800,"log":[]},{"name":"Lock Nut 36mm (1-1/4\")","qty":200,"unit":"EA","remaining":200,"log":[]},{"name":"Lock Nut 42mm (1-1/2\")","qty":100,"unit":"EA","remaining":100,"log":[]},{"name":"Lock Nut 54mm (2\")","qty":50,"unit":"EA","remaining":50,"log":[]},{"name":"Lock Nut 82mm (3\")","qty":160,"unit":"EA","remaining":160,"log":[]},{"name":"Lock Nut 104mm (4\")","qty":100,"unit":"EA","remaining":100,"log":[]},{"name":"Lock Nut 125mm (5\")","qty":120,"unit":"EA","remaining":120,"log":[]},{"name":"Flexible Conduit (Water proof type) 36mm (1-1/4\")","qty":330,"unit":"M","remaining":330,"log":[]}]</v>
+        <v>[{"name":"Condulet (\"LT\" Type) 28mm (1\")","qty":30,"unit":"EA","remaining":25,"log":[{"time":"22:31:13 18/8/2026","change":-1,"after":25},{"time":"22:31:05 18/8/2026","change":-1,"after":26},{"time":"22:31:00 18/8/2026","change":-1,"after":27},{"time":"22:30:47 18/8/2026","change":-1,"after":28},{"time":"22:30:41 18/8/2026","change":-1,"after":29}]},{"name":"Condulet (\"LT\" Type) 36mm (1-1/4\")","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"Condulet (\"LT\" Type) 42mm (1-1/2\")","qty":10,"unit":"EA","remaining":10,"log":[]},{"name":"Condulet (\"LT\" Type) 54mm (2\")","qty":15,"unit":"EA","remaining":15,"log":[]},{"name":"Condulet (\"LT\" Type) 82mm (3\")","qty":15,"unit":"EA","remaining":15,"log":[]},{"name":"Condulet (\"LT\" Type) 104mm (4\")","qty":10,"unit":"EA","remaining":10,"log":[]},{"name":"Flexible Conduit Connector (Male Type) 28mm (1\")","qty":420,"unit":"EA","remaining":420,"log":[]},{"name":"Flexible Conduit Connector (Male Type) 36mm (1-1/4\")","qty":150,"unit":"EA","remaining":150,"log":[]},{"name":"Flexible Conduit Connector (Male Type) 42mm (1-1/2\")","qty":50,"unit":"EA","remaining":50,"log":[]},{"name":"Flexible Conduit Connector (Male Type) 54mm (2\")","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"Flexible Conduit Connector (Male Type) 82mm (3\")","qty":80,"unit":"EA","remaining":80,"log":[]},{"name":"Flexible Conduit Connector (Male Type) 104mm (4\")","qty":50,"unit":"EA","remaining":50,"log":[]},{"name":"Flexible Conduit Connector (Female Type) 28mm (1\")","qty":420,"unit":"EA","remaining":420,"log":[]},{"name":"Flexible Conduit Connector (Female Type) 36mm (1-1/4\")","qty":150,"unit":"EA","remaining":150,"log":[]},{"name":"Flexible Conduit Connector (Female Type) 42mm (1-1/2\")","qty":50,"unit":"EA","remaining":50,"log":[]},{"name":"Flexible Conduit Connector (Female Type) 54mm (2\")","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"Flexible Conduit Connector (Female Type) 82mm (3\")","qty":80,"unit":"EA","remaining":80,"log":[]},{"name":"Flexible Conduit Connector (Female Type) 104mm (4\")","qty":50,"unit":"EA","remaining":50,"log":[]},{"name":"Union Coupling (Male Type) 28mm (1\")","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"Union Coupling (Male Type) 36mm (1-1/4\")","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"Union Coupling (Male Type) 42mm (1-1/2\")","qty":10,"unit":"EA","remaining":10,"log":[]},{"name":"Union Coupling (Male Type) 54mm (2\")","qty":10,"unit":"EA","remaining":10,"log":[]},{"name":"Union Coupling (Male Type) 82mm (3\")","qty":10,"unit":"EA","remaining":10,"log":[]},{"name":"Nipple(EXPLOSION TYPE, NPT to PF) 28mm (1\")","qty":10,"unit":"EA","remaining":10,"log":[]},{"name":"Nipple(EXPLOSION TYPE, NPT to PF) 36mm (1-1/4\")","qty":5,"unit":"EA","remaining":5,"log":[]},{"name":"Nipple(EXPLOSION TYPE, NPT to PF) 42mm (1-1/2\")","qty":5,"unit":"EA","remaining":5,"log":[]},{"name":"Nipple(EXPLOSION TYPE, NPT to PF) 54mm (2\")","qty":5,"unit":"EA","remaining":5,"log":[]},{"name":"SEALING COMPOUND Plaster FOR SEALING FITTING 1KG/CAN","qty":50,"unit":"EA","remaining":50,"log":[]},{"name":"REDUCER(ADAPTER TYPE) 36mm Male - 28mm Female","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"REDUCER(ADAPTER TYPE) 36mm Male - 28mm Female","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"REDUCER(ADAPTER TYPE) 42mm Male - 28mm Female","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"REDUCER(ADAPTER TYPE) 54mm Male - 28mm Female","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"REDUCER(ADAPTER TYPE) 54mm Male - 42mm Female","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"REDUCER(ADAPTER TYPE) 28mm Male - 42mm Female","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"REDUCER(ADAPTER TYPE) 36mm Male - 28mm Female","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"REDUCER(ADAPTER TYPE) 42mm Male - 36mm Female","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"Lock Nut 28mm (1\")","qty":800,"unit":"EA","remaining":800,"log":[]},{"name":"Lock Nut 36mm (1-1/4\")","qty":200,"unit":"EA","remaining":200,"log":[]},{"name":"Lock Nut 42mm (1-1/2\")","qty":100,"unit":"EA","remaining":100,"log":[]},{"name":"Lock Nut 54mm (2\")","qty":50,"unit":"EA","remaining":50,"log":[]},{"name":"Lock Nut 82mm (3\")","qty":160,"unit":"EA","remaining":160,"log":[]},{"name":"Lock Nut 104mm (4\")","qty":100,"unit":"EA","remaining":100,"log":[]},{"name":"Lock Nut 125mm (5\")","qty":120,"unit":"EA","remaining":120,"log":[]},{"name":"Flexible Conduit (Water proof type) 36mm (1-1/4\")","qty":330,"unit":"M","remaining":330,"log":[]}]</v>
       </c>
     </row>
   </sheetData>

--- a/du-lieu/chinh-sua-tay.xlsx
+++ b/du-lieu/chinh-sua-tay.xlsx
@@ -732,7 +732,7 @@
         <v/>
       </c>
       <c r="Z4" t="str">
-        <v>[{"name":"Condulet (\"LT\" Type) 28mm (1\")","qty":30,"unit":"EA","remaining":25,"log":[{"time":"22:31:13 18/8/2026","change":-1,"after":25},{"time":"22:31:05 18/8/2026","change":-1,"after":26},{"time":"22:31:00 18/8/2026","change":-1,"after":27},{"time":"22:30:47 18/8/2026","change":-1,"after":28},{"time":"22:30:41 18/8/2026","change":-1,"after":29}]},{"name":"Condulet (\"LT\" Type) 36mm (1-1/4\")","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"Condulet (\"LT\" Type) 42mm (1-1/2\")","qty":10,"unit":"EA","remaining":10,"log":[]},{"name":"Condulet (\"LT\" Type) 54mm (2\")","qty":15,"unit":"EA","remaining":15,"log":[]},{"name":"Condulet (\"LT\" Type) 82mm (3\")","qty":15,"unit":"EA","remaining":15,"log":[]},{"name":"Condulet (\"LT\" Type) 104mm (4\")","qty":10,"unit":"EA","remaining":10,"log":[]},{"name":"Flexible Conduit Connector (Male Type) 28mm (1\")","qty":420,"unit":"EA","remaining":420,"log":[]},{"name":"Flexible Conduit Connector (Male Type) 36mm (1-1/4\")","qty":150,"unit":"EA","remaining":150,"log":[]},{"name":"Flexible Conduit Connector (Male Type) 42mm (1-1/2\")","qty":50,"unit":"EA","remaining":50,"log":[]},{"name":"Flexible Conduit Connector (Male Type) 54mm (2\")","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"Flexible Conduit Connector (Male Type) 82mm (3\")","qty":80,"unit":"EA","remaining":80,"log":[]},{"name":"Flexible Conduit Connector (Male Type) 104mm (4\")","qty":50,"unit":"EA","remaining":50,"log":[]},{"name":"Flexible Conduit Connector (Female Type) 28mm (1\")","qty":420,"unit":"EA","remaining":420,"log":[]},{"name":"Flexible Conduit Connector (Female Type) 36mm (1-1/4\")","qty":150,"unit":"EA","remaining":150,"log":[]},{"name":"Flexible Conduit Connector (Female Type) 42mm (1-1/2\")","qty":50,"unit":"EA","remaining":50,"log":[]},{"name":"Flexible Conduit Connector (Female Type) 54mm (2\")","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"Flexible Conduit Connector (Female Type) 82mm (3\")","qty":80,"unit":"EA","remaining":80,"log":[]},{"name":"Flexible Conduit Connector (Female Type) 104mm (4\")","qty":50,"unit":"EA","remaining":50,"log":[]},{"name":"Union Coupling (Male Type) 28mm (1\")","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"Union Coupling (Male Type) 36mm (1-1/4\")","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"Union Coupling (Male Type) 42mm (1-1/2\")","qty":10,"unit":"EA","remaining":10,"log":[]},{"name":"Union Coupling (Male Type) 54mm (2\")","qty":10,"unit":"EA","remaining":10,"log":[]},{"name":"Union Coupling (Male Type) 82mm (3\")","qty":10,"unit":"EA","remaining":10,"log":[]},{"name":"Nipple(EXPLOSION TYPE, NPT to PF) 28mm (1\")","qty":10,"unit":"EA","remaining":10,"log":[]},{"name":"Nipple(EXPLOSION TYPE, NPT to PF) 36mm (1-1/4\")","qty":5,"unit":"EA","remaining":5,"log":[]},{"name":"Nipple(EXPLOSION TYPE, NPT to PF) 42mm (1-1/2\")","qty":5,"unit":"EA","remaining":5,"log":[]},{"name":"Nipple(EXPLOSION TYPE, NPT to PF) 54mm (2\")","qty":5,"unit":"EA","remaining":5,"log":[]},{"name":"SEALING COMPOUND Plaster FOR SEALING FITTING 1KG/CAN","qty":50,"unit":"EA","remaining":50,"log":[]},{"name":"REDUCER(ADAPTER TYPE) 36mm Male - 28mm Female","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"REDUCER(ADAPTER TYPE) 36mm Male - 28mm Female","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"REDUCER(ADAPTER TYPE) 42mm Male - 28mm Female","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"REDUCER(ADAPTER TYPE) 54mm Male - 28mm Female","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"REDUCER(ADAPTER TYPE) 54mm Male - 42mm Female","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"REDUCER(ADAPTER TYPE) 28mm Male - 42mm Female","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"REDUCER(ADAPTER TYPE) 36mm Male - 28mm Female","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"REDUCER(ADAPTER TYPE) 42mm Male - 36mm Female","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"Lock Nut 28mm (1\")","qty":800,"unit":"EA","remaining":800,"log":[]},{"name":"Lock Nut 36mm (1-1/4\")","qty":200,"unit":"EA","remaining":200,"log":[]},{"name":"Lock Nut 42mm (1-1/2\")","qty":100,"unit":"EA","remaining":100,"log":[]},{"name":"Lock Nut 54mm (2\")","qty":50,"unit":"EA","remaining":50,"log":[]},{"name":"Lock Nut 82mm (3\")","qty":160,"unit":"EA","remaining":160,"log":[]},{"name":"Lock Nut 104mm (4\")","qty":100,"unit":"EA","remaining":100,"log":[]},{"name":"Lock Nut 125mm (5\")","qty":120,"unit":"EA","remaining":120,"log":[]},{"name":"Flexible Conduit (Water proof type) 36mm (1-1/4\")","qty":330,"unit":"M","remaining":330,"log":[]}]</v>
+        <v>[{"name":"Condulet (\"LT\" Type) 28mm (1\")","qty":30,"unit":"EA","remaining":24,"log":[{"time":"22:31:43 18/8/2026","change":-1,"after":24},{"time":"22:31:13 18/8/2026","change":-1,"after":25},{"time":"22:31:05 18/8/2026","change":-1,"after":26},{"time":"22:31:00 18/8/2026","change":-1,"after":27},{"time":"22:30:47 18/8/2026","change":-1,"after":28},{"time":"22:30:41 18/8/2026","change":-1,"after":29}]},{"name":"Condulet (\"LT\" Type) 36mm (1-1/4\")","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"Condulet (\"LT\" Type) 42mm (1-1/2\")","qty":10,"unit":"EA","remaining":10,"log":[]},{"name":"Condulet (\"LT\" Type) 54mm (2\")","qty":15,"unit":"EA","remaining":15,"log":[]},{"name":"Condulet (\"LT\" Type) 82mm (3\")","qty":15,"unit":"EA","remaining":15,"log":[]},{"name":"Condulet (\"LT\" Type) 104mm (4\")","qty":10,"unit":"EA","remaining":10,"log":[]},{"name":"Flexible Conduit Connector (Male Type) 28mm (1\")","qty":420,"unit":"EA","remaining":420,"log":[]},{"name":"Flexible Conduit Connector (Male Type) 36mm (1-1/4\")","qty":150,"unit":"EA","remaining":150,"log":[]},{"name":"Flexible Conduit Connector (Male Type) 42mm (1-1/2\")","qty":50,"unit":"EA","remaining":50,"log":[]},{"name":"Flexible Conduit Connector (Male Type) 54mm (2\")","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"Flexible Conduit Connector (Male Type) 82mm (3\")","qty":80,"unit":"EA","remaining":80,"log":[]},{"name":"Flexible Conduit Connector (Male Type) 104mm (4\")","qty":50,"unit":"EA","remaining":50,"log":[]},{"name":"Flexible Conduit Connector (Female Type) 28mm (1\")","qty":420,"unit":"EA","remaining":420,"log":[]},{"name":"Flexible Conduit Connector (Female Type) 36mm (1-1/4\")","qty":150,"unit":"EA","remaining":150,"log":[]},{"name":"Flexible Conduit Connector (Female Type) 42mm (1-1/2\")","qty":50,"unit":"EA","remaining":50,"log":[]},{"name":"Flexible Conduit Connector (Female Type) 54mm (2\")","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"Flexible Conduit Connector (Female Type) 82mm (3\")","qty":80,"unit":"EA","remaining":80,"log":[]},{"name":"Flexible Conduit Connector (Female Type) 104mm (4\")","qty":50,"unit":"EA","remaining":50,"log":[]},{"name":"Union Coupling (Male Type) 28mm (1\")","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"Union Coupling (Male Type) 36mm (1-1/4\")","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"Union Coupling (Male Type) 42mm (1-1/2\")","qty":10,"unit":"EA","remaining":10,"log":[]},{"name":"Union Coupling (Male Type) 54mm (2\")","qty":10,"unit":"EA","remaining":10,"log":[]},{"name":"Union Coupling (Male Type) 82mm (3\")","qty":10,"unit":"EA","remaining":10,"log":[]},{"name":"Nipple(EXPLOSION TYPE, NPT to PF) 28mm (1\")","qty":10,"unit":"EA","remaining":10,"log":[]},{"name":"Nipple(EXPLOSION TYPE, NPT to PF) 36mm (1-1/4\")","qty":5,"unit":"EA","remaining":5,"log":[]},{"name":"Nipple(EXPLOSION TYPE, NPT to PF) 42mm (1-1/2\")","qty":5,"unit":"EA","remaining":5,"log":[]},{"name":"Nipple(EXPLOSION TYPE, NPT to PF) 54mm (2\")","qty":5,"unit":"EA","remaining":5,"log":[]},{"name":"SEALING COMPOUND Plaster FOR SEALING FITTING 1KG/CAN","qty":50,"unit":"EA","remaining":50,"log":[]},{"name":"REDUCER(ADAPTER TYPE) 36mm Male - 28mm Female","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"REDUCER(ADAPTER TYPE) 36mm Male - 28mm Female","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"REDUCER(ADAPTER TYPE) 42mm Male - 28mm Female","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"REDUCER(ADAPTER TYPE) 54mm Male - 28mm Female","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"REDUCER(ADAPTER TYPE) 54mm Male - 42mm Female","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"REDUCER(ADAPTER TYPE) 28mm Male - 42mm Female","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"REDUCER(ADAPTER TYPE) 36mm Male - 28mm Female","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"REDUCER(ADAPTER TYPE) 42mm Male - 36mm Female","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"Lock Nut 28mm (1\")","qty":800,"unit":"EA","remaining":800,"log":[]},{"name":"Lock Nut 36mm (1-1/4\")","qty":200,"unit":"EA","remaining":200,"log":[]},{"name":"Lock Nut 42mm (1-1/2\")","qty":100,"unit":"EA","remaining":100,"log":[]},{"name":"Lock Nut 54mm (2\")","qty":50,"unit":"EA","remaining":50,"log":[]},{"name":"Lock Nut 82mm (3\")","qty":160,"unit":"EA","remaining":160,"log":[]},{"name":"Lock Nut 104mm (4\")","qty":100,"unit":"EA","remaining":100,"log":[]},{"name":"Lock Nut 125mm (5\")","qty":120,"unit":"EA","remaining":120,"log":[]},{"name":"Flexible Conduit (Water proof type) 36mm (1-1/4\")","qty":330,"unit":"M","remaining":330,"log":[]}]</v>
       </c>
     </row>
   </sheetData>

--- a/du-lieu/chinh-sua-tay.xlsx
+++ b/du-lieu/chinh-sua-tay.xlsx
@@ -732,7 +732,7 @@
         <v/>
       </c>
       <c r="Z4" t="str">
-        <v>[{"name":"Condulet (\"LT\" Type) 28mm (1\")","qty":30,"unit":"EA","remaining":24,"log":[{"time":"22:31:43 18/8/2026","change":-1,"after":24},{"time":"22:31:13 18/8/2026","change":-1,"after":25},{"time":"22:31:05 18/8/2026","change":-1,"after":26},{"time":"22:31:00 18/8/2026","change":-1,"after":27},{"time":"22:30:47 18/8/2026","change":-1,"after":28},{"time":"22:30:41 18/8/2026","change":-1,"after":29}]},{"name":"Condulet (\"LT\" Type) 36mm (1-1/4\")","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"Condulet (\"LT\" Type) 42mm (1-1/2\")","qty":10,"unit":"EA","remaining":10,"log":[]},{"name":"Condulet (\"LT\" Type) 54mm (2\")","qty":15,"unit":"EA","remaining":15,"log":[]},{"name":"Condulet (\"LT\" Type) 82mm (3\")","qty":15,"unit":"EA","remaining":15,"log":[]},{"name":"Condulet (\"LT\" Type) 104mm (4\")","qty":10,"unit":"EA","remaining":10,"log":[]},{"name":"Flexible Conduit Connector (Male Type) 28mm (1\")","qty":420,"unit":"EA","remaining":420,"log":[]},{"name":"Flexible Conduit Connector (Male Type) 36mm (1-1/4\")","qty":150,"unit":"EA","remaining":150,"log":[]},{"name":"Flexible Conduit Connector (Male Type) 42mm (1-1/2\")","qty":50,"unit":"EA","remaining":50,"log":[]},{"name":"Flexible Conduit Connector (Male Type) 54mm (2\")","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"Flexible Conduit Connector (Male Type) 82mm (3\")","qty":80,"unit":"EA","remaining":80,"log":[]},{"name":"Flexible Conduit Connector (Male Type) 104mm (4\")","qty":50,"unit":"EA","remaining":50,"log":[]},{"name":"Flexible Conduit Connector (Female Type) 28mm (1\")","qty":420,"unit":"EA","remaining":420,"log":[]},{"name":"Flexible Conduit Connector (Female Type) 36mm (1-1/4\")","qty":150,"unit":"EA","remaining":150,"log":[]},{"name":"Flexible Conduit Connector (Female Type) 42mm (1-1/2\")","qty":50,"unit":"EA","remaining":50,"log":[]},{"name":"Flexible Conduit Connector (Female Type) 54mm (2\")","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"Flexible Conduit Connector (Female Type) 82mm (3\")","qty":80,"unit":"EA","remaining":80,"log":[]},{"name":"Flexible Conduit Connector (Female Type) 104mm (4\")","qty":50,"unit":"EA","remaining":50,"log":[]},{"name":"Union Coupling (Male Type) 28mm (1\")","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"Union Coupling (Male Type) 36mm (1-1/4\")","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"Union Coupling (Male Type) 42mm (1-1/2\")","qty":10,"unit":"EA","remaining":10,"log":[]},{"name":"Union Coupling (Male Type) 54mm (2\")","qty":10,"unit":"EA","remaining":10,"log":[]},{"name":"Union Coupling (Male Type) 82mm (3\")","qty":10,"unit":"EA","remaining":10,"log":[]},{"name":"Nipple(EXPLOSION TYPE, NPT to PF) 28mm (1\")","qty":10,"unit":"EA","remaining":10,"log":[]},{"name":"Nipple(EXPLOSION TYPE, NPT to PF) 36mm (1-1/4\")","qty":5,"unit":"EA","remaining":5,"log":[]},{"name":"Nipple(EXPLOSION TYPE, NPT to PF) 42mm (1-1/2\")","qty":5,"unit":"EA","remaining":5,"log":[]},{"name":"Nipple(EXPLOSION TYPE, NPT to PF) 54mm (2\")","qty":5,"unit":"EA","remaining":5,"log":[]},{"name":"SEALING COMPOUND Plaster FOR SEALING FITTING 1KG/CAN","qty":50,"unit":"EA","remaining":50,"log":[]},{"name":"REDUCER(ADAPTER TYPE) 36mm Male - 28mm Female","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"REDUCER(ADAPTER TYPE) 36mm Male - 28mm Female","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"REDUCER(ADAPTER TYPE) 42mm Male - 28mm Female","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"REDUCER(ADAPTER TYPE) 54mm Male - 28mm Female","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"REDUCER(ADAPTER TYPE) 54mm Male - 42mm Female","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"REDUCER(ADAPTER TYPE) 28mm Male - 42mm Female","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"REDUCER(ADAPTER TYPE) 36mm Male - 28mm Female","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"REDUCER(ADAPTER TYPE) 42mm Male - 36mm Female","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"Lock Nut 28mm (1\")","qty":800,"unit":"EA","remaining":800,"log":[]},{"name":"Lock Nut 36mm (1-1/4\")","qty":200,"unit":"EA","remaining":200,"log":[]},{"name":"Lock Nut 42mm (1-1/2\")","qty":100,"unit":"EA","remaining":100,"log":[]},{"name":"Lock Nut 54mm (2\")","qty":50,"unit":"EA","remaining":50,"log":[]},{"name":"Lock Nut 82mm (3\")","qty":160,"unit":"EA","remaining":160,"log":[]},{"name":"Lock Nut 104mm (4\")","qty":100,"unit":"EA","remaining":100,"log":[]},{"name":"Lock Nut 125mm (5\")","qty":120,"unit":"EA","remaining":120,"log":[]},{"name":"Flexible Conduit (Water proof type) 36mm (1-1/4\")","qty":330,"unit":"M","remaining":330,"log":[]}]</v>
+        <v>[{"name":"Condulet (\"LT\" Type) 28mm (1\")","qty":30,"unit":"EA","remaining":25,"log":[{"time":"22:31:49 18/8/2026","change":1,"after":25},{"time":"22:31:43 18/8/2026","change":-1,"after":24},{"time":"22:31:13 18/8/2026","change":-1,"after":25},{"time":"22:31:05 18/8/2026","change":-1,"after":26},{"time":"22:31:00 18/8/2026","change":-1,"after":27},{"time":"22:30:47 18/8/2026","change":-1,"after":28},{"time":"22:30:41 18/8/2026","change":-1,"after":29}]},{"name":"Condulet (\"LT\" Type) 36mm (1-1/4\")","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"Condulet (\"LT\" Type) 42mm (1-1/2\")","qty":10,"unit":"EA","remaining":10,"log":[]},{"name":"Condulet (\"LT\" Type) 54mm (2\")","qty":15,"unit":"EA","remaining":15,"log":[]},{"name":"Condulet (\"LT\" Type) 82mm (3\")","qty":15,"unit":"EA","remaining":15,"log":[]},{"name":"Condulet (\"LT\" Type) 104mm (4\")","qty":10,"unit":"EA","remaining":10,"log":[]},{"name":"Flexible Conduit Connector (Male Type) 28mm (1\")","qty":420,"unit":"EA","remaining":420,"log":[]},{"name":"Flexible Conduit Connector (Male Type) 36mm (1-1/4\")","qty":150,"unit":"EA","remaining":150,"log":[]},{"name":"Flexible Conduit Connector (Male Type) 42mm (1-1/2\")","qty":50,"unit":"EA","remaining":50,"log":[]},{"name":"Flexible Conduit Connector (Male Type) 54mm (2\")","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"Flexible Conduit Connector (Male Type) 82mm (3\")","qty":80,"unit":"EA","remaining":80,"log":[]},{"name":"Flexible Conduit Connector (Male Type) 104mm (4\")","qty":50,"unit":"EA","remaining":50,"log":[]},{"name":"Flexible Conduit Connector (Female Type) 28mm (1\")","qty":420,"unit":"EA","remaining":420,"log":[]},{"name":"Flexible Conduit Connector (Female Type) 36mm (1-1/4\")","qty":150,"unit":"EA","remaining":150,"log":[]},{"name":"Flexible Conduit Connector (Female Type) 42mm (1-1/2\")","qty":50,"unit":"EA","remaining":50,"log":[]},{"name":"Flexible Conduit Connector (Female Type) 54mm (2\")","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"Flexible Conduit Connector (Female Type) 82mm (3\")","qty":80,"unit":"EA","remaining":80,"log":[]},{"name":"Flexible Conduit Connector (Female Type) 104mm (4\")","qty":50,"unit":"EA","remaining":50,"log":[]},{"name":"Union Coupling (Male Type) 28mm (1\")","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"Union Coupling (Male Type) 36mm (1-1/4\")","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"Union Coupling (Male Type) 42mm (1-1/2\")","qty":10,"unit":"EA","remaining":10,"log":[]},{"name":"Union Coupling (Male Type) 54mm (2\")","qty":10,"unit":"EA","remaining":10,"log":[]},{"name":"Union Coupling (Male Type) 82mm (3\")","qty":10,"unit":"EA","remaining":10,"log":[]},{"name":"Nipple(EXPLOSION TYPE, NPT to PF) 28mm (1\")","qty":10,"unit":"EA","remaining":10,"log":[]},{"name":"Nipple(EXPLOSION TYPE, NPT to PF) 36mm (1-1/4\")","qty":5,"unit":"EA","remaining":5,"log":[]},{"name":"Nipple(EXPLOSION TYPE, NPT to PF) 42mm (1-1/2\")","qty":5,"unit":"EA","remaining":5,"log":[]},{"name":"Nipple(EXPLOSION TYPE, NPT to PF) 54mm (2\")","qty":5,"unit":"EA","remaining":5,"log":[]},{"name":"SEALING COMPOUND Plaster FOR SEALING FITTING 1KG/CAN","qty":50,"unit":"EA","remaining":50,"log":[]},{"name":"REDUCER(ADAPTER TYPE) 36mm Male - 28mm Female","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"REDUCER(ADAPTER TYPE) 36mm Male - 28mm Female","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"REDUCER(ADAPTER TYPE) 42mm Male - 28mm Female","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"REDUCER(ADAPTER TYPE) 54mm Male - 28mm Female","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"REDUCER(ADAPTER TYPE) 54mm Male - 42mm Female","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"REDUCER(ADAPTER TYPE) 28mm Male - 42mm Female","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"REDUCER(ADAPTER TYPE) 36mm Male - 28mm Female","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"REDUCER(ADAPTER TYPE) 42mm Male - 36mm Female","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"Lock Nut 28mm (1\")","qty":800,"unit":"EA","remaining":800,"log":[]},{"name":"Lock Nut 36mm (1-1/4\")","qty":200,"unit":"EA","remaining":200,"log":[]},{"name":"Lock Nut 42mm (1-1/2\")","qty":100,"unit":"EA","remaining":100,"log":[]},{"name":"Lock Nut 54mm (2\")","qty":50,"unit":"EA","remaining":50,"log":[]},{"name":"Lock Nut 82mm (3\")","qty":160,"unit":"EA","remaining":160,"log":[]},{"name":"Lock Nut 104mm (4\")","qty":100,"unit":"EA","remaining":100,"log":[]},{"name":"Lock Nut 125mm (5\")","qty":120,"unit":"EA","remaining":120,"log":[]},{"name":"Flexible Conduit (Water proof type) 36mm (1-1/4\")","qty":330,"unit":"M","remaining":330,"log":[]}]</v>
       </c>
     </row>
   </sheetData>

--- a/du-lieu/chinh-sua-tay.xlsx
+++ b/du-lieu/chinh-sua-tay.xlsx
@@ -732,7 +732,7 @@
         <v/>
       </c>
       <c r="Z4" t="str">
-        <v>[{"name":"Condulet (\"LT\" Type) 28mm (1\")","qty":30,"unit":"EA","remaining":25,"log":[{"time":"22:31:49 18/8/2026","change":1,"after":25},{"time":"22:31:43 18/8/2026","change":-1,"after":24},{"time":"22:31:13 18/8/2026","change":-1,"after":25},{"time":"22:31:05 18/8/2026","change":-1,"after":26},{"time":"22:31:00 18/8/2026","change":-1,"after":27},{"time":"22:30:47 18/8/2026","change":-1,"after":28},{"time":"22:30:41 18/8/2026","change":-1,"after":29}]},{"name":"Condulet (\"LT\" Type) 36mm (1-1/4\")","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"Condulet (\"LT\" Type) 42mm (1-1/2\")","qty":10,"unit":"EA","remaining":10,"log":[]},{"name":"Condulet (\"LT\" Type) 54mm (2\")","qty":15,"unit":"EA","remaining":15,"log":[]},{"name":"Condulet (\"LT\" Type) 82mm (3\")","qty":15,"unit":"EA","remaining":15,"log":[]},{"name":"Condulet (\"LT\" Type) 104mm (4\")","qty":10,"unit":"EA","remaining":10,"log":[]},{"name":"Flexible Conduit Connector (Male Type) 28mm (1\")","qty":420,"unit":"EA","remaining":420,"log":[]},{"name":"Flexible Conduit Connector (Male Type) 36mm (1-1/4\")","qty":150,"unit":"EA","remaining":150,"log":[]},{"name":"Flexible Conduit Connector (Male Type) 42mm (1-1/2\")","qty":50,"unit":"EA","remaining":50,"log":[]},{"name":"Flexible Conduit Connector (Male Type) 54mm (2\")","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"Flexible Conduit Connector (Male Type) 82mm (3\")","qty":80,"unit":"EA","remaining":80,"log":[]},{"name":"Flexible Conduit Connector (Male Type) 104mm (4\")","qty":50,"unit":"EA","remaining":50,"log":[]},{"name":"Flexible Conduit Connector (Female Type) 28mm (1\")","qty":420,"unit":"EA","remaining":420,"log":[]},{"name":"Flexible Conduit Connector (Female Type) 36mm (1-1/4\")","qty":150,"unit":"EA","remaining":150,"log":[]},{"name":"Flexible Conduit Connector (Female Type) 42mm (1-1/2\")","qty":50,"unit":"EA","remaining":50,"log":[]},{"name":"Flexible Conduit Connector (Female Type) 54mm (2\")","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"Flexible Conduit Connector (Female Type) 82mm (3\")","qty":80,"unit":"EA","remaining":80,"log":[]},{"name":"Flexible Conduit Connector (Female Type) 104mm (4\")","qty":50,"unit":"EA","remaining":50,"log":[]},{"name":"Union Coupling (Male Type) 28mm (1\")","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"Union Coupling (Male Type) 36mm (1-1/4\")","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"Union Coupling (Male Type) 42mm (1-1/2\")","qty":10,"unit":"EA","remaining":10,"log":[]},{"name":"Union Coupling (Male Type) 54mm (2\")","qty":10,"unit":"EA","remaining":10,"log":[]},{"name":"Union Coupling (Male Type) 82mm (3\")","qty":10,"unit":"EA","remaining":10,"log":[]},{"name":"Nipple(EXPLOSION TYPE, NPT to PF) 28mm (1\")","qty":10,"unit":"EA","remaining":10,"log":[]},{"name":"Nipple(EXPLOSION TYPE, NPT to PF) 36mm (1-1/4\")","qty":5,"unit":"EA","remaining":5,"log":[]},{"name":"Nipple(EXPLOSION TYPE, NPT to PF) 42mm (1-1/2\")","qty":5,"unit":"EA","remaining":5,"log":[]},{"name":"Nipple(EXPLOSION TYPE, NPT to PF) 54mm (2\")","qty":5,"unit":"EA","remaining":5,"log":[]},{"name":"SEALING COMPOUND Plaster FOR SEALING FITTING 1KG/CAN","qty":50,"unit":"EA","remaining":50,"log":[]},{"name":"REDUCER(ADAPTER TYPE) 36mm Male - 28mm Female","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"REDUCER(ADAPTER TYPE) 36mm Male - 28mm Female","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"REDUCER(ADAPTER TYPE) 42mm Male - 28mm Female","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"REDUCER(ADAPTER TYPE) 54mm Male - 28mm Female","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"REDUCER(ADAPTER TYPE) 54mm Male - 42mm Female","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"REDUCER(ADAPTER TYPE) 28mm Male - 42mm Female","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"REDUCER(ADAPTER TYPE) 36mm Male - 28mm Female","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"REDUCER(ADAPTER TYPE) 42mm Male - 36mm Female","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"Lock Nut 28mm (1\")","qty":800,"unit":"EA","remaining":800,"log":[]},{"name":"Lock Nut 36mm (1-1/4\")","qty":200,"unit":"EA","remaining":200,"log":[]},{"name":"Lock Nut 42mm (1-1/2\")","qty":100,"unit":"EA","remaining":100,"log":[]},{"name":"Lock Nut 54mm (2\")","qty":50,"unit":"EA","remaining":50,"log":[]},{"name":"Lock Nut 82mm (3\")","qty":160,"unit":"EA","remaining":160,"log":[]},{"name":"Lock Nut 104mm (4\")","qty":100,"unit":"EA","remaining":100,"log":[]},{"name":"Lock Nut 125mm (5\")","qty":120,"unit":"EA","remaining":120,"log":[]},{"name":"Flexible Conduit (Water proof type) 36mm (1-1/4\")","qty":330,"unit":"M","remaining":330,"log":[]}]</v>
+        <v>[{"name":"Condulet (\"LT\" Type) 28mm (1\")","qty":30,"unit":"EA","remaining":26,"log":[{"time":"22:31:54 18/8/2026","change":1,"after":26},{"time":"22:31:49 18/8/2026","change":1,"after":25},{"time":"22:31:43 18/8/2026","change":-1,"after":24},{"time":"22:31:13 18/8/2026","change":-1,"after":25},{"time":"22:31:05 18/8/2026","change":-1,"after":26},{"time":"22:31:00 18/8/2026","change":-1,"after":27},{"time":"22:30:47 18/8/2026","change":-1,"after":28},{"time":"22:30:41 18/8/2026","change":-1,"after":29}]},{"name":"Condulet (\"LT\" Type) 36mm (1-1/4\")","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"Condulet (\"LT\" Type) 42mm (1-1/2\")","qty":10,"unit":"EA","remaining":10,"log":[]},{"name":"Condulet (\"LT\" Type) 54mm (2\")","qty":15,"unit":"EA","remaining":15,"log":[]},{"name":"Condulet (\"LT\" Type) 82mm (3\")","qty":15,"unit":"EA","remaining":15,"log":[]},{"name":"Condulet (\"LT\" Type) 104mm (4\")","qty":10,"unit":"EA","remaining":10,"log":[]},{"name":"Flexible Conduit Connector (Male Type) 28mm (1\")","qty":420,"unit":"EA","remaining":420,"log":[]},{"name":"Flexible Conduit Connector (Male Type) 36mm (1-1/4\")","qty":150,"unit":"EA","remaining":150,"log":[]},{"name":"Flexible Conduit Connector (Male Type) 42mm (1-1/2\")","qty":50,"unit":"EA","remaining":50,"log":[]},{"name":"Flexible Conduit Connector (Male Type) 54mm (2\")","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"Flexible Conduit Connector (Male Type) 82mm (3\")","qty":80,"unit":"EA","remaining":80,"log":[]},{"name":"Flexible Conduit Connector (Male Type) 104mm (4\")","qty":50,"unit":"EA","remaining":50,"log":[]},{"name":"Flexible Conduit Connector (Female Type) 28mm (1\")","qty":420,"unit":"EA","remaining":420,"log":[]},{"name":"Flexible Conduit Connector (Female Type) 36mm (1-1/4\")","qty":150,"unit":"EA","remaining":150,"log":[]},{"name":"Flexible Conduit Connector (Female Type) 42mm (1-1/2\")","qty":50,"unit":"EA","remaining":50,"log":[]},{"name":"Flexible Conduit Connector (Female Type) 54mm (2\")","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"Flexible Conduit Connector (Female Type) 82mm (3\")","qty":80,"unit":"EA","remaining":80,"log":[]},{"name":"Flexible Conduit Connector (Female Type) 104mm (4\")","qty":50,"unit":"EA","remaining":50,"log":[]},{"name":"Union Coupling (Male Type) 28mm (1\")","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"Union Coupling (Male Type) 36mm (1-1/4\")","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"Union Coupling (Male Type) 42mm (1-1/2\")","qty":10,"unit":"EA","remaining":10,"log":[]},{"name":"Union Coupling (Male Type) 54mm (2\")","qty":10,"unit":"EA","remaining":10,"log":[]},{"name":"Union Coupling (Male Type) 82mm (3\")","qty":10,"unit":"EA","remaining":10,"log":[]},{"name":"Nipple(EXPLOSION TYPE, NPT to PF) 28mm (1\")","qty":10,"unit":"EA","remaining":10,"log":[]},{"name":"Nipple(EXPLOSION TYPE, NPT to PF) 36mm (1-1/4\")","qty":5,"unit":"EA","remaining":5,"log":[]},{"name":"Nipple(EXPLOSION TYPE, NPT to PF) 42mm (1-1/2\")","qty":5,"unit":"EA","remaining":5,"log":[]},{"name":"Nipple(EXPLOSION TYPE, NPT to PF) 54mm (2\")","qty":5,"unit":"EA","remaining":5,"log":[]},{"name":"SEALING COMPOUND Plaster FOR SEALING FITTING 1KG/CAN","qty":50,"unit":"EA","remaining":50,"log":[]},{"name":"REDUCER(ADAPTER TYPE) 36mm Male - 28mm Female","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"REDUCER(ADAPTER TYPE) 36mm Male - 28mm Female","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"REDUCER(ADAPTER TYPE) 42mm Male - 28mm Female","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"REDUCER(ADAPTER TYPE) 54mm Male - 28mm Female","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"REDUCER(ADAPTER TYPE) 54mm Male - 42mm Female","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"REDUCER(ADAPTER TYPE) 28mm Male - 42mm Female","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"REDUCER(ADAPTER TYPE) 36mm Male - 28mm Female","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"REDUCER(ADAPTER TYPE) 42mm Male - 36mm Female","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"Lock Nut 28mm (1\")","qty":800,"unit":"EA","remaining":800,"log":[]},{"name":"Lock Nut 36mm (1-1/4\")","qty":200,"unit":"EA","remaining":200,"log":[]},{"name":"Lock Nut 42mm (1-1/2\")","qty":100,"unit":"EA","remaining":100,"log":[]},{"name":"Lock Nut 54mm (2\")","qty":50,"unit":"EA","remaining":50,"log":[]},{"name":"Lock Nut 82mm (3\")","qty":160,"unit":"EA","remaining":160,"log":[]},{"name":"Lock Nut 104mm (4\")","qty":100,"unit":"EA","remaining":100,"log":[]},{"name":"Lock Nut 125mm (5\")","qty":120,"unit":"EA","remaining":120,"log":[]},{"name":"Flexible Conduit (Water proof type) 36mm (1-1/4\")","qty":330,"unit":"M","remaining":330,"log":[]}]</v>
       </c>
     </row>
   </sheetData>

--- a/du-lieu/chinh-sua-tay.xlsx
+++ b/du-lieu/chinh-sua-tay.xlsx
@@ -732,7 +732,7 @@
         <v/>
       </c>
       <c r="Z4" t="str">
-        <v>[{"name":"Condulet (\"LT\" Type) 28mm (1\")","qty":30,"unit":"EA","remaining":26,"log":[{"time":"22:31:54 18/8/2026","change":1,"after":26},{"time":"22:31:49 18/8/2026","change":1,"after":25},{"time":"22:31:43 18/8/2026","change":-1,"after":24},{"time":"22:31:13 18/8/2026","change":-1,"after":25},{"time":"22:31:05 18/8/2026","change":-1,"after":26},{"time":"22:31:00 18/8/2026","change":-1,"after":27},{"time":"22:30:47 18/8/2026","change":-1,"after":28},{"time":"22:30:41 18/8/2026","change":-1,"after":29}]},{"name":"Condulet (\"LT\" Type) 36mm (1-1/4\")","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"Condulet (\"LT\" Type) 42mm (1-1/2\")","qty":10,"unit":"EA","remaining":10,"log":[]},{"name":"Condulet (\"LT\" Type) 54mm (2\")","qty":15,"unit":"EA","remaining":15,"log":[]},{"name":"Condulet (\"LT\" Type) 82mm (3\")","qty":15,"unit":"EA","remaining":15,"log":[]},{"name":"Condulet (\"LT\" Type) 104mm (4\")","qty":10,"unit":"EA","remaining":10,"log":[]},{"name":"Flexible Conduit Connector (Male Type) 28mm (1\")","qty":420,"unit":"EA","remaining":420,"log":[]},{"name":"Flexible Conduit Connector (Male Type) 36mm (1-1/4\")","qty":150,"unit":"EA","remaining":150,"log":[]},{"name":"Flexible Conduit Connector (Male Type) 42mm (1-1/2\")","qty":50,"unit":"EA","remaining":50,"log":[]},{"name":"Flexible Conduit Connector (Male Type) 54mm (2\")","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"Flexible Conduit Connector (Male Type) 82mm (3\")","qty":80,"unit":"EA","remaining":80,"log":[]},{"name":"Flexible Conduit Connector (Male Type) 104mm (4\")","qty":50,"unit":"EA","remaining":50,"log":[]},{"name":"Flexible Conduit Connector (Female Type) 28mm (1\")","qty":420,"unit":"EA","remaining":420,"log":[]},{"name":"Flexible Conduit Connector (Female Type) 36mm (1-1/4\")","qty":150,"unit":"EA","remaining":150,"log":[]},{"name":"Flexible Conduit Connector (Female Type) 42mm (1-1/2\")","qty":50,"unit":"EA","remaining":50,"log":[]},{"name":"Flexible Conduit Connector (Female Type) 54mm (2\")","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"Flexible Conduit Connector (Female Type) 82mm (3\")","qty":80,"unit":"EA","remaining":80,"log":[]},{"name":"Flexible Conduit Connector (Female Type) 104mm (4\")","qty":50,"unit":"EA","remaining":50,"log":[]},{"name":"Union Coupling (Male Type) 28mm (1\")","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"Union Coupling (Male Type) 36mm (1-1/4\")","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"Union Coupling (Male Type) 42mm (1-1/2\")","qty":10,"unit":"EA","remaining":10,"log":[]},{"name":"Union Coupling (Male Type) 54mm (2\")","qty":10,"unit":"EA","remaining":10,"log":[]},{"name":"Union Coupling (Male Type) 82mm (3\")","qty":10,"unit":"EA","remaining":10,"log":[]},{"name":"Nipple(EXPLOSION TYPE, NPT to PF) 28mm (1\")","qty":10,"unit":"EA","remaining":10,"log":[]},{"name":"Nipple(EXPLOSION TYPE, NPT to PF) 36mm (1-1/4\")","qty":5,"unit":"EA","remaining":5,"log":[]},{"name":"Nipple(EXPLOSION TYPE, NPT to PF) 42mm (1-1/2\")","qty":5,"unit":"EA","remaining":5,"log":[]},{"name":"Nipple(EXPLOSION TYPE, NPT to PF) 54mm (2\")","qty":5,"unit":"EA","remaining":5,"log":[]},{"name":"SEALING COMPOUND Plaster FOR SEALING FITTING 1KG/CAN","qty":50,"unit":"EA","remaining":50,"log":[]},{"name":"REDUCER(ADAPTER TYPE) 36mm Male - 28mm Female","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"REDUCER(ADAPTER TYPE) 36mm Male - 28mm Female","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"REDUCER(ADAPTER TYPE) 42mm Male - 28mm Female","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"REDUCER(ADAPTER TYPE) 54mm Male - 28mm Female","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"REDUCER(ADAPTER TYPE) 54mm Male - 42mm Female","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"REDUCER(ADAPTER TYPE) 28mm Male - 42mm Female","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"REDUCER(ADAPTER TYPE) 36mm Male - 28mm Female","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"REDUCER(ADAPTER TYPE) 42mm Male - 36mm Female","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"Lock Nut 28mm (1\")","qty":800,"unit":"EA","remaining":800,"log":[]},{"name":"Lock Nut 36mm (1-1/4\")","qty":200,"unit":"EA","remaining":200,"log":[]},{"name":"Lock Nut 42mm (1-1/2\")","qty":100,"unit":"EA","remaining":100,"log":[]},{"name":"Lock Nut 54mm (2\")","qty":50,"unit":"EA","remaining":50,"log":[]},{"name":"Lock Nut 82mm (3\")","qty":160,"unit":"EA","remaining":160,"log":[]},{"name":"Lock Nut 104mm (4\")","qty":100,"unit":"EA","remaining":100,"log":[]},{"name":"Lock Nut 125mm (5\")","qty":120,"unit":"EA","remaining":120,"log":[]},{"name":"Flexible Conduit (Water proof type) 36mm (1-1/4\")","qty":330,"unit":"M","remaining":330,"log":[]}]</v>
+        <v>[{"name":"Condulet (\"LT\" Type) 28mm (1\")","qty":30,"unit":"EA","remaining":27,"log":[{"time":"22:31:58 18/8/2026","change":1,"after":27},{"time":"22:31:54 18/8/2026","change":1,"after":26},{"time":"22:31:49 18/8/2026","change":1,"after":25},{"time":"22:31:43 18/8/2026","change":-1,"after":24},{"time":"22:31:13 18/8/2026","change":-1,"after":25},{"time":"22:31:05 18/8/2026","change":-1,"after":26},{"time":"22:31:00 18/8/2026","change":-1,"after":27},{"time":"22:30:47 18/8/2026","change":-1,"after":28},{"time":"22:30:41 18/8/2026","change":-1,"after":29}]},{"name":"Condulet (\"LT\" Type) 36mm (1-1/4\")","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"Condulet (\"LT\" Type) 42mm (1-1/2\")","qty":10,"unit":"EA","remaining":10,"log":[]},{"name":"Condulet (\"LT\" Type) 54mm (2\")","qty":15,"unit":"EA","remaining":15,"log":[]},{"name":"Condulet (\"LT\" Type) 82mm (3\")","qty":15,"unit":"EA","remaining":15,"log":[]},{"name":"Condulet (\"LT\" Type) 104mm (4\")","qty":10,"unit":"EA","remaining":10,"log":[]},{"name":"Flexible Conduit Connector (Male Type) 28mm (1\")","qty":420,"unit":"EA","remaining":420,"log":[]},{"name":"Flexible Conduit Connector (Male Type) 36mm (1-1/4\")","qty":150,"unit":"EA","remaining":150,"log":[]},{"name":"Flexible Conduit Connector (Male Type) 42mm (1-1/2\")","qty":50,"unit":"EA","remaining":50,"log":[]},{"name":"Flexible Conduit Connector (Male Type) 54mm (2\")","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"Flexible Conduit Connector (Male Type) 82mm (3\")","qty":80,"unit":"EA","remaining":80,"log":[]},{"name":"Flexible Conduit Connector (Male Type) 104mm (4\")","qty":50,"unit":"EA","remaining":50,"log":[]},{"name":"Flexible Conduit Connector (Female Type) 28mm (1\")","qty":420,"unit":"EA","remaining":420,"log":[]},{"name":"Flexible Conduit Connector (Female Type) 36mm (1-1/4\")","qty":150,"unit":"EA","remaining":150,"log":[]},{"name":"Flexible Conduit Connector (Female Type) 42mm (1-1/2\")","qty":50,"unit":"EA","remaining":50,"log":[]},{"name":"Flexible Conduit Connector (Female Type) 54mm (2\")","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"Flexible Conduit Connector (Female Type) 82mm (3\")","qty":80,"unit":"EA","remaining":80,"log":[]},{"name":"Flexible Conduit Connector (Female Type) 104mm (4\")","qty":50,"unit":"EA","remaining":50,"log":[]},{"name":"Union Coupling (Male Type) 28mm (1\")","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"Union Coupling (Male Type) 36mm (1-1/4\")","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"Union Coupling (Male Type) 42mm (1-1/2\")","qty":10,"unit":"EA","remaining":10,"log":[]},{"name":"Union Coupling (Male Type) 54mm (2\")","qty":10,"unit":"EA","remaining":10,"log":[]},{"name":"Union Coupling (Male Type) 82mm (3\")","qty":10,"unit":"EA","remaining":10,"log":[]},{"name":"Nipple(EXPLOSION TYPE, NPT to PF) 28mm (1\")","qty":10,"unit":"EA","remaining":10,"log":[]},{"name":"Nipple(EXPLOSION TYPE, NPT to PF) 36mm (1-1/4\")","qty":5,"unit":"EA","remaining":5,"log":[]},{"name":"Nipple(EXPLOSION TYPE, NPT to PF) 42mm (1-1/2\")","qty":5,"unit":"EA","remaining":5,"log":[]},{"name":"Nipple(EXPLOSION TYPE, NPT to PF) 54mm (2\")","qty":5,"unit":"EA","remaining":5,"log":[]},{"name":"SEALING COMPOUND Plaster FOR SEALING FITTING 1KG/CAN","qty":50,"unit":"EA","remaining":50,"log":[]},{"name":"REDUCER(ADAPTER TYPE) 36mm Male - 28mm Female","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"REDUCER(ADAPTER TYPE) 36mm Male - 28mm Female","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"REDUCER(ADAPTER TYPE) 42mm Male - 28mm Female","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"REDUCER(ADAPTER TYPE) 54mm Male - 28mm Female","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"REDUCER(ADAPTER TYPE) 54mm Male - 42mm Female","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"REDUCER(ADAPTER TYPE) 28mm Male - 42mm Female","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"REDUCER(ADAPTER TYPE) 36mm Male - 28mm Female","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"REDUCER(ADAPTER TYPE) 42mm Male - 36mm Female","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"Lock Nut 28mm (1\")","qty":800,"unit":"EA","remaining":800,"log":[]},{"name":"Lock Nut 36mm (1-1/4\")","qty":200,"unit":"EA","remaining":200,"log":[]},{"name":"Lock Nut 42mm (1-1/2\")","qty":100,"unit":"EA","remaining":100,"log":[]},{"name":"Lock Nut 54mm (2\")","qty":50,"unit":"EA","remaining":50,"log":[]},{"name":"Lock Nut 82mm (3\")","qty":160,"unit":"EA","remaining":160,"log":[]},{"name":"Lock Nut 104mm (4\")","qty":100,"unit":"EA","remaining":100,"log":[]},{"name":"Lock Nut 125mm (5\")","qty":120,"unit":"EA","remaining":120,"log":[]},{"name":"Flexible Conduit (Water proof type) 36mm (1-1/4\")","qty":330,"unit":"M","remaining":330,"log":[]}]</v>
       </c>
     </row>
   </sheetData>

--- a/du-lieu/chinh-sua-tay.xlsx
+++ b/du-lieu/chinh-sua-tay.xlsx
@@ -732,7 +732,7 @@
         <v/>
       </c>
       <c r="Z4" t="str">
-        <v>[{"name":"Condulet (\"LT\" Type) 28mm (1\")","qty":30,"unit":"EA","remaining":27,"log":[{"time":"22:31:58 18/8/2026","change":1,"after":27},{"time":"22:31:54 18/8/2026","change":1,"after":26},{"time":"22:31:49 18/8/2026","change":1,"after":25},{"time":"22:31:43 18/8/2026","change":-1,"after":24},{"time":"22:31:13 18/8/2026","change":-1,"after":25},{"time":"22:31:05 18/8/2026","change":-1,"after":26},{"time":"22:31:00 18/8/2026","change":-1,"after":27},{"time":"22:30:47 18/8/2026","change":-1,"after":28},{"time":"22:30:41 18/8/2026","change":-1,"after":29}]},{"name":"Condulet (\"LT\" Type) 36mm (1-1/4\")","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"Condulet (\"LT\" Type) 42mm (1-1/2\")","qty":10,"unit":"EA","remaining":10,"log":[]},{"name":"Condulet (\"LT\" Type) 54mm (2\")","qty":15,"unit":"EA","remaining":15,"log":[]},{"name":"Condulet (\"LT\" Type) 82mm (3\")","qty":15,"unit":"EA","remaining":15,"log":[]},{"name":"Condulet (\"LT\" Type) 104mm (4\")","qty":10,"unit":"EA","remaining":10,"log":[]},{"name":"Flexible Conduit Connector (Male Type) 28mm (1\")","qty":420,"unit":"EA","remaining":420,"log":[]},{"name":"Flexible Conduit Connector (Male Type) 36mm (1-1/4\")","qty":150,"unit":"EA","remaining":150,"log":[]},{"name":"Flexible Conduit Connector (Male Type) 42mm (1-1/2\")","qty":50,"unit":"EA","remaining":50,"log":[]},{"name":"Flexible Conduit Connector (Male Type) 54mm (2\")","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"Flexible Conduit Connector (Male Type) 82mm (3\")","qty":80,"unit":"EA","remaining":80,"log":[]},{"name":"Flexible Conduit Connector (Male Type) 104mm (4\")","qty":50,"unit":"EA","remaining":50,"log":[]},{"name":"Flexible Conduit Connector (Female Type) 28mm (1\")","qty":420,"unit":"EA","remaining":420,"log":[]},{"name":"Flexible Conduit Connector (Female Type) 36mm (1-1/4\")","qty":150,"unit":"EA","remaining":150,"log":[]},{"name":"Flexible Conduit Connector (Female Type) 42mm (1-1/2\")","qty":50,"unit":"EA","remaining":50,"log":[]},{"name":"Flexible Conduit Connector (Female Type) 54mm (2\")","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"Flexible Conduit Connector (Female Type) 82mm (3\")","qty":80,"unit":"EA","remaining":80,"log":[]},{"name":"Flexible Conduit Connector (Female Type) 104mm (4\")","qty":50,"unit":"EA","remaining":50,"log":[]},{"name":"Union Coupling (Male Type) 28mm (1\")","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"Union Coupling (Male Type) 36mm (1-1/4\")","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"Union Coupling (Male Type) 42mm (1-1/2\")","qty":10,"unit":"EA","remaining":10,"log":[]},{"name":"Union Coupling (Male Type) 54mm (2\")","qty":10,"unit":"EA","remaining":10,"log":[]},{"name":"Union Coupling (Male Type) 82mm (3\")","qty":10,"unit":"EA","remaining":10,"log":[]},{"name":"Nipple(EXPLOSION TYPE, NPT to PF) 28mm (1\")","qty":10,"unit":"EA","remaining":10,"log":[]},{"name":"Nipple(EXPLOSION TYPE, NPT to PF) 36mm (1-1/4\")","qty":5,"unit":"EA","remaining":5,"log":[]},{"name":"Nipple(EXPLOSION TYPE, NPT to PF) 42mm (1-1/2\")","qty":5,"unit":"EA","remaining":5,"log":[]},{"name":"Nipple(EXPLOSION TYPE, NPT to PF) 54mm (2\")","qty":5,"unit":"EA","remaining":5,"log":[]},{"name":"SEALING COMPOUND Plaster FOR SEALING FITTING 1KG/CAN","qty":50,"unit":"EA","remaining":50,"log":[]},{"name":"REDUCER(ADAPTER TYPE) 36mm Male - 28mm Female","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"REDUCER(ADAPTER TYPE) 36mm Male - 28mm Female","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"REDUCER(ADAPTER TYPE) 42mm Male - 28mm Female","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"REDUCER(ADAPTER TYPE) 54mm Male - 28mm Female","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"REDUCER(ADAPTER TYPE) 54mm Male - 42mm Female","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"REDUCER(ADAPTER TYPE) 28mm Male - 42mm Female","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"REDUCER(ADAPTER TYPE) 36mm Male - 28mm Female","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"REDUCER(ADAPTER TYPE) 42mm Male - 36mm Female","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"Lock Nut 28mm (1\")","qty":800,"unit":"EA","remaining":800,"log":[]},{"name":"Lock Nut 36mm (1-1/4\")","qty":200,"unit":"EA","remaining":200,"log":[]},{"name":"Lock Nut 42mm (1-1/2\")","qty":100,"unit":"EA","remaining":100,"log":[]},{"name":"Lock Nut 54mm (2\")","qty":50,"unit":"EA","remaining":50,"log":[]},{"name":"Lock Nut 82mm (3\")","qty":160,"unit":"EA","remaining":160,"log":[]},{"name":"Lock Nut 104mm (4\")","qty":100,"unit":"EA","remaining":100,"log":[]},{"name":"Lock Nut 125mm (5\")","qty":120,"unit":"EA","remaining":120,"log":[]},{"name":"Flexible Conduit (Water proof type) 36mm (1-1/4\")","qty":330,"unit":"M","remaining":330,"log":[]}]</v>
+        <v>[{"name":"Condulet (\"LT\" Type) 28mm (1\")","qty":30,"unit":"EA","remaining":28,"log":[{"time":"22:32:22 18/8/2026","change":1,"after":28},{"time":"22:31:58 18/8/2026","change":1,"after":27},{"time":"22:31:54 18/8/2026","change":1,"after":26},{"time":"22:31:49 18/8/2026","change":1,"after":25},{"time":"22:31:43 18/8/2026","change":-1,"after":24},{"time":"22:31:13 18/8/2026","change":-1,"after":25},{"time":"22:31:05 18/8/2026","change":-1,"after":26},{"time":"22:31:00 18/8/2026","change":-1,"after":27},{"time":"22:30:47 18/8/2026","change":-1,"after":28},{"time":"22:30:41 18/8/2026","change":-1,"after":29}]},{"name":"Condulet (\"LT\" Type) 36mm (1-1/4\")","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"Condulet (\"LT\" Type) 42mm (1-1/2\")","qty":10,"unit":"EA","remaining":10,"log":[]},{"name":"Condulet (\"LT\" Type) 54mm (2\")","qty":15,"unit":"EA","remaining":15,"log":[]},{"name":"Condulet (\"LT\" Type) 82mm (3\")","qty":15,"unit":"EA","remaining":15,"log":[]},{"name":"Condulet (\"LT\" Type) 104mm (4\")","qty":10,"unit":"EA","remaining":10,"log":[]},{"name":"Flexible Conduit Connector (Male Type) 28mm (1\")","qty":420,"unit":"EA","remaining":420,"log":[]},{"name":"Flexible Conduit Connector (Male Type) 36mm (1-1/4\")","qty":150,"unit":"EA","remaining":150,"log":[]},{"name":"Flexible Conduit Connector (Male Type) 42mm (1-1/2\")","qty":50,"unit":"EA","remaining":50,"log":[]},{"name":"Flexible Conduit Connector (Male Type) 54mm (2\")","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"Flexible Conduit Connector (Male Type) 82mm (3\")","qty":80,"unit":"EA","remaining":80,"log":[]},{"name":"Flexible Conduit Connector (Male Type) 104mm (4\")","qty":50,"unit":"EA","remaining":50,"log":[]},{"name":"Flexible Conduit Connector (Female Type) 28mm (1\")","qty":420,"unit":"EA","remaining":420,"log":[]},{"name":"Flexible Conduit Connector (Female Type) 36mm (1-1/4\")","qty":150,"unit":"EA","remaining":150,"log":[]},{"name":"Flexible Conduit Connector (Female Type) 42mm (1-1/2\")","qty":50,"unit":"EA","remaining":50,"log":[]},{"name":"Flexible Conduit Connector (Female Type) 54mm (2\")","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"Flexible Conduit Connector (Female Type) 82mm (3\")","qty":80,"unit":"EA","remaining":80,"log":[]},{"name":"Flexible Conduit Connector (Female Type) 104mm (4\")","qty":50,"unit":"EA","remaining":50,"log":[]},{"name":"Union Coupling (Male Type) 28mm (1\")","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"Union Coupling (Male Type) 36mm (1-1/4\")","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"Union Coupling (Male Type) 42mm (1-1/2\")","qty":10,"unit":"EA","remaining":10,"log":[]},{"name":"Union Coupling (Male Type) 54mm (2\")","qty":10,"unit":"EA","remaining":10,"log":[]},{"name":"Union Coupling (Male Type) 82mm (3\")","qty":10,"unit":"EA","remaining":10,"log":[]},{"name":"Nipple(EXPLOSION TYPE, NPT to PF) 28mm (1\")","qty":10,"unit":"EA","remaining":10,"log":[]},{"name":"Nipple(EXPLOSION TYPE, NPT to PF) 36mm (1-1/4\")","qty":5,"unit":"EA","remaining":5,"log":[]},{"name":"Nipple(EXPLOSION TYPE, NPT to PF) 42mm (1-1/2\")","qty":5,"unit":"EA","remaining":5,"log":[]},{"name":"Nipple(EXPLOSION TYPE, NPT to PF) 54mm (2\")","qty":5,"unit":"EA","remaining":5,"log":[]},{"name":"SEALING COMPOUND Plaster FOR SEALING FITTING 1KG/CAN","qty":50,"unit":"EA","remaining":50,"log":[]},{"name":"REDUCER(ADAPTER TYPE) 36mm Male - 28mm Female","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"REDUCER(ADAPTER TYPE) 36mm Male - 28mm Female","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"REDUCER(ADAPTER TYPE) 42mm Male - 28mm Female","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"REDUCER(ADAPTER TYPE) 54mm Male - 28mm Female","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"REDUCER(ADAPTER TYPE) 54mm Male - 42mm Female","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"REDUCER(ADAPTER TYPE) 28mm Male - 42mm Female","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"REDUCER(ADAPTER TYPE) 36mm Male - 28mm Female","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"REDUCER(ADAPTER TYPE) 42mm Male - 36mm Female","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"Lock Nut 28mm (1\")","qty":800,"unit":"EA","remaining":800,"log":[]},{"name":"Lock Nut 36mm (1-1/4\")","qty":200,"unit":"EA","remaining":200,"log":[]},{"name":"Lock Nut 42mm (1-1/2\")","qty":100,"unit":"EA","remaining":100,"log":[]},{"name":"Lock Nut 54mm (2\")","qty":50,"unit":"EA","remaining":50,"log":[]},{"name":"Lock Nut 82mm (3\")","qty":160,"unit":"EA","remaining":160,"log":[]},{"name":"Lock Nut 104mm (4\")","qty":100,"unit":"EA","remaining":100,"log":[]},{"name":"Lock Nut 125mm (5\")","qty":120,"unit":"EA","remaining":120,"log":[]},{"name":"Flexible Conduit (Water proof type) 36mm (1-1/4\")","qty":330,"unit":"M","remaining":330,"log":[]}]</v>
       </c>
     </row>
   </sheetData>

--- a/du-lieu/chinh-sua-tay.xlsx
+++ b/du-lieu/chinh-sua-tay.xlsx
@@ -732,7 +732,7 @@
         <v/>
       </c>
       <c r="Z4" t="str">
-        <v>[{"name":"Condulet (\"LT\" Type) 28mm (1\")","qty":30,"unit":"EA","remaining":28,"log":[{"time":"22:32:22 18/8/2026","change":1,"after":28},{"time":"22:31:58 18/8/2026","change":1,"after":27},{"time":"22:31:54 18/8/2026","change":1,"after":26},{"time":"22:31:49 18/8/2026","change":1,"after":25},{"time":"22:31:43 18/8/2026","change":-1,"after":24},{"time":"22:31:13 18/8/2026","change":-1,"after":25},{"time":"22:31:05 18/8/2026","change":-1,"after":26},{"time":"22:31:00 18/8/2026","change":-1,"after":27},{"time":"22:30:47 18/8/2026","change":-1,"after":28},{"time":"22:30:41 18/8/2026","change":-1,"after":29}]},{"name":"Condulet (\"LT\" Type) 36mm (1-1/4\")","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"Condulet (\"LT\" Type) 42mm (1-1/2\")","qty":10,"unit":"EA","remaining":10,"log":[]},{"name":"Condulet (\"LT\" Type) 54mm (2\")","qty":15,"unit":"EA","remaining":15,"log":[]},{"name":"Condulet (\"LT\" Type) 82mm (3\")","qty":15,"unit":"EA","remaining":15,"log":[]},{"name":"Condulet (\"LT\" Type) 104mm (4\")","qty":10,"unit":"EA","remaining":10,"log":[]},{"name":"Flexible Conduit Connector (Male Type) 28mm (1\")","qty":420,"unit":"EA","remaining":420,"log":[]},{"name":"Flexible Conduit Connector (Male Type) 36mm (1-1/4\")","qty":150,"unit":"EA","remaining":150,"log":[]},{"name":"Flexible Conduit Connector (Male Type) 42mm (1-1/2\")","qty":50,"unit":"EA","remaining":50,"log":[]},{"name":"Flexible Conduit Connector (Male Type) 54mm (2\")","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"Flexible Conduit Connector (Male Type) 82mm (3\")","qty":80,"unit":"EA","remaining":80,"log":[]},{"name":"Flexible Conduit Connector (Male Type) 104mm (4\")","qty":50,"unit":"EA","remaining":50,"log":[]},{"name":"Flexible Conduit Connector (Female Type) 28mm (1\")","qty":420,"unit":"EA","remaining":420,"log":[]},{"name":"Flexible Conduit Connector (Female Type) 36mm (1-1/4\")","qty":150,"unit":"EA","remaining":150,"log":[]},{"name":"Flexible Conduit Connector (Female Type) 42mm (1-1/2\")","qty":50,"unit":"EA","remaining":50,"log":[]},{"name":"Flexible Conduit Connector (Female Type) 54mm (2\")","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"Flexible Conduit Connector (Female Type) 82mm (3\")","qty":80,"unit":"EA","remaining":80,"log":[]},{"name":"Flexible Conduit Connector (Female Type) 104mm (4\")","qty":50,"unit":"EA","remaining":50,"log":[]},{"name":"Union Coupling (Male Type) 28mm (1\")","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"Union Coupling (Male Type) 36mm (1-1/4\")","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"Union Coupling (Male Type) 42mm (1-1/2\")","qty":10,"unit":"EA","remaining":10,"log":[]},{"name":"Union Coupling (Male Type) 54mm (2\")","qty":10,"unit":"EA","remaining":10,"log":[]},{"name":"Union Coupling (Male Type) 82mm (3\")","qty":10,"unit":"EA","remaining":10,"log":[]},{"name":"Nipple(EXPLOSION TYPE, NPT to PF) 28mm (1\")","qty":10,"unit":"EA","remaining":10,"log":[]},{"name":"Nipple(EXPLOSION TYPE, NPT to PF) 36mm (1-1/4\")","qty":5,"unit":"EA","remaining":5,"log":[]},{"name":"Nipple(EXPLOSION TYPE, NPT to PF) 42mm (1-1/2\")","qty":5,"unit":"EA","remaining":5,"log":[]},{"name":"Nipple(EXPLOSION TYPE, NPT to PF) 54mm (2\")","qty":5,"unit":"EA","remaining":5,"log":[]},{"name":"SEALING COMPOUND Plaster FOR SEALING FITTING 1KG/CAN","qty":50,"unit":"EA","remaining":50,"log":[]},{"name":"REDUCER(ADAPTER TYPE) 36mm Male - 28mm Female","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"REDUCER(ADAPTER TYPE) 36mm Male - 28mm Female","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"REDUCER(ADAPTER TYPE) 42mm Male - 28mm Female","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"REDUCER(ADAPTER TYPE) 54mm Male - 28mm Female","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"REDUCER(ADAPTER TYPE) 54mm Male - 42mm Female","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"REDUCER(ADAPTER TYPE) 28mm Male - 42mm Female","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"REDUCER(ADAPTER TYPE) 36mm Male - 28mm Female","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"REDUCER(ADAPTER TYPE) 42mm Male - 36mm Female","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"Lock Nut 28mm (1\")","qty":800,"unit":"EA","remaining":800,"log":[]},{"name":"Lock Nut 36mm (1-1/4\")","qty":200,"unit":"EA","remaining":200,"log":[]},{"name":"Lock Nut 42mm (1-1/2\")","qty":100,"unit":"EA","remaining":100,"log":[]},{"name":"Lock Nut 54mm (2\")","qty":50,"unit":"EA","remaining":50,"log":[]},{"name":"Lock Nut 82mm (3\")","qty":160,"unit":"EA","remaining":160,"log":[]},{"name":"Lock Nut 104mm (4\")","qty":100,"unit":"EA","remaining":100,"log":[]},{"name":"Lock Nut 125mm (5\")","qty":120,"unit":"EA","remaining":120,"log":[]},{"name":"Flexible Conduit (Water proof type) 36mm (1-1/4\")","qty":330,"unit":"M","remaining":330,"log":[]}]</v>
+        <v>[{"name":"Condulet (\"LT\" Type) 28mm (1\")","qty":30,"unit":"EA","remaining":29,"log":[{"time":"22:32:36 18/8/2026","change":1,"after":29},{"time":"22:32:22 18/8/2026","change":1,"after":28},{"time":"22:31:58 18/8/2026","change":1,"after":27},{"time":"22:31:54 18/8/2026","change":1,"after":26},{"time":"22:31:49 18/8/2026","change":1,"after":25},{"time":"22:31:43 18/8/2026","change":-1,"after":24},{"time":"22:31:13 18/8/2026","change":-1,"after":25},{"time":"22:31:05 18/8/2026","change":-1,"after":26},{"time":"22:31:00 18/8/2026","change":-1,"after":27},{"time":"22:30:47 18/8/2026","change":-1,"after":28},{"time":"22:30:41 18/8/2026","change":-1,"after":29}]},{"name":"Condulet (\"LT\" Type) 36mm (1-1/4\")","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"Condulet (\"LT\" Type) 42mm (1-1/2\")","qty":10,"unit":"EA","remaining":10,"log":[]},{"name":"Condulet (\"LT\" Type) 54mm (2\")","qty":15,"unit":"EA","remaining":15,"log":[]},{"name":"Condulet (\"LT\" Type) 82mm (3\")","qty":15,"unit":"EA","remaining":15,"log":[]},{"name":"Condulet (\"LT\" Type) 104mm (4\")","qty":10,"unit":"EA","remaining":10,"log":[]},{"name":"Flexible Conduit Connector (Male Type) 28mm (1\")","qty":420,"unit":"EA","remaining":420,"log":[]},{"name":"Flexible Conduit Connector (Male Type) 36mm (1-1/4\")","qty":150,"unit":"EA","remaining":150,"log":[]},{"name":"Flexible Conduit Connector (Male Type) 42mm (1-1/2\")","qty":50,"unit":"EA","remaining":50,"log":[]},{"name":"Flexible Conduit Connector (Male Type) 54mm (2\")","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"Flexible Conduit Connector (Male Type) 82mm (3\")","qty":80,"unit":"EA","remaining":80,"log":[]},{"name":"Flexible Conduit Connector (Male Type) 104mm (4\")","qty":50,"unit":"EA","remaining":50,"log":[]},{"name":"Flexible Conduit Connector (Female Type) 28mm (1\")","qty":420,"unit":"EA","remaining":420,"log":[]},{"name":"Flexible Conduit Connector (Female Type) 36mm (1-1/4\")","qty":150,"unit":"EA","remaining":150,"log":[]},{"name":"Flexible Conduit Connector (Female Type) 42mm (1-1/2\")","qty":50,"unit":"EA","remaining":50,"log":[]},{"name":"Flexible Conduit Connector (Female Type) 54mm (2\")","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"Flexible Conduit Connector (Female Type) 82mm (3\")","qty":80,"unit":"EA","remaining":80,"log":[]},{"name":"Flexible Conduit Connector (Female Type) 104mm (4\")","qty":50,"unit":"EA","remaining":50,"log":[]},{"name":"Union Coupling (Male Type) 28mm (1\")","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"Union Coupling (Male Type) 36mm (1-1/4\")","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"Union Coupling (Male Type) 42mm (1-1/2\")","qty":10,"unit":"EA","remaining":10,"log":[]},{"name":"Union Coupling (Male Type) 54mm (2\")","qty":10,"unit":"EA","remaining":10,"log":[]},{"name":"Union Coupling (Male Type) 82mm (3\")","qty":10,"unit":"EA","remaining":10,"log":[]},{"name":"Nipple(EXPLOSION TYPE, NPT to PF) 28mm (1\")","qty":10,"unit":"EA","remaining":10,"log":[]},{"name":"Nipple(EXPLOSION TYPE, NPT to PF) 36mm (1-1/4\")","qty":5,"unit":"EA","remaining":5,"log":[]},{"name":"Nipple(EXPLOSION TYPE, NPT to PF) 42mm (1-1/2\")","qty":5,"unit":"EA","remaining":5,"log":[]},{"name":"Nipple(EXPLOSION TYPE, NPT to PF) 54mm (2\")","qty":5,"unit":"EA","remaining":5,"log":[]},{"name":"SEALING COMPOUND Plaster FOR SEALING FITTING 1KG/CAN","qty":50,"unit":"EA","remaining":50,"log":[]},{"name":"REDUCER(ADAPTER TYPE) 36mm Male - 28mm Female","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"REDUCER(ADAPTER TYPE) 36mm Male - 28mm Female","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"REDUCER(ADAPTER TYPE) 42mm Male - 28mm Female","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"REDUCER(ADAPTER TYPE) 54mm Male - 28mm Female","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"REDUCER(ADAPTER TYPE) 54mm Male - 42mm Female","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"REDUCER(ADAPTER TYPE) 28mm Male - 42mm Female","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"REDUCER(ADAPTER TYPE) 36mm Male - 28mm Female","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"REDUCER(ADAPTER TYPE) 42mm Male - 36mm Female","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"Lock Nut 28mm (1\")","qty":800,"unit":"EA","remaining":800,"log":[]},{"name":"Lock Nut 36mm (1-1/4\")","qty":200,"unit":"EA","remaining":200,"log":[]},{"name":"Lock Nut 42mm (1-1/2\")","qty":100,"unit":"EA","remaining":100,"log":[]},{"name":"Lock Nut 54mm (2\")","qty":50,"unit":"EA","remaining":50,"log":[]},{"name":"Lock Nut 82mm (3\")","qty":160,"unit":"EA","remaining":160,"log":[]},{"name":"Lock Nut 104mm (4\")","qty":100,"unit":"EA","remaining":100,"log":[]},{"name":"Lock Nut 125mm (5\")","qty":120,"unit":"EA","remaining":120,"log":[]},{"name":"Flexible Conduit (Water proof type) 36mm (1-1/4\")","qty":330,"unit":"M","remaining":330,"log":[]}]</v>
       </c>
     </row>
   </sheetData>

--- a/du-lieu/chinh-sua-tay.xlsx
+++ b/du-lieu/chinh-sua-tay.xlsx
@@ -732,7 +732,7 @@
         <v/>
       </c>
       <c r="Z4" t="str">
-        <v>[{"name":"Condulet (\"LT\" Type) 28mm (1\")","qty":30,"unit":"EA","remaining":29,"log":[{"time":"22:32:36 18/8/2026","change":1,"after":29},{"time":"22:32:22 18/8/2026","change":1,"after":28},{"time":"22:31:58 18/8/2026","change":1,"after":27},{"time":"22:31:54 18/8/2026","change":1,"after":26},{"time":"22:31:49 18/8/2026","change":1,"after":25},{"time":"22:31:43 18/8/2026","change":-1,"after":24},{"time":"22:31:13 18/8/2026","change":-1,"after":25},{"time":"22:31:05 18/8/2026","change":-1,"after":26},{"time":"22:31:00 18/8/2026","change":-1,"after":27},{"time":"22:30:47 18/8/2026","change":-1,"after":28},{"time":"22:30:41 18/8/2026","change":-1,"after":29}]},{"name":"Condulet (\"LT\" Type) 36mm (1-1/4\")","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"Condulet (\"LT\" Type) 42mm (1-1/2\")","qty":10,"unit":"EA","remaining":10,"log":[]},{"name":"Condulet (\"LT\" Type) 54mm (2\")","qty":15,"unit":"EA","remaining":15,"log":[]},{"name":"Condulet (\"LT\" Type) 82mm (3\")","qty":15,"unit":"EA","remaining":15,"log":[]},{"name":"Condulet (\"LT\" Type) 104mm (4\")","qty":10,"unit":"EA","remaining":10,"log":[]},{"name":"Flexible Conduit Connector (Male Type) 28mm (1\")","qty":420,"unit":"EA","remaining":420,"log":[]},{"name":"Flexible Conduit Connector (Male Type) 36mm (1-1/4\")","qty":150,"unit":"EA","remaining":150,"log":[]},{"name":"Flexible Conduit Connector (Male Type) 42mm (1-1/2\")","qty":50,"unit":"EA","remaining":50,"log":[]},{"name":"Flexible Conduit Connector (Male Type) 54mm (2\")","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"Flexible Conduit Connector (Male Type) 82mm (3\")","qty":80,"unit":"EA","remaining":80,"log":[]},{"name":"Flexible Conduit Connector (Male Type) 104mm (4\")","qty":50,"unit":"EA","remaining":50,"log":[]},{"name":"Flexible Conduit Connector (Female Type) 28mm (1\")","qty":420,"unit":"EA","remaining":420,"log":[]},{"name":"Flexible Conduit Connector (Female Type) 36mm (1-1/4\")","qty":150,"unit":"EA","remaining":150,"log":[]},{"name":"Flexible Conduit Connector (Female Type) 42mm (1-1/2\")","qty":50,"unit":"EA","remaining":50,"log":[]},{"name":"Flexible Conduit Connector (Female Type) 54mm (2\")","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"Flexible Conduit Connector (Female Type) 82mm (3\")","qty":80,"unit":"EA","remaining":80,"log":[]},{"name":"Flexible Conduit Connector (Female Type) 104mm (4\")","qty":50,"unit":"EA","remaining":50,"log":[]},{"name":"Union Coupling (Male Type) 28mm (1\")","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"Union Coupling (Male Type) 36mm (1-1/4\")","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"Union Coupling (Male Type) 42mm (1-1/2\")","qty":10,"unit":"EA","remaining":10,"log":[]},{"name":"Union Coupling (Male Type) 54mm (2\")","qty":10,"unit":"EA","remaining":10,"log":[]},{"name":"Union Coupling (Male Type) 82mm (3\")","qty":10,"unit":"EA","remaining":10,"log":[]},{"name":"Nipple(EXPLOSION TYPE, NPT to PF) 28mm (1\")","qty":10,"unit":"EA","remaining":10,"log":[]},{"name":"Nipple(EXPLOSION TYPE, NPT to PF) 36mm (1-1/4\")","qty":5,"unit":"EA","remaining":5,"log":[]},{"name":"Nipple(EXPLOSION TYPE, NPT to PF) 42mm (1-1/2\")","qty":5,"unit":"EA","remaining":5,"log":[]},{"name":"Nipple(EXPLOSION TYPE, NPT to PF) 54mm (2\")","qty":5,"unit":"EA","remaining":5,"log":[]},{"name":"SEALING COMPOUND Plaster FOR SEALING FITTING 1KG/CAN","qty":50,"unit":"EA","remaining":50,"log":[]},{"name":"REDUCER(ADAPTER TYPE) 36mm Male - 28mm Female","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"REDUCER(ADAPTER TYPE) 36mm Male - 28mm Female","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"REDUCER(ADAPTER TYPE) 42mm Male - 28mm Female","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"REDUCER(ADAPTER TYPE) 54mm Male - 28mm Female","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"REDUCER(ADAPTER TYPE) 54mm Male - 42mm Female","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"REDUCER(ADAPTER TYPE) 28mm Male - 42mm Female","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"REDUCER(ADAPTER TYPE) 36mm Male - 28mm Female","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"REDUCER(ADAPTER TYPE) 42mm Male - 36mm Female","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"Lock Nut 28mm (1\")","qty":800,"unit":"EA","remaining":800,"log":[]},{"name":"Lock Nut 36mm (1-1/4\")","qty":200,"unit":"EA","remaining":200,"log":[]},{"name":"Lock Nut 42mm (1-1/2\")","qty":100,"unit":"EA","remaining":100,"log":[]},{"name":"Lock Nut 54mm (2\")","qty":50,"unit":"EA","remaining":50,"log":[]},{"name":"Lock Nut 82mm (3\")","qty":160,"unit":"EA","remaining":160,"log":[]},{"name":"Lock Nut 104mm (4\")","qty":100,"unit":"EA","remaining":100,"log":[]},{"name":"Lock Nut 125mm (5\")","qty":120,"unit":"EA","remaining":120,"log":[]},{"name":"Flexible Conduit (Water proof type) 36mm (1-1/4\")","qty":330,"unit":"M","remaining":330,"log":[]}]</v>
+        <v>[{"name":"Condulet (\"LT\" Type) 28mm (1\")","qty":30,"unit":"EA","remaining":30,"log":[{"time":"22:32:42 18/8/2026","change":1,"after":30},{"time":"22:32:36 18/8/2026","change":1,"after":29},{"time":"22:32:22 18/8/2026","change":1,"after":28},{"time":"22:31:58 18/8/2026","change":1,"after":27},{"time":"22:31:54 18/8/2026","change":1,"after":26},{"time":"22:31:49 18/8/2026","change":1,"after":25},{"time":"22:31:43 18/8/2026","change":-1,"after":24},{"time":"22:31:13 18/8/2026","change":-1,"after":25},{"time":"22:31:05 18/8/2026","change":-1,"after":26},{"time":"22:31:00 18/8/2026","change":-1,"after":27},{"time":"22:30:47 18/8/2026","change":-1,"after":28},{"time":"22:30:41 18/8/2026","change":-1,"after":29}]},{"name":"Condulet (\"LT\" Type) 36mm (1-1/4\")","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"Condulet (\"LT\" Type) 42mm (1-1/2\")","qty":10,"unit":"EA","remaining":10,"log":[]},{"name":"Condulet (\"LT\" Type) 54mm (2\")","qty":15,"unit":"EA","remaining":15,"log":[]},{"name":"Condulet (\"LT\" Type) 82mm (3\")","qty":15,"unit":"EA","remaining":15,"log":[]},{"name":"Condulet (\"LT\" Type) 104mm (4\")","qty":10,"unit":"EA","remaining":10,"log":[]},{"name":"Flexible Conduit Connector (Male Type) 28mm (1\")","qty":420,"unit":"EA","remaining":420,"log":[]},{"name":"Flexible Conduit Connector (Male Type) 36mm (1-1/4\")","qty":150,"unit":"EA","remaining":150,"log":[]},{"name":"Flexible Conduit Connector (Male Type) 42mm (1-1/2\")","qty":50,"unit":"EA","remaining":50,"log":[]},{"name":"Flexible Conduit Connector (Male Type) 54mm (2\")","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"Flexible Conduit Connector (Male Type) 82mm (3\")","qty":80,"unit":"EA","remaining":80,"log":[]},{"name":"Flexible Conduit Connector (Male Type) 104mm (4\")","qty":50,"unit":"EA","remaining":50,"log":[]},{"name":"Flexible Conduit Connector (Female Type) 28mm (1\")","qty":420,"unit":"EA","remaining":420,"log":[]},{"name":"Flexible Conduit Connector (Female Type) 36mm (1-1/4\")","qty":150,"unit":"EA","remaining":150,"log":[]},{"name":"Flexible Conduit Connector (Female Type) 42mm (1-1/2\")","qty":50,"unit":"EA","remaining":50,"log":[]},{"name":"Flexible Conduit Connector (Female Type) 54mm (2\")","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"Flexible Conduit Connector (Female Type) 82mm (3\")","qty":80,"unit":"EA","remaining":80,"log":[]},{"name":"Flexible Conduit Connector (Female Type) 104mm (4\")","qty":50,"unit":"EA","remaining":50,"log":[]},{"name":"Union Coupling (Male Type) 28mm (1\")","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"Union Coupling (Male Type) 36mm (1-1/4\")","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"Union Coupling (Male Type) 42mm (1-1/2\")","qty":10,"unit":"EA","remaining":10,"log":[]},{"name":"Union Coupling (Male Type) 54mm (2\")","qty":10,"unit":"EA","remaining":10,"log":[]},{"name":"Union Coupling (Male Type) 82mm (3\")","qty":10,"unit":"EA","remaining":10,"log":[]},{"name":"Nipple(EXPLOSION TYPE, NPT to PF) 28mm (1\")","qty":10,"unit":"EA","remaining":10,"log":[]},{"name":"Nipple(EXPLOSION TYPE, NPT to PF) 36mm (1-1/4\")","qty":5,"unit":"EA","remaining":5,"log":[]},{"name":"Nipple(EXPLOSION TYPE, NPT to PF) 42mm (1-1/2\")","qty":5,"unit":"EA","remaining":5,"log":[]},{"name":"Nipple(EXPLOSION TYPE, NPT to PF) 54mm (2\")","qty":5,"unit":"EA","remaining":5,"log":[]},{"name":"SEALING COMPOUND Plaster FOR SEALING FITTING 1KG/CAN","qty":50,"unit":"EA","remaining":50,"log":[]},{"name":"REDUCER(ADAPTER TYPE) 36mm Male - 28mm Female","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"REDUCER(ADAPTER TYPE) 36mm Male - 28mm Female","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"REDUCER(ADAPTER TYPE) 42mm Male - 28mm Female","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"REDUCER(ADAPTER TYPE) 54mm Male - 28mm Female","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"REDUCER(ADAPTER TYPE) 54mm Male - 42mm Female","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"REDUCER(ADAPTER TYPE) 28mm Male - 42mm Female","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"REDUCER(ADAPTER TYPE) 36mm Male - 28mm Female","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"REDUCER(ADAPTER TYPE) 42mm Male - 36mm Female","qty":30,"unit":"EA","remaining":30,"log":[]},{"name":"Lock Nut 28mm (1\")","qty":800,"unit":"EA","remaining":800,"log":[]},{"name":"Lock Nut 36mm (1-1/4\")","qty":200,"unit":"EA","remaining":200,"log":[]},{"name":"Lock Nut 42mm (1-1/2\")","qty":100,"unit":"EA","remaining":100,"log":[]},{"name":"Lock Nut 54mm (2\")","qty":50,"unit":"EA","remaining":50,"log":[]},{"name":"Lock Nut 82mm (3\")","qty":160,"unit":"EA","remaining":160,"log":[]},{"name":"Lock Nut 104mm (4\")","qty":100,"unit":"EA","remaining":100,"log":[]},{"name":"Lock Nut 125mm (5\")","qty":120,"unit":"EA","remaining":120,"log":[]},{"name":"Flexible Conduit (Water proof type) 36mm (1-1/4\")","qty":330,"unit":"M","remaining":330,"log":[]}]</v>
       </c>
     </row>
   </sheetData>

--- a/du-lieu/chinh-sua-tay.xlsx
+++ b/du-lieu/chinh-sua-tay.xlsx
@@ -572,7 +572,7 @@
         <v/>
       </c>
       <c r="Z2" t="str">
-        <v>[{"name":"HRSG Embeded Material (Template)","qty":1,"unit":"PKG","remaining":1,"log":[{"time":"21:59:36 18/8/2026","change":1,"after":1},{"time":"21:59:33 18/8/2026","change":-1,"after":0}]},{"name":"TEMPLATE(TP-1)_10T*374*374","qty":20,"unit":"EA","remaining":20,"log":[{"time":"22:09:54 18/8/2026","change":1,"after":20},{"time":"22:00:37 18/8/2026","change":-1,"after":19}]},{"name":"TEMPLATE(TP-2)_10T*450*900","qty":40,"unit":"EA","remaining":40,"log":[]},{"name":"TEMPLATE(TP-3)_10T*270*320","qty":8,"unit":"EA","remaining":8,"log":[]},{"name":"TEMPLATE(STP-1)_15T*250*3801","qty":6,"unit":"EA","remaining":6,"log":[]},{"name":"TEMPLATE(STP-2)_10T*60*250","qty":6,"unit":"EA","remaining":6,"log":[]},{"name":"TEMPLATE(STP-3)_15T*250*3801","qty":6,"unit":"EA","remaining":6,"log":[]},{"name":"TEMPLATE(STP-4)_10T*60*250","qty":6,"unit":"EA","remaining":6,"log":[]}]</v>
+        <v>[{"name":"HRSG Embeded Material (Template)","qty":1,"unit":"PKG","remaining":0,"log":[{"time":"22:36:08 18/8/2026","change":-1,"after":0},{"time":"21:59:36 18/8/2026","change":1,"after":1},{"time":"21:59:33 18/8/2026","change":-1,"after":0}]},{"name":"TEMPLATE(TP-1)_10T*374*374","qty":20,"unit":"EA","remaining":20,"log":[{"time":"22:09:54 18/8/2026","change":1,"after":20},{"time":"22:00:37 18/8/2026","change":-1,"after":19}]},{"name":"TEMPLATE(TP-2)_10T*450*900","qty":40,"unit":"EA","remaining":40,"log":[]},{"name":"TEMPLATE(TP-3)_10T*270*320","qty":8,"unit":"EA","remaining":8,"log":[]},{"name":"TEMPLATE(STP-1)_15T*250*3801","qty":6,"unit":"EA","remaining":6,"log":[]},{"name":"TEMPLATE(STP-2)_10T*60*250","qty":6,"unit":"EA","remaining":6,"log":[]},{"name":"TEMPLATE(STP-3)_15T*250*3801","qty":6,"unit":"EA","remaining":6,"log":[]},{"name":"TEMPLATE(STP-4)_10T*60*250","qty":6,"unit":"EA","remaining":6,"log":[]}]</v>
       </c>
     </row>
     <row r="3">

--- a/du-lieu/chinh-sua-tay.xlsx
+++ b/du-lieu/chinh-sua-tay.xlsx
@@ -572,7 +572,7 @@
         <v/>
       </c>
       <c r="Z2" t="str">
-        <v>[{"name":"HRSG Embeded Material (Template)","qty":1,"unit":"PKG","remaining":0,"log":[{"time":"22:36:08 18/8/2026","change":-1,"after":0},{"time":"21:59:36 18/8/2026","change":1,"after":1},{"time":"21:59:33 18/8/2026","change":-1,"after":0}]},{"name":"TEMPLATE(TP-1)_10T*374*374","qty":20,"unit":"EA","remaining":20,"log":[{"time":"22:09:54 18/8/2026","change":1,"after":20},{"time":"22:00:37 18/8/2026","change":-1,"after":19}]},{"name":"TEMPLATE(TP-2)_10T*450*900","qty":40,"unit":"EA","remaining":40,"log":[]},{"name":"TEMPLATE(TP-3)_10T*270*320","qty":8,"unit":"EA","remaining":8,"log":[]},{"name":"TEMPLATE(STP-1)_15T*250*3801","qty":6,"unit":"EA","remaining":6,"log":[]},{"name":"TEMPLATE(STP-2)_10T*60*250","qty":6,"unit":"EA","remaining":6,"log":[]},{"name":"TEMPLATE(STP-3)_15T*250*3801","qty":6,"unit":"EA","remaining":6,"log":[]},{"name":"TEMPLATE(STP-4)_10T*60*250","qty":6,"unit":"EA","remaining":6,"log":[]}]</v>
+        <v>[{"name":"HRSG Embeded Material (Template)","qty":1,"unit":"PKG","remaining":1,"log":[{"time":"22:36:27 18/8/2026","change":1,"after":1},{"time":"22:36:08 18/8/2026","change":-1,"after":0},{"time":"21:59:36 18/8/2026","change":1,"after":1},{"time":"21:59:33 18/8/2026","change":-1,"after":0}]},{"name":"TEMPLATE(TP-1)_10T*374*374","qty":20,"unit":"EA","remaining":20,"log":[{"time":"22:09:54 18/8/2026","change":1,"after":20},{"time":"22:00:37 18/8/2026","change":-1,"after":19}]},{"name":"TEMPLATE(TP-2)_10T*450*900","qty":40,"unit":"EA","remaining":40,"log":[]},{"name":"TEMPLATE(TP-3)_10T*270*320","qty":8,"unit":"EA","remaining":8,"log":[]},{"name":"TEMPLATE(STP-1)_15T*250*3801","qty":6,"unit":"EA","remaining":6,"log":[]},{"name":"TEMPLATE(STP-2)_10T*60*250","qty":6,"unit":"EA","remaining":6,"log":[]},{"name":"TEMPLATE(STP-3)_15T*250*3801","qty":6,"unit":"EA","remaining":6,"log":[]},{"name":"TEMPLATE(STP-4)_10T*60*250","qty":6,"unit":"EA","remaining":6,"log":[]}]</v>
       </c>
     </row>
     <row r="3">

--- a/du-lieu/chinh-sua-tay.xlsx
+++ b/du-lieu/chinh-sua-tay.xlsx
@@ -572,7 +572,7 @@
         <v/>
       </c>
       <c r="Z2" t="str">
-        <v>[{"name":"HRSG Embeded Material (Template)","qty":1,"unit":"PKG","remaining":1,"log":[{"time":"22:36:27 18/8/2026","change":1,"after":1},{"time":"22:36:08 18/8/2026","change":-1,"after":0},{"time":"21:59:36 18/8/2026","change":1,"after":1},{"time":"21:59:33 18/8/2026","change":-1,"after":0}]},{"name":"TEMPLATE(TP-1)_10T*374*374","qty":20,"unit":"EA","remaining":20,"log":[{"time":"22:09:54 18/8/2026","change":1,"after":20},{"time":"22:00:37 18/8/2026","change":-1,"after":19}]},{"name":"TEMPLATE(TP-2)_10T*450*900","qty":40,"unit":"EA","remaining":40,"log":[]},{"name":"TEMPLATE(TP-3)_10T*270*320","qty":8,"unit":"EA","remaining":8,"log":[]},{"name":"TEMPLATE(STP-1)_15T*250*3801","qty":6,"unit":"EA","remaining":6,"log":[]},{"name":"TEMPLATE(STP-2)_10T*60*250","qty":6,"unit":"EA","remaining":6,"log":[]},{"name":"TEMPLATE(STP-3)_15T*250*3801","qty":6,"unit":"EA","remaining":6,"log":[]},{"name":"TEMPLATE(STP-4)_10T*60*250","qty":6,"unit":"EA","remaining":6,"log":[]}]</v>
+        <v>[{"name":"HRSG Embeded Material (Template)","qty":1,"unit":"PKG","remaining":0,"log":[{"time":"22:36:52 18/8/2026","change":-1,"after":0},{"time":"21:59:36 18/8/2026","change":1,"after":1},{"time":"21:59:33 18/8/2026","change":-1,"after":0}]},{"name":"TEMPLATE(TP-1)_10T*374*374","qty":20,"unit":"EA","remaining":20,"log":[{"time":"22:09:54 18/8/2026","change":1,"after":20},{"time":"22:00:37 18/8/2026","change":-1,"after":19}]},{"name":"TEMPLATE(TP-2)_10T*450*900","qty":40,"unit":"EA","remaining":40,"log":[]},{"name":"TEMPLATE(TP-3)_10T*270*320","qty":8,"unit":"EA","remaining":8,"log":[]},{"name":"TEMPLATE(STP-1)_15T*250*3801","qty":6,"unit":"EA","remaining":6,"log":[]},{"name":"TEMPLATE(STP-2)_10T*60*250","qty":6,"unit":"EA","remaining":6,"log":[]},{"name":"TEMPLATE(STP-3)_15T*250*3801","qty":6,"unit":"EA","remaining":6,"log":[]},{"name":"TEMPLATE(STP-4)_10T*60*250","qty":6,"unit":"EA","remaining":6,"log":[]}]</v>
       </c>
     </row>
     <row r="3">

--- a/du-lieu/chinh-sua-tay.xlsx
+++ b/du-lieu/chinh-sua-tay.xlsx
@@ -572,7 +572,7 @@
         <v/>
       </c>
       <c r="Z2" t="str">
-        <v>[{"name":"HRSG Embeded Material (Template)","qty":1,"unit":"PKG","remaining":0,"log":[{"time":"22:36:52 18/8/2026","change":-1,"after":0},{"time":"21:59:36 18/8/2026","change":1,"after":1},{"time":"21:59:33 18/8/2026","change":-1,"after":0}]},{"name":"TEMPLATE(TP-1)_10T*374*374","qty":20,"unit":"EA","remaining":20,"log":[{"time":"22:09:54 18/8/2026","change":1,"after":20},{"time":"22:00:37 18/8/2026","change":-1,"after":19}]},{"name":"TEMPLATE(TP-2)_10T*450*900","qty":40,"unit":"EA","remaining":40,"log":[]},{"name":"TEMPLATE(TP-3)_10T*270*320","qty":8,"unit":"EA","remaining":8,"log":[]},{"name":"TEMPLATE(STP-1)_15T*250*3801","qty":6,"unit":"EA","remaining":6,"log":[]},{"name":"TEMPLATE(STP-2)_10T*60*250","qty":6,"unit":"EA","remaining":6,"log":[]},{"name":"TEMPLATE(STP-3)_15T*250*3801","qty":6,"unit":"EA","remaining":6,"log":[]},{"name":"TEMPLATE(STP-4)_10T*60*250","qty":6,"unit":"EA","remaining":6,"log":[]}]</v>
+        <v>[{"name":"HRSG Embeded Material (Template)","qty":1,"unit":"PKG","remaining":1,"log":[{"time":"22:36:58 18/8/2026","change":1,"after":1},{"time":"22:36:52 18/8/2026","change":-1,"after":0},{"time":"21:59:36 18/8/2026","change":1,"after":1},{"time":"21:59:33 18/8/2026","change":-1,"after":0}]},{"name":"TEMPLATE(TP-1)_10T*374*374","qty":20,"unit":"EA","remaining":20,"log":[{"time":"22:09:54 18/8/2026","change":1,"after":20},{"time":"22:00:37 18/8/2026","change":-1,"after":19}]},{"name":"TEMPLATE(TP-2)_10T*450*900","qty":40,"unit":"EA","remaining":40,"log":[]},{"name":"TEMPLATE(TP-3)_10T*270*320","qty":8,"unit":"EA","remaining":8,"log":[]},{"name":"TEMPLATE(STP-1)_15T*250*3801","qty":6,"unit":"EA","remaining":6,"log":[]},{"name":"TEMPLATE(STP-2)_10T*60*250","qty":6,"unit":"EA","remaining":6,"log":[]},{"name":"TEMPLATE(STP-3)_15T*250*3801","qty":6,"unit":"EA","remaining":6,"log":[]},{"name":"TEMPLATE(STP-4)_10T*60*250","qty":6,"unit":"EA","remaining":6,"log":[]}]</v>
       </c>
     </row>
     <row r="3">

--- a/du-lieu/chinh-sua-tay.xlsx
+++ b/du-lieu/chinh-sua-tay.xlsx
@@ -572,7 +572,7 @@
         <v/>
       </c>
       <c r="Z2" t="str">
-        <v>[{"name":"HRSG Embeded Material (Template)","qty":1,"unit":"PKG","remaining":1,"log":[{"time":"22:36:58 18/8/2026","change":1,"after":1},{"time":"22:36:52 18/8/2026","change":-1,"after":0},{"time":"21:59:36 18/8/2026","change":1,"after":1},{"time":"21:59:33 18/8/2026","change":-1,"after":0}]},{"name":"TEMPLATE(TP-1)_10T*374*374","qty":20,"unit":"EA","remaining":20,"log":[{"time":"22:09:54 18/8/2026","change":1,"after":20},{"time":"22:00:37 18/8/2026","change":-1,"after":19}]},{"name":"TEMPLATE(TP-2)_10T*450*900","qty":40,"unit":"EA","remaining":40,"log":[]},{"name":"TEMPLATE(TP-3)_10T*270*320","qty":8,"unit":"EA","remaining":8,"log":[]},{"name":"TEMPLATE(STP-1)_15T*250*3801","qty":6,"unit":"EA","remaining":6,"log":[]},{"name":"TEMPLATE(STP-2)_10T*60*250","qty":6,"unit":"EA","remaining":6,"log":[]},{"name":"TEMPLATE(STP-3)_15T*250*3801","qty":6,"unit":"EA","remaining":6,"log":[]},{"name":"TEMPLATE(STP-4)_10T*60*250","qty":6,"unit":"EA","remaining":6,"log":[]}]</v>
+        <v>[{"name":"HRSG Embeded Material (Template)","qty":1,"unit":"PKG","remaining":1,"log":[{"time":"22:36:58 18/8/2026","change":1,"after":1},{"time":"22:36:52 18/8/2026","change":-1,"after":0},{"time":"21:59:36 18/8/2026","change":1,"after":1},{"time":"21:59:33 18/8/2026","change":-1,"after":0}]},{"name":"TEMPLATE(TP-1)_10T*374*374","qty":20,"unit":"EA","remaining":19,"log":[{"time":"22:37:00 18/8/2026","change":-1,"after":19},{"time":"22:09:54 18/8/2026","change":1,"after":20},{"time":"22:00:37 18/8/2026","change":-1,"after":19}]},{"name":"TEMPLATE(TP-2)_10T*450*900","qty":40,"unit":"EA","remaining":40,"log":[]},{"name":"TEMPLATE(TP-3)_10T*270*320","qty":8,"unit":"EA","remaining":8,"log":[]},{"name":"TEMPLATE(STP-1)_15T*250*3801","qty":6,"unit":"EA","remaining":6,"log":[]},{"name":"TEMPLATE(STP-2)_10T*60*250","qty":6,"unit":"EA","remaining":6,"log":[]},{"name":"TEMPLATE(STP-3)_15T*250*3801","qty":6,"unit":"EA","remaining":6,"log":[]},{"name":"TEMPLATE(STP-4)_10T*60*250","qty":6,"unit":"EA","remaining":6,"log":[]}]</v>
       </c>
     </row>
     <row r="3">

--- a/du-lieu/chinh-sua-tay.xlsx
+++ b/du-lieu/chinh-sua-tay.xlsx
@@ -572,7 +572,7 @@
         <v/>
       </c>
       <c r="Z2" t="str">
-        <v>[{"name":"HRSG Embeded Material (Template)","qty":1,"unit":"PKG","remaining":1,"log":[{"time":"22:36:58 18/8/2026","change":1,"after":1},{"time":"22:36:52 18/8/2026","change":-1,"after":0},{"time":"21:59:36 18/8/2026","change":1,"after":1},{"time":"21:59:33 18/8/2026","change":-1,"after":0}]},{"name":"TEMPLATE(TP-1)_10T*374*374","qty":20,"unit":"EA","remaining":19,"log":[{"time":"22:37:00 18/8/2026","change":-1,"after":19},{"time":"22:09:54 18/8/2026","change":1,"after":20},{"time":"22:00:37 18/8/2026","change":-1,"after":19}]},{"name":"TEMPLATE(TP-2)_10T*450*900","qty":40,"unit":"EA","remaining":40,"log":[]},{"name":"TEMPLATE(TP-3)_10T*270*320","qty":8,"unit":"EA","remaining":8,"log":[]},{"name":"TEMPLATE(STP-1)_15T*250*3801","qty":6,"unit":"EA","remaining":6,"log":[]},{"name":"TEMPLATE(STP-2)_10T*60*250","qty":6,"unit":"EA","remaining":6,"log":[]},{"name":"TEMPLATE(STP-3)_15T*250*3801","qty":6,"unit":"EA","remaining":6,"log":[]},{"name":"TEMPLATE(STP-4)_10T*60*250","qty":6,"unit":"EA","remaining":6,"log":[]}]</v>
+        <v>[{"name":"HRSG Embeded Material (Template)","qty":1,"unit":"PKG","remaining":1,"log":[{"time":"22:36:58 18/8/2026","change":1,"after":1},{"time":"22:36:52 18/8/2026","change":-1,"after":0},{"time":"21:59:36 18/8/2026","change":1,"after":1},{"time":"21:59:33 18/8/2026","change":-1,"after":0}]},{"name":"TEMPLATE(TP-1)_10T*374*374","qty":20,"unit":"EA","remaining":20,"log":[{"time":"22:37:08 18/8/2026","change":1,"after":20},{"time":"22:37:00 18/8/2026","change":-1,"after":19},{"time":"22:09:54 18/8/2026","change":1,"after":20},{"time":"22:00:37 18/8/2026","change":-1,"after":19}]},{"name":"TEMPLATE(TP-2)_10T*450*900","qty":40,"unit":"EA","remaining":40,"log":[]},{"name":"TEMPLATE(TP-3)_10T*270*320","qty":8,"unit":"EA","remaining":8,"log":[]},{"name":"TEMPLATE(STP-1)_15T*250*3801","qty":6,"unit":"EA","remaining":6,"log":[]},{"name":"TEMPLATE(STP-2)_10T*60*250","qty":6,"unit":"EA","remaining":6,"log":[]},{"name":"TEMPLATE(STP-3)_15T*250*3801","qty":6,"unit":"EA","remaining":6,"log":[]},{"name":"TEMPLATE(STP-4)_10T*60*250","qty":6,"unit":"EA","remaining":6,"log":[]}]</v>
       </c>
     </row>
     <row r="3">

--- a/du-lieu/chinh-sua-tay.xlsx
+++ b/du-lieu/chinh-sua-tay.xlsx
@@ -572,7 +572,7 @@
         <v/>
       </c>
       <c r="Z2" t="str">
-        <v>[{"name":"HRSG Embeded Material (Template)","qty":1,"unit":"PKG","remaining":1,"log":[{"time":"22:36:58 18/8/2026","change":1,"after":1},{"time":"22:36:52 18/8/2026","change":-1,"after":0},{"time":"21:59:36 18/8/2026","change":1,"after":1},{"time":"21:59:33 18/8/2026","change":-1,"after":0}]},{"name":"TEMPLATE(TP-1)_10T*374*374","qty":20,"unit":"EA","remaining":20,"log":[{"time":"22:37:08 18/8/2026","change":1,"after":20},{"time":"22:37:00 18/8/2026","change":-1,"after":19},{"time":"22:09:54 18/8/2026","change":1,"after":20},{"time":"22:00:37 18/8/2026","change":-1,"after":19}]},{"name":"TEMPLATE(TP-2)_10T*450*900","qty":40,"unit":"EA","remaining":40,"log":[]},{"name":"TEMPLATE(TP-3)_10T*270*320","qty":8,"unit":"EA","remaining":8,"log":[]},{"name":"TEMPLATE(STP-1)_15T*250*3801","qty":6,"unit":"EA","remaining":6,"log":[]},{"name":"TEMPLATE(STP-2)_10T*60*250","qty":6,"unit":"EA","remaining":6,"log":[]},{"name":"TEMPLATE(STP-3)_15T*250*3801","qty":6,"unit":"EA","remaining":6,"log":[]},{"name":"TEMPLATE(STP-4)_10T*60*250","qty":6,"unit":"EA","remaining":6,"log":[]}]</v>
+        <v>[{"name":"HRSG Embeded Material (Template)","qty":1,"unit":"PKG","remaining":1,"log":[{"time":"22:36:58 18/8/2026","change":1,"after":1},{"time":"22:36:52 18/8/2026","change":-1,"after":0},{"time":"21:59:36 18/8/2026","change":1,"after":1},{"time":"21:59:33 18/8/2026","change":-1,"after":0}]},{"name":"TEMPLATE(TP-1)_10T*374*374","qty":20,"unit":"EA","remaining":19,"log":[{"time":"22:41:44 18/8/2026","change":-1,"after":19},{"time":"22:37:08 18/8/2026","change":1,"after":20},{"time":"22:37:00 18/8/2026","change":-1,"after":19},{"time":"22:09:54 18/8/2026","change":1,"after":20},{"time":"22:00:37 18/8/2026","change":-1,"after":19}]},{"name":"TEMPLATE(TP-2)_10T*450*900","qty":40,"unit":"EA","remaining":40,"log":[]},{"name":"TEMPLATE(TP-3)_10T*270*320","qty":8,"unit":"EA","remaining":8,"log":[]},{"name":"TEMPLATE(STP-1)_15T*250*3801","qty":6,"unit":"EA","remaining":6,"log":[]},{"name":"TEMPLATE(STP-2)_10T*60*250","qty":6,"unit":"EA","remaining":6,"log":[]},{"name":"TEMPLATE(STP-3)_15T*250*3801","qty":6,"unit":"EA","remaining":6,"log":[]},{"name":"TEMPLATE(STP-4)_10T*60*250","qty":6,"unit":"EA","remaining":6,"log":[]}]</v>
       </c>
     </row>
     <row r="3">

--- a/du-lieu/chinh-sua-tay.xlsx
+++ b/du-lieu/chinh-sua-tay.xlsx
@@ -572,7 +572,7 @@
         <v/>
       </c>
       <c r="Z2" t="str">
-        <v>[{"name":"HRSG Embeded Material (Template)","qty":1,"unit":"PKG","remaining":1,"log":[{"time":"22:36:58 18/8/2026","change":1,"after":1},{"time":"22:36:52 18/8/2026","change":-1,"after":0},{"time":"21:59:36 18/8/2026","change":1,"after":1},{"time":"21:59:33 18/8/2026","change":-1,"after":0}]},{"name":"TEMPLATE(TP-1)_10T*374*374","qty":20,"unit":"EA","remaining":19,"log":[{"time":"22:41:44 18/8/2026","change":-1,"after":19},{"time":"22:37:08 18/8/2026","change":1,"after":20},{"time":"22:37:00 18/8/2026","change":-1,"after":19},{"time":"22:09:54 18/8/2026","change":1,"after":20},{"time":"22:00:37 18/8/2026","change":-1,"after":19}]},{"name":"TEMPLATE(TP-2)_10T*450*900","qty":40,"unit":"EA","remaining":40,"log":[]},{"name":"TEMPLATE(TP-3)_10T*270*320","qty":8,"unit":"EA","remaining":8,"log":[]},{"name":"TEMPLATE(STP-1)_15T*250*3801","qty":6,"unit":"EA","remaining":6,"log":[]},{"name":"TEMPLATE(STP-2)_10T*60*250","qty":6,"unit":"EA","remaining":6,"log":[]},{"name":"TEMPLATE(STP-3)_15T*250*3801","qty":6,"unit":"EA","remaining":6,"log":[]},{"name":"TEMPLATE(STP-4)_10T*60*250","qty":6,"unit":"EA","remaining":6,"log":[]}]</v>
+        <v>[{"name":"HRSG Embeded Material (Template)","qty":1,"unit":"PKG","remaining":1,"log":[{"time":"22:36:58 18/8/2026","change":1,"after":1},{"time":"22:36:52 18/8/2026","change":-1,"after":0},{"time":"21:59:36 18/8/2026","change":1,"after":1},{"time":"21:59:33 18/8/2026","change":-1,"after":0}]},{"name":"TEMPLATE(TP-1)_10T*374*374","qty":20,"unit":"EA","remaining":20,"log":[{"time":"22:42:03 18/8/2026","change":1,"after":20},{"time":"22:41:44 18/8/2026","change":-1,"after":19},{"time":"22:37:08 18/8/2026","change":1,"after":20},{"time":"22:37:00 18/8/2026","change":-1,"after":19},{"time":"22:09:54 18/8/2026","change":1,"after":20},{"time":"22:00:37 18/8/2026","change":-1,"after":19}]},{"name":"TEMPLATE(TP-2)_10T*450*900","qty":40,"unit":"EA","remaining":40,"log":[]},{"name":"TEMPLATE(TP-3)_10T*270*320","qty":8,"unit":"EA","remaining":8,"log":[]},{"name":"TEMPLATE(STP-1)_15T*250*3801","qty":6,"unit":"EA","remaining":6,"log":[]},{"name":"TEMPLATE(STP-2)_10T*60*250","qty":6,"unit":"EA","remaining":6,"log":[]},{"name":"TEMPLATE(STP-3)_15T*250*3801","qty":6,"unit":"EA","remaining":6,"log":[]},{"name":"TEMPLATE(STP-4)_10T*60*250","qty":6,"unit":"EA","remaining":6,"log":[]}]</v>
       </c>
     </row>
     <row r="3">

--- a/du-lieu/chinh-sua-tay.xlsx
+++ b/du-lieu/chinh-sua-tay.xlsx
@@ -572,7 +572,7 @@
         <v/>
       </c>
       <c r="Z2" t="str">
-        <v>[{"name":"HRSG Embeded Material (Template)","qty":1,"unit":"PKG","remaining":1,"log":[{"time":"22:36:58 18/8/2026","change":1,"after":1},{"time":"22:36:52 18/8/2026","change":-1,"after":0},{"time":"21:59:36 18/8/2026","change":1,"after":1},{"time":"21:59:33 18/8/2026","change":-1,"after":0}]},{"name":"TEMPLATE(TP-1)_10T*374*374","qty":20,"unit":"EA","remaining":20,"log":[{"time":"22:42:03 18/8/2026","change":1,"after":20},{"time":"22:41:44 18/8/2026","change":-1,"after":19},{"time":"22:37:08 18/8/2026","change":1,"after":20},{"time":"22:37:00 18/8/2026","change":-1,"after":19},{"time":"22:09:54 18/8/2026","change":1,"after":20},{"time":"22:00:37 18/8/2026","change":-1,"after":19}]},{"name":"TEMPLATE(TP-2)_10T*450*900","qty":40,"unit":"EA","remaining":40,"log":[]},{"name":"TEMPLATE(TP-3)_10T*270*320","qty":8,"unit":"EA","remaining":8,"log":[]},{"name":"TEMPLATE(STP-1)_15T*250*3801","qty":6,"unit":"EA","remaining":6,"log":[]},{"name":"TEMPLATE(STP-2)_10T*60*250","qty":6,"unit":"EA","remaining":6,"log":[]},{"name":"TEMPLATE(STP-3)_15T*250*3801","qty":6,"unit":"EA","remaining":6,"log":[]},{"name":"TEMPLATE(STP-4)_10T*60*250","qty":6,"unit":"EA","remaining":6,"log":[]}]</v>
+        <v>[{"name":"HRSG Embeded Material (Template)","qty":1,"unit":"PKG","remaining":0,"log":[{"time":"22:43:11 18/8/2026","change":-1,"after":0},{"time":"22:36:58 18/8/2026","change":1,"after":1},{"time":"22:36:52 18/8/2026","change":-1,"after":0},{"time":"21:59:36 18/8/2026","change":1,"after":1},{"time":"21:59:33 18/8/2026","change":-1,"after":0}]},{"name":"TEMPLATE(TP-1)_10T*374*374","qty":20,"unit":"EA","remaining":20,"log":[{"time":"22:42:03 18/8/2026","change":1,"after":20},{"time":"22:41:44 18/8/2026","change":-1,"after":19},{"time":"22:37:08 18/8/2026","change":1,"after":20},{"time":"22:37:00 18/8/2026","change":-1,"after":19},{"time":"22:09:54 18/8/2026","change":1,"after":20},{"time":"22:00:37 18/8/2026","change":-1,"after":19}]},{"name":"TEMPLATE(TP-2)_10T*450*900","qty":40,"unit":"EA","remaining":40,"log":[]},{"name":"TEMPLATE(TP-3)_10T*270*320","qty":8,"unit":"EA","remaining":8,"log":[]},{"name":"TEMPLATE(STP-1)_15T*250*3801","qty":6,"unit":"EA","remaining":6,"log":[]},{"name":"TEMPLATE(STP-2)_10T*60*250","qty":6,"unit":"EA","remaining":6,"log":[]},{"name":"TEMPLATE(STP-3)_15T*250*3801","qty":6,"unit":"EA","remaining":6,"log":[]},{"name":"TEMPLATE(STP-4)_10T*60*250","qty":6,"unit":"EA","remaining":6,"log":[]}]</v>
       </c>
     </row>
     <row r="3">

--- a/du-lieu/chinh-sua-tay.xlsx
+++ b/du-lieu/chinh-sua-tay.xlsx
@@ -572,7 +572,7 @@
         <v/>
       </c>
       <c r="Z2" t="str">
-        <v>[{"name":"HRSG Embeded Material (Template)","qty":1,"unit":"PKG","remaining":0,"log":[{"time":"22:43:11 18/8/2026","change":-1,"after":0},{"time":"22:36:58 18/8/2026","change":1,"after":1},{"time":"22:36:52 18/8/2026","change":-1,"after":0},{"time":"21:59:36 18/8/2026","change":1,"after":1},{"time":"21:59:33 18/8/2026","change":-1,"after":0}]},{"name":"TEMPLATE(TP-1)_10T*374*374","qty":20,"unit":"EA","remaining":20,"log":[{"time":"22:42:03 18/8/2026","change":1,"after":20},{"time":"22:41:44 18/8/2026","change":-1,"after":19},{"time":"22:37:08 18/8/2026","change":1,"after":20},{"time":"22:37:00 18/8/2026","change":-1,"after":19},{"time":"22:09:54 18/8/2026","change":1,"after":20},{"time":"22:00:37 18/8/2026","change":-1,"after":19}]},{"name":"TEMPLATE(TP-2)_10T*450*900","qty":40,"unit":"EA","remaining":40,"log":[]},{"name":"TEMPLATE(TP-3)_10T*270*320","qty":8,"unit":"EA","remaining":8,"log":[]},{"name":"TEMPLATE(STP-1)_15T*250*3801","qty":6,"unit":"EA","remaining":6,"log":[]},{"name":"TEMPLATE(STP-2)_10T*60*250","qty":6,"unit":"EA","remaining":6,"log":[]},{"name":"TEMPLATE(STP-3)_15T*250*3801","qty":6,"unit":"EA","remaining":6,"log":[]},{"name":"TEMPLATE(STP-4)_10T*60*250","qty":6,"unit":"EA","remaining":6,"log":[]}]</v>
+        <v>[{"name":"HRSG Embeded Material (Template)","qty":1,"unit":"PKG","remaining":1,"log":[{"time":"22:43:30 18/8/2026","change":1,"after":1},{"time":"22:43:11 18/8/2026","change":-1,"after":0},{"time":"22:36:58 18/8/2026","change":1,"after":1},{"time":"22:36:52 18/8/2026","change":-1,"after":0},{"time":"21:59:36 18/8/2026","change":1,"after":1},{"time":"21:59:33 18/8/2026","change":-1,"after":0}]},{"name":"TEMPLATE(TP-1)_10T*374*374","qty":20,"unit":"EA","remaining":20,"log":[{"time":"22:42:03 18/8/2026","change":1,"after":20},{"time":"22:41:44 18/8/2026","change":-1,"after":19},{"time":"22:37:08 18/8/2026","change":1,"after":20},{"time":"22:37:00 18/8/2026","change":-1,"after":19},{"time":"22:09:54 18/8/2026","change":1,"after":20},{"time":"22:00:37 18/8/2026","change":-1,"after":19}]},{"name":"TEMPLATE(TP-2)_10T*450*900","qty":40,"unit":"EA","remaining":40,"log":[]},{"name":"TEMPLATE(TP-3)_10T*270*320","qty":8,"unit":"EA","remaining":8,"log":[]},{"name":"TEMPLATE(STP-1)_15T*250*3801","qty":6,"unit":"EA","remaining":6,"log":[]},{"name":"TEMPLATE(STP-2)_10T*60*250","qty":6,"unit":"EA","remaining":6,"log":[]},{"name":"TEMPLATE(STP-3)_15T*250*3801","qty":6,"unit":"EA","remaining":6,"log":[]},{"name":"TEMPLATE(STP-4)_10T*60*250","qty":6,"unit":"EA","remaining":6,"log":[]}]</v>
       </c>
     </row>
     <row r="3">

--- a/du-lieu/chinh-sua-tay.xlsx
+++ b/du-lieu/chinh-sua-tay.xlsx
@@ -572,7 +572,7 @@
         <v/>
       </c>
       <c r="Z2" t="str">
-        <v>[{"name":"HRSG Embeded Material (Template)","qty":1,"unit":"PKG","remaining":1,"log":[{"time":"22:43:30 18/8/2026","change":1,"after":1},{"time":"22:43:11 18/8/2026","change":-1,"after":0},{"time":"22:36:58 18/8/2026","change":1,"after":1},{"time":"22:36:52 18/8/2026","change":-1,"after":0},{"time":"21:59:36 18/8/2026","change":1,"after":1},{"time":"21:59:33 18/8/2026","change":-1,"after":0}]},{"name":"TEMPLATE(TP-1)_10T*374*374","qty":20,"unit":"EA","remaining":20,"log":[{"time":"22:42:03 18/8/2026","change":1,"after":20},{"time":"22:41:44 18/8/2026","change":-1,"after":19},{"time":"22:37:08 18/8/2026","change":1,"after":20},{"time":"22:37:00 18/8/2026","change":-1,"after":19},{"time":"22:09:54 18/8/2026","change":1,"after":20},{"time":"22:00:37 18/8/2026","change":-1,"after":19}]},{"name":"TEMPLATE(TP-2)_10T*450*900","qty":40,"unit":"EA","remaining":40,"log":[]},{"name":"TEMPLATE(TP-3)_10T*270*320","qty":8,"unit":"EA","remaining":8,"log":[]},{"name":"TEMPLATE(STP-1)_15T*250*3801","qty":6,"unit":"EA","remaining":6,"log":[]},{"name":"TEMPLATE(STP-2)_10T*60*250","qty":6,"unit":"EA","remaining":6,"log":[]},{"name":"TEMPLATE(STP-3)_15T*250*3801","qty":6,"unit":"EA","remaining":6,"log":[]},{"name":"TEMPLATE(STP-4)_10T*60*250","qty":6,"unit":"EA","remaining":6,"log":[]}]</v>
+        <v>[{"name":"HRSG Embeded Material (Template)","qty":1,"unit":"PKG","remaining":0,"log":[{"time":"22:43:40 18/8/2026","change":-1,"after":0},{"time":"22:43:30 18/8/2026","change":1,"after":1},{"time":"22:43:11 18/8/2026","change":-1,"after":0},{"time":"22:36:58 18/8/2026","change":1,"after":1},{"time":"22:36:52 18/8/2026","change":-1,"after":0},{"time":"21:59:36 18/8/2026","change":1,"after":1},{"time":"21:59:33 18/8/2026","change":-1,"after":0}]},{"name":"TEMPLATE(TP-1)_10T*374*374","qty":20,"unit":"EA","remaining":20,"log":[{"time":"22:42:03 18/8/2026","change":1,"after":20},{"time":"22:41:44 18/8/2026","change":-1,"after":19},{"time":"22:37:08 18/8/2026","change":1,"after":20},{"time":"22:37:00 18/8/2026","change":-1,"after":19},{"time":"22:09:54 18/8/2026","change":1,"after":20},{"time":"22:00:37 18/8/2026","change":-1,"after":19}]},{"name":"TEMPLATE(TP-2)_10T*450*900","qty":40,"unit":"EA","remaining":40,"log":[]},{"name":"TEMPLATE(TP-3)_10T*270*320","qty":8,"unit":"EA","remaining":8,"log":[]},{"name":"TEMPLATE(STP-1)_15T*250*3801","qty":6,"unit":"EA","remaining":6,"log":[]},{"name":"TEMPLATE(STP-2)_10T*60*250","qty":6,"unit":"EA","remaining":6,"log":[]},{"name":"TEMPLATE(STP-3)_15T*250*3801","qty":6,"unit":"EA","remaining":6,"log":[]},{"name":"TEMPLATE(STP-4)_10T*60*250","qty":6,"unit":"EA","remaining":6,"log":[]}]</v>
       </c>
     </row>
     <row r="3">

--- a/du-lieu/chinh-sua-tay.xlsx
+++ b/du-lieu/chinh-sua-tay.xlsx
@@ -572,7 +572,7 @@
         <v/>
       </c>
       <c r="Z2" t="str">
-        <v>[{"name":"HRSG Embeded Material (Template)","qty":1,"unit":"PKG","remaining":0,"log":[{"time":"22:43:40 18/8/2026","change":-1,"after":0},{"time":"22:43:30 18/8/2026","change":1,"after":1},{"time":"22:43:11 18/8/2026","change":-1,"after":0},{"time":"22:36:58 18/8/2026","change":1,"after":1},{"time":"22:36:52 18/8/2026","change":-1,"after":0},{"time":"21:59:36 18/8/2026","change":1,"after":1},{"time":"21:59:33 18/8/2026","change":-1,"after":0}]},{"name":"TEMPLATE(TP-1)_10T*374*374","qty":20,"unit":"EA","remaining":20,"log":[{"time":"22:42:03 18/8/2026","change":1,"after":20},{"time":"22:41:44 18/8/2026","change":-1,"after":19},{"time":"22:37:08 18/8/2026","change":1,"after":20},{"time":"22:37:00 18/8/2026","change":-1,"after":19},{"time":"22:09:54 18/8/2026","change":1,"after":20},{"time":"22:00:37 18/8/2026","change":-1,"after":19}]},{"name":"TEMPLATE(TP-2)_10T*450*900","qty":40,"unit":"EA","remaining":40,"log":[]},{"name":"TEMPLATE(TP-3)_10T*270*320","qty":8,"unit":"EA","remaining":8,"log":[]},{"name":"TEMPLATE(STP-1)_15T*250*3801","qty":6,"unit":"EA","remaining":6,"log":[]},{"name":"TEMPLATE(STP-2)_10T*60*250","qty":6,"unit":"EA","remaining":6,"log":[]},{"name":"TEMPLATE(STP-3)_15T*250*3801","qty":6,"unit":"EA","remaining":6,"log":[]},{"name":"TEMPLATE(STP-4)_10T*60*250","qty":6,"unit":"EA","remaining":6,"log":[]}]</v>
+        <v>[{"name":"HRSG Embeded Material (Template)","qty":1,"unit":"PKG","remaining":0,"log":[{"time":"22:43:53 18/8/2026","change":-1,"after":0},{"time":"22:36:58 18/8/2026","change":1,"after":1},{"time":"22:36:52 18/8/2026","change":-1,"after":0},{"time":"21:59:36 18/8/2026","change":1,"after":1},{"time":"21:59:33 18/8/2026","change":-1,"after":0}]},{"name":"TEMPLATE(TP-1)_10T*374*374","qty":20,"unit":"EA","remaining":20,"log":[{"time":"22:37:08 18/8/2026","change":1,"after":20},{"time":"22:37:00 18/8/2026","change":-1,"after":19},{"time":"22:09:54 18/8/2026","change":1,"after":20},{"time":"22:00:37 18/8/2026","change":-1,"after":19}]},{"name":"TEMPLATE(TP-2)_10T*450*900","qty":40,"unit":"EA","remaining":40,"log":[]},{"name":"TEMPLATE(TP-3)_10T*270*320","qty":8,"unit":"EA","remaining":8,"log":[]},{"name":"TEMPLATE(STP-1)_15T*250*3801","qty":6,"unit":"EA","remaining":6,"log":[]},{"name":"TEMPLATE(STP-2)_10T*60*250","qty":6,"unit":"EA","remaining":6,"log":[]},{"name":"TEMPLATE(STP-3)_15T*250*3801","qty":6,"unit":"EA","remaining":6,"log":[]},{"name":"TEMPLATE(STP-4)_10T*60*250","qty":6,"unit":"EA","remaining":6,"log":[]}]</v>
       </c>
     </row>
     <row r="3">

--- a/du-lieu/chinh-sua-tay.xlsx
+++ b/du-lieu/chinh-sua-tay.xlsx
@@ -572,7 +572,7 @@
         <v/>
       </c>
       <c r="Z2" t="str">
-        <v>[{"name":"HRSG Embeded Material (Template)","qty":1,"unit":"PKG","remaining":0,"log":[{"time":"22:43:53 18/8/2026","change":-1,"after":0},{"time":"22:36:58 18/8/2026","change":1,"after":1},{"time":"22:36:52 18/8/2026","change":-1,"after":0},{"time":"21:59:36 18/8/2026","change":1,"after":1},{"time":"21:59:33 18/8/2026","change":-1,"after":0}]},{"name":"TEMPLATE(TP-1)_10T*374*374","qty":20,"unit":"EA","remaining":20,"log":[{"time":"22:37:08 18/8/2026","change":1,"after":20},{"time":"22:37:00 18/8/2026","change":-1,"after":19},{"time":"22:09:54 18/8/2026","change":1,"after":20},{"time":"22:00:37 18/8/2026","change":-1,"after":19}]},{"name":"TEMPLATE(TP-2)_10T*450*900","qty":40,"unit":"EA","remaining":40,"log":[]},{"name":"TEMPLATE(TP-3)_10T*270*320","qty":8,"unit":"EA","remaining":8,"log":[]},{"name":"TEMPLATE(STP-1)_15T*250*3801","qty":6,"unit":"EA","remaining":6,"log":[]},{"name":"TEMPLATE(STP-2)_10T*60*250","qty":6,"unit":"EA","remaining":6,"log":[]},{"name":"TEMPLATE(STP-3)_15T*250*3801","qty":6,"unit":"EA","remaining":6,"log":[]},{"name":"TEMPLATE(STP-4)_10T*60*250","qty":6,"unit":"EA","remaining":6,"log":[]}]</v>
+        <v>[{"name":"HRSG Embeded Material (Template)","qty":1,"unit":"PKG","remaining":0,"log":[{"time":"22:45:08 18/8/2026","change":-1,"after":0},{"time":"22:36:58 18/8/2026","change":1,"after":1},{"time":"22:36:52 18/8/2026","change":-1,"after":0},{"time":"21:59:36 18/8/2026","change":1,"after":1},{"time":"21:59:33 18/8/2026","change":-1,"after":0}]},{"name":"TEMPLATE(TP-1)_10T*374*374","qty":20,"unit":"EA","remaining":20,"log":[{"time":"22:37:08 18/8/2026","change":1,"after":20},{"time":"22:37:00 18/8/2026","change":-1,"after":19},{"time":"22:09:54 18/8/2026","change":1,"after":20},{"time":"22:00:37 18/8/2026","change":-1,"after":19}]},{"name":"TEMPLATE(TP-2)_10T*450*900","qty":40,"unit":"EA","remaining":40,"log":[]},{"name":"TEMPLATE(TP-3)_10T*270*320","qty":8,"unit":"EA","remaining":8,"log":[]},{"name":"TEMPLATE(STP-1)_15T*250*3801","qty":6,"unit":"EA","remaining":6,"log":[]},{"name":"TEMPLATE(STP-2)_10T*60*250","qty":6,"unit":"EA","remaining":6,"log":[]},{"name":"TEMPLATE(STP-3)_15T*250*3801","qty":6,"unit":"EA","remaining":6,"log":[]},{"name":"TEMPLATE(STP-4)_10T*60*250","qty":6,"unit":"EA","remaining":6,"log":[]}]</v>
       </c>
     </row>
     <row r="3">

--- a/du-lieu/chinh-sua-tay.xlsx
+++ b/du-lieu/chinh-sua-tay.xlsx
@@ -572,7 +572,7 @@
         <v/>
       </c>
       <c r="Z2" t="str">
-        <v>[{"name":"HRSG Embeded Material (Template)","qty":1,"unit":"PKG","remaining":0,"log":[{"time":"22:45:08 18/8/2026","change":-1,"after":0},{"time":"22:36:58 18/8/2026","change":1,"after":1},{"time":"22:36:52 18/8/2026","change":-1,"after":0},{"time":"21:59:36 18/8/2026","change":1,"after":1},{"time":"21:59:33 18/8/2026","change":-1,"after":0}]},{"name":"TEMPLATE(TP-1)_10T*374*374","qty":20,"unit":"EA","remaining":20,"log":[{"time":"22:37:08 18/8/2026","change":1,"after":20},{"time":"22:37:00 18/8/2026","change":-1,"after":19},{"time":"22:09:54 18/8/2026","change":1,"after":20},{"time":"22:00:37 18/8/2026","change":-1,"after":19}]},{"name":"TEMPLATE(TP-2)_10T*450*900","qty":40,"unit":"EA","remaining":40,"log":[]},{"name":"TEMPLATE(TP-3)_10T*270*320","qty":8,"unit":"EA","remaining":8,"log":[]},{"name":"TEMPLATE(STP-1)_15T*250*3801","qty":6,"unit":"EA","remaining":6,"log":[]},{"name":"TEMPLATE(STP-2)_10T*60*250","qty":6,"unit":"EA","remaining":6,"log":[]},{"name":"TEMPLATE(STP-3)_15T*250*3801","qty":6,"unit":"EA","remaining":6,"log":[]},{"name":"TEMPLATE(STP-4)_10T*60*250","qty":6,"unit":"EA","remaining":6,"log":[]}]</v>
+        <v>[{"name":"HRSG Embeded Material (Template)","qty":1,"unit":"PKG","remaining":1,"log":[{"time":"22:52:52 18/8/2026","change":1,"after":1},{"time":"22:45:08 18/8/2026","change":-1,"after":0},{"time":"22:36:58 18/8/2026","change":1,"after":1},{"time":"22:36:52 18/8/2026","change":-1,"after":0},{"time":"21:59:36 18/8/2026","change":1,"after":1},{"time":"21:59:33 18/8/2026","change":-1,"after":0}]},{"name":"TEMPLATE(TP-1)_10T*374*374","qty":20,"unit":"EA","remaining":20,"log":[{"time":"22:37:08 18/8/2026","change":1,"after":20},{"time":"22:37:00 18/8/2026","change":-1,"after":19},{"time":"22:09:54 18/8/2026","change":1,"after":20},{"time":"22:00:37 18/8/2026","change":-1,"after":19}]},{"name":"TEMPLATE(TP-2)_10T*450*900","qty":40,"unit":"EA","remaining":40,"log":[]},{"name":"TEMPLATE(TP-3)_10T*270*320","qty":8,"unit":"EA","remaining":8,"log":[]},{"name":"TEMPLATE(STP-1)_15T*250*3801","qty":6,"unit":"EA","remaining":6,"log":[]},{"name":"TEMPLATE(STP-2)_10T*60*250","qty":6,"unit":"EA","remaining":6,"log":[]},{"name":"TEMPLATE(STP-3)_15T*250*3801","qty":6,"unit":"EA","remaining":6,"log":[]},{"name":"TEMPLATE(STP-4)_10T*60*250","qty":6,"unit":"EA","remaining":6,"log":[]}]</v>
       </c>
     </row>
     <row r="3">

--- a/du-lieu/chinh-sua-tay.xlsx
+++ b/du-lieu/chinh-sua-tay.xlsx
@@ -572,7 +572,7 @@
         <v/>
       </c>
       <c r="Z2" t="str">
-        <v>[{"name":"HRSG Embeded Material (Template)","qty":1,"unit":"PKG","remaining":1,"log":[{"time":"22:52:52 18/8/2026","change":1,"after":1},{"time":"22:45:08 18/8/2026","change":-1,"after":0},{"time":"22:36:58 18/8/2026","change":1,"after":1},{"time":"22:36:52 18/8/2026","change":-1,"after":0},{"time":"21:59:36 18/8/2026","change":1,"after":1},{"time":"21:59:33 18/8/2026","change":-1,"after":0}]},{"name":"TEMPLATE(TP-1)_10T*374*374","qty":20,"unit":"EA","remaining":20,"log":[{"time":"22:37:08 18/8/2026","change":1,"after":20},{"time":"22:37:00 18/8/2026","change":-1,"after":19},{"time":"22:09:54 18/8/2026","change":1,"after":20},{"time":"22:00:37 18/8/2026","change":-1,"after":19}]},{"name":"TEMPLATE(TP-2)_10T*450*900","qty":40,"unit":"EA","remaining":40,"log":[]},{"name":"TEMPLATE(TP-3)_10T*270*320","qty":8,"unit":"EA","remaining":8,"log":[]},{"name":"TEMPLATE(STP-1)_15T*250*3801","qty":6,"unit":"EA","remaining":6,"log":[]},{"name":"TEMPLATE(STP-2)_10T*60*250","qty":6,"unit":"EA","remaining":6,"log":[]},{"name":"TEMPLATE(STP-3)_15T*250*3801","qty":6,"unit":"EA","remaining":6,"log":[]},{"name":"TEMPLATE(STP-4)_10T*60*250","qty":6,"unit":"EA","remaining":6,"log":[]}]</v>
+        <v>[{"name":"HRSG Embeded Material (Template)","qty":1,"unit":"PKG","remaining":0,"log":[{"time":"22:56:30 18/8/2026","change":-1,"after":0},{"time":"22:52:52 18/8/2026","change":1,"after":1},{"time":"22:45:08 18/8/2026","change":-1,"after":0},{"time":"22:36:58 18/8/2026","change":1,"after":1},{"time":"22:36:52 18/8/2026","change":-1,"after":0},{"time":"21:59:36 18/8/2026","change":1,"after":1},{"time":"21:59:33 18/8/2026","change":-1,"after":0}]},{"name":"TEMPLATE(TP-1)_10T*374*374","qty":20,"unit":"EA","remaining":20,"log":[{"time":"22:37:08 18/8/2026","change":1,"after":20},{"time":"22:37:00 18/8/2026","change":-1,"after":19},{"time":"22:09:54 18/8/2026","change":1,"after":20},{"time":"22:00:37 18/8/2026","change":-1,"after":19}]},{"name":"TEMPLATE(TP-2)_10T*450*900","qty":40,"unit":"EA","remaining":40,"log":[]},{"name":"TEMPLATE(TP-3)_10T*270*320","qty":8,"unit":"EA","remaining":8,"log":[]},{"name":"TEMPLATE(STP-1)_15T*250*3801","qty":6,"unit":"EA","remaining":6,"log":[]},{"name":"TEMPLATE(STP-2)_10T*60*250","qty":6,"unit":"EA","remaining":6,"log":[]},{"name":"TEMPLATE(STP-3)_15T*250*3801","qty":6,"unit":"EA","remaining":6,"log":[]},{"name":"TEMPLATE(STP-4)_10T*60*250","qty":6,"unit":"EA","remaining":6,"log":[]}]</v>
       </c>
     </row>
     <row r="3">

--- a/du-lieu/chinh-sua-tay.xlsx
+++ b/du-lieu/chinh-sua-tay.xlsx
@@ -572,7 +572,7 @@
         <v/>
       </c>
       <c r="Z2" t="str">
-        <v>[{"name":"HRSG Embeded Material (Template)","qty":1,"unit":"PKG","remaining":0,"log":[{"time":"22:56:30 18/8/2026","change":-1,"after":0},{"time":"22:52:52 18/8/2026","change":1,"after":1},{"time":"22:45:08 18/8/2026","change":-1,"after":0},{"time":"22:36:58 18/8/2026","change":1,"after":1},{"time":"22:36:52 18/8/2026","change":-1,"after":0},{"time":"21:59:36 18/8/2026","change":1,"after":1},{"time":"21:59:33 18/8/2026","change":-1,"after":0}]},{"name":"TEMPLATE(TP-1)_10T*374*374","qty":20,"unit":"EA","remaining":20,"log":[{"time":"22:37:08 18/8/2026","change":1,"after":20},{"time":"22:37:00 18/8/2026","change":-1,"after":19},{"time":"22:09:54 18/8/2026","change":1,"after":20},{"time":"22:00:37 18/8/2026","change":-1,"after":19}]},{"name":"TEMPLATE(TP-2)_10T*450*900","qty":40,"unit":"EA","remaining":40,"log":[]},{"name":"TEMPLATE(TP-3)_10T*270*320","qty":8,"unit":"EA","remaining":8,"log":[]},{"name":"TEMPLATE(STP-1)_15T*250*3801","qty":6,"unit":"EA","remaining":6,"log":[]},{"name":"TEMPLATE(STP-2)_10T*60*250","qty":6,"unit":"EA","remaining":6,"log":[]},{"name":"TEMPLATE(STP-3)_15T*250*3801","qty":6,"unit":"EA","remaining":6,"log":[]},{"name":"TEMPLATE(STP-4)_10T*60*250","qty":6,"unit":"EA","remaining":6,"log":[]}]</v>
+        <v>[{"name":"HRSG Embeded Material (Template)","qty":1,"unit":"PKG","remaining":0,"log":[{"time":"22:57:47 18/8/2026","change":-1,"after":0},{"time":"22:52:52 18/8/2026","change":1,"after":1},{"time":"22:45:08 18/8/2026","change":-1,"after":0},{"time":"22:36:58 18/8/2026","change":1,"after":1},{"time":"22:36:52 18/8/2026","change":-1,"after":0},{"time":"21:59:36 18/8/2026","change":1,"after":1},{"time":"21:59:33 18/8/2026","change":-1,"after":0}]},{"name":"TEMPLATE(TP-1)_10T*374*374","qty":20,"unit":"EA","remaining":20,"log":[{"time":"22:37:08 18/8/2026","change":1,"after":20},{"time":"22:37:00 18/8/2026","change":-1,"after":19},{"time":"22:09:54 18/8/2026","change":1,"after":20},{"time":"22:00:37 18/8/2026","change":-1,"after":19}]},{"name":"TEMPLATE(TP-2)_10T*450*900","qty":40,"unit":"EA","remaining":40,"log":[]},{"name":"TEMPLATE(TP-3)_10T*270*320","qty":8,"unit":"EA","remaining":8,"log":[]},{"name":"TEMPLATE(STP-1)_15T*250*3801","qty":6,"unit":"EA","remaining":6,"log":[]},{"name":"TEMPLATE(STP-2)_10T*60*250","qty":6,"unit":"EA","remaining":6,"log":[]},{"name":"TEMPLATE(STP-3)_15T*250*3801","qty":6,"unit":"EA","remaining":6,"log":[]},{"name":"TEMPLATE(STP-4)_10T*60*250","qty":6,"unit":"EA","remaining":6,"log":[]}]</v>
       </c>
     </row>
     <row r="3">

--- a/du-lieu/chinh-sua-tay.xlsx
+++ b/du-lieu/chinh-sua-tay.xlsx
@@ -502,7 +502,7 @@
         <v>OM4-DE-IS-0001</v>
       </c>
       <c r="E2" t="str">
-        <v>S1</v>
+        <v/>
       </c>
       <c r="F2" t="str">
         <v>Trong kho</v>

--- a/du-lieu/chinh-sua-tay.xlsx
+++ b/du-lieu/chinh-sua-tay.xlsx
@@ -502,7 +502,7 @@
         <v>OM4-DE-IS-0001</v>
       </c>
       <c r="E2" t="str">
-        <v/>
+        <v>S2</v>
       </c>
       <c r="F2" t="str">
         <v>Trong kho</v>

--- a/du-lieu/chinh-sua-tay.xlsx
+++ b/du-lieu/chinh-sua-tay.xlsx
@@ -502,7 +502,7 @@
         <v>OM4-DE-IS-0001</v>
       </c>
       <c r="E2" t="str">
-        <v>S2</v>
+        <v/>
       </c>
       <c r="F2" t="str">
         <v>Trong kho</v>

--- a/du-lieu/chinh-sua-tay.xlsx
+++ b/du-lieu/chinh-sua-tay.xlsx
@@ -406,7 +406,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z2"/>
+  <dimension ref="A1:Z4"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -568,9 +568,169 @@
         <v/>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>19/08/2026</v>
+      </c>
+      <c r="B3" t="str">
+        <v>OM4-DE-IS-0011-001</v>
+      </c>
+      <c r="C3" t="str">
+        <v>Coupling for Steel Conduit 125mm (5") (50 EA); Flexible Conduit Connector (Male Type) 125mm (5") (50 EA); Flexible Conduit Connector (Female Type) 125mm (5") (50 EA); PIPE CLAMP With Bolt/Nut/Washer 125mm (5") (500 SET); Insulation Bushing W/Earthing 150mm (6") (70 EA)</v>
+      </c>
+      <c r="D3" t="str">
+        <v>OM4-DE-IS-0011</v>
+      </c>
+      <c r="E3" t="str">
+        <v>Office</v>
+      </c>
+      <c r="F3" t="str">
+        <v>Trong kho</v>
+      </c>
+      <c r="G3" t="str">
+        <v/>
+      </c>
+      <c r="H3" t="str">
+        <v>19/08/2026</v>
+      </c>
+      <c r="I3" t="str">
+        <v/>
+      </c>
+      <c r="J3" t="str">
+        <v/>
+      </c>
+      <c r="K3" t="str">
+        <v/>
+      </c>
+      <c r="L3" t="str">
+        <v/>
+      </c>
+      <c r="M3" t="str">
+        <v/>
+      </c>
+      <c r="N3" t="str">
+        <v/>
+      </c>
+      <c r="O3" t="str">
+        <v/>
+      </c>
+      <c r="P3" t="str">
+        <v/>
+      </c>
+      <c r="Q3" t="str">
+        <v/>
+      </c>
+      <c r="R3" t="str">
+        <v/>
+      </c>
+      <c r="S3" t="str">
+        <v/>
+      </c>
+      <c r="T3" t="str">
+        <v/>
+      </c>
+      <c r="U3" t="str">
+        <v/>
+      </c>
+      <c r="V3" t="str">
+        <v/>
+      </c>
+      <c r="W3" t="str">
+        <v/>
+      </c>
+      <c r="X3" t="str">
+        <v/>
+      </c>
+      <c r="Y3" t="str">
+        <v/>
+      </c>
+      <c r="Z3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>19/08/2026</v>
+      </c>
+      <c r="B4" t="str">
+        <v>OM4-DE-IS-0011-002</v>
+      </c>
+      <c r="C4" t="str">
+        <v>Flexible Conduit (Water proof type) 125mm (5") (120 M)</v>
+      </c>
+      <c r="D4" t="str">
+        <v>OM4-DE-IS-0011</v>
+      </c>
+      <c r="E4" t="str">
+        <v>Office</v>
+      </c>
+      <c r="F4" t="str">
+        <v>Trong kho</v>
+      </c>
+      <c r="G4" t="str">
+        <v/>
+      </c>
+      <c r="H4" t="str">
+        <v>19/08/2026</v>
+      </c>
+      <c r="I4" t="str">
+        <v/>
+      </c>
+      <c r="J4" t="str">
+        <v/>
+      </c>
+      <c r="K4" t="str">
+        <v/>
+      </c>
+      <c r="L4" t="str">
+        <v/>
+      </c>
+      <c r="M4" t="str">
+        <v/>
+      </c>
+      <c r="N4" t="str">
+        <v/>
+      </c>
+      <c r="O4" t="str">
+        <v/>
+      </c>
+      <c r="P4" t="str">
+        <v/>
+      </c>
+      <c r="Q4" t="str">
+        <v/>
+      </c>
+      <c r="R4" t="str">
+        <v/>
+      </c>
+      <c r="S4" t="str">
+        <v/>
+      </c>
+      <c r="T4" t="str">
+        <v/>
+      </c>
+      <c r="U4" t="str">
+        <v/>
+      </c>
+      <c r="V4" t="str">
+        <v/>
+      </c>
+      <c r="W4" t="str">
+        <v/>
+      </c>
+      <c r="X4" t="str">
+        <v/>
+      </c>
+      <c r="Y4" t="str">
+        <v/>
+      </c>
+      <c r="Z4" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:Z2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:Z4"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/du-lieu/chinh-sua-tay.xlsx
+++ b/du-lieu/chinh-sua-tay.xlsx
@@ -502,7 +502,7 @@
         <v>OM4-DE-IS-0001</v>
       </c>
       <c r="E2" t="str">
-        <v/>
+        <v>S1</v>
       </c>
       <c r="F2" t="str">
         <v>Trong kho</v>

--- a/du-lieu/chinh-sua-tay.xlsx
+++ b/du-lieu/chinh-sua-tay.xlsx
@@ -406,7 +406,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z4"/>
+  <dimension ref="A1:Z5"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -502,7 +502,7 @@
         <v>OM4-DE-IS-0001</v>
       </c>
       <c r="E2" t="str">
-        <v>S1</v>
+        <v/>
       </c>
       <c r="F2" t="str">
         <v>Trong kho</v>
@@ -728,9 +728,89 @@
         <v/>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>19/08/2026</v>
+      </c>
+      <c r="B5" t="str">
+        <v>OM4-DE-IS-0001-002</v>
+      </c>
+      <c r="C5" t="str">
+        <v>Anchor Bolt (40 EA); Nut M56 (160 EA); Anchor Bolt (16 EA); Nut M42 (64 EA)</v>
+      </c>
+      <c r="D5" t="str">
+        <v>OM4-DE-IS-0001</v>
+      </c>
+      <c r="E5" t="str">
+        <v>S2</v>
+      </c>
+      <c r="F5" t="str">
+        <v>Trong kho</v>
+      </c>
+      <c r="G5" t="str">
+        <v/>
+      </c>
+      <c r="H5" t="str">
+        <v>19/08/2026</v>
+      </c>
+      <c r="I5" t="str">
+        <v/>
+      </c>
+      <c r="J5" t="str">
+        <v/>
+      </c>
+      <c r="K5" t="str">
+        <v/>
+      </c>
+      <c r="L5" t="str">
+        <v/>
+      </c>
+      <c r="M5" t="str">
+        <v/>
+      </c>
+      <c r="N5" t="str">
+        <v/>
+      </c>
+      <c r="O5" t="str">
+        <v/>
+      </c>
+      <c r="P5" t="str">
+        <v/>
+      </c>
+      <c r="Q5" t="str">
+        <v/>
+      </c>
+      <c r="R5" t="str">
+        <v/>
+      </c>
+      <c r="S5" t="str">
+        <v/>
+      </c>
+      <c r="T5" t="str">
+        <v/>
+      </c>
+      <c r="U5" t="str">
+        <v/>
+      </c>
+      <c r="V5" t="str">
+        <v/>
+      </c>
+      <c r="W5" t="str">
+        <v/>
+      </c>
+      <c r="X5" t="str">
+        <v/>
+      </c>
+      <c r="Y5" t="str">
+        <v/>
+      </c>
+      <c r="Z5" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:Z4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:Z5"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/du-lieu/chinh-sua-tay.xlsx
+++ b/du-lieu/chinh-sua-tay.xlsx
@@ -406,7 +406,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z5"/>
+  <dimension ref="A1:Z13"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -502,7 +502,7 @@
         <v>OM4-DE-IS-0001</v>
       </c>
       <c r="E2" t="str">
-        <v/>
+        <v>S3</v>
       </c>
       <c r="F2" t="str">
         <v>Trong kho</v>
@@ -742,7 +742,7 @@
         <v>OM4-DE-IS-0001</v>
       </c>
       <c r="E5" t="str">
-        <v>S2</v>
+        <v>S3</v>
       </c>
       <c r="F5" t="str">
         <v>Trong kho</v>
@@ -805,12 +805,652 @@
         <v/>
       </c>
       <c r="Z5" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>19/08/2026</v>
+      </c>
+      <c r="B6" t="str">
+        <v>OM4-DE-IS-0001-003</v>
+      </c>
+      <c r="C6" t="str">
+        <v>HRSG Embeded Material (Anchor Bolt/Nut/Washer) (1 PKG); Anchor Bolt (53 EA); Nut M60 (212 EA)</v>
+      </c>
+      <c r="D6" t="str">
+        <v>OM4-DE-IS-0001</v>
+      </c>
+      <c r="E6" t="str">
+        <v>S3</v>
+      </c>
+      <c r="F6" t="str">
+        <v>Trong kho</v>
+      </c>
+      <c r="G6" t="str">
+        <v/>
+      </c>
+      <c r="H6" t="str">
+        <v>19/08/2026</v>
+      </c>
+      <c r="I6" t="str">
+        <v/>
+      </c>
+      <c r="J6" t="str">
+        <v/>
+      </c>
+      <c r="K6" t="str">
+        <v/>
+      </c>
+      <c r="L6" t="str">
+        <v/>
+      </c>
+      <c r="M6" t="str">
+        <v/>
+      </c>
+      <c r="N6" t="str">
+        <v/>
+      </c>
+      <c r="O6" t="str">
+        <v/>
+      </c>
+      <c r="P6" t="str">
+        <v/>
+      </c>
+      <c r="Q6" t="str">
+        <v/>
+      </c>
+      <c r="R6" t="str">
+        <v/>
+      </c>
+      <c r="S6" t="str">
+        <v/>
+      </c>
+      <c r="T6" t="str">
+        <v/>
+      </c>
+      <c r="U6" t="str">
+        <v/>
+      </c>
+      <c r="V6" t="str">
+        <v/>
+      </c>
+      <c r="W6" t="str">
+        <v/>
+      </c>
+      <c r="X6" t="str">
+        <v/>
+      </c>
+      <c r="Y6" t="str">
+        <v/>
+      </c>
+      <c r="Z6" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>19/08/2026</v>
+      </c>
+      <c r="B7" t="str">
+        <v>OM4-DE-IS-0001-004</v>
+      </c>
+      <c r="C7" t="str">
+        <v>HRSG Embeded Material (Anchor Bolt/Nut/Washer) (1 PKG); Anchor Bolt (53 EA); Nut M60 (212 EA)</v>
+      </c>
+      <c r="D7" t="str">
+        <v>OM4-DE-IS-0001</v>
+      </c>
+      <c r="E7" t="str">
+        <v>S3</v>
+      </c>
+      <c r="F7" t="str">
+        <v>Trong kho</v>
+      </c>
+      <c r="G7" t="str">
+        <v/>
+      </c>
+      <c r="H7" t="str">
+        <v>19/08/2026</v>
+      </c>
+      <c r="I7" t="str">
+        <v/>
+      </c>
+      <c r="J7" t="str">
+        <v/>
+      </c>
+      <c r="K7" t="str">
+        <v/>
+      </c>
+      <c r="L7" t="str">
+        <v/>
+      </c>
+      <c r="M7" t="str">
+        <v/>
+      </c>
+      <c r="N7" t="str">
+        <v/>
+      </c>
+      <c r="O7" t="str">
+        <v/>
+      </c>
+      <c r="P7" t="str">
+        <v/>
+      </c>
+      <c r="Q7" t="str">
+        <v/>
+      </c>
+      <c r="R7" t="str">
+        <v/>
+      </c>
+      <c r="S7" t="str">
+        <v/>
+      </c>
+      <c r="T7" t="str">
+        <v/>
+      </c>
+      <c r="U7" t="str">
+        <v/>
+      </c>
+      <c r="V7" t="str">
+        <v/>
+      </c>
+      <c r="W7" t="str">
+        <v/>
+      </c>
+      <c r="X7" t="str">
+        <v/>
+      </c>
+      <c r="Y7" t="str">
+        <v/>
+      </c>
+      <c r="Z7" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>19/08/2026</v>
+      </c>
+      <c r="B8" t="str">
+        <v>OM4-DE-IS-0001-005</v>
+      </c>
+      <c r="C8" t="str">
+        <v>HRSG Embeded Material (Anchor Bolt/Nut/Washer) (1 PKG); Anchor Bolt (54 EA); Nut M60 (216 EA)</v>
+      </c>
+      <c r="D8" t="str">
+        <v>OM4-DE-IS-0001</v>
+      </c>
+      <c r="E8" t="str">
+        <v>S3</v>
+      </c>
+      <c r="F8" t="str">
+        <v>Trong kho</v>
+      </c>
+      <c r="G8" t="str">
+        <v/>
+      </c>
+      <c r="H8" t="str">
+        <v>19/08/2026</v>
+      </c>
+      <c r="I8" t="str">
+        <v/>
+      </c>
+      <c r="J8" t="str">
+        <v/>
+      </c>
+      <c r="K8" t="str">
+        <v/>
+      </c>
+      <c r="L8" t="str">
+        <v/>
+      </c>
+      <c r="M8" t="str">
+        <v/>
+      </c>
+      <c r="N8" t="str">
+        <v/>
+      </c>
+      <c r="O8" t="str">
+        <v/>
+      </c>
+      <c r="P8" t="str">
+        <v/>
+      </c>
+      <c r="Q8" t="str">
+        <v/>
+      </c>
+      <c r="R8" t="str">
+        <v/>
+      </c>
+      <c r="S8" t="str">
+        <v/>
+      </c>
+      <c r="T8" t="str">
+        <v/>
+      </c>
+      <c r="U8" t="str">
+        <v/>
+      </c>
+      <c r="V8" t="str">
+        <v/>
+      </c>
+      <c r="W8" t="str">
+        <v/>
+      </c>
+      <c r="X8" t="str">
+        <v/>
+      </c>
+      <c r="Y8" t="str">
+        <v/>
+      </c>
+      <c r="Z8" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>19/08/2026</v>
+      </c>
+      <c r="B9" t="str">
+        <v>OM4-DE-IS-0001-006</v>
+      </c>
+      <c r="C9" t="str">
+        <v>HRSG Embeded Material (Anchor Bolt/Nut/Washer) (1 PKG); Anchor Bolt (72 EA); Nut M48 (288 EA)</v>
+      </c>
+      <c r="D9" t="str">
+        <v>OM4-DE-IS-0001</v>
+      </c>
+      <c r="E9" t="str">
+        <v>S3</v>
+      </c>
+      <c r="F9" t="str">
+        <v>Trong kho</v>
+      </c>
+      <c r="G9" t="str">
+        <v/>
+      </c>
+      <c r="H9" t="str">
+        <v>19/08/2026</v>
+      </c>
+      <c r="I9" t="str">
+        <v/>
+      </c>
+      <c r="J9" t="str">
+        <v/>
+      </c>
+      <c r="K9" t="str">
+        <v/>
+      </c>
+      <c r="L9" t="str">
+        <v/>
+      </c>
+      <c r="M9" t="str">
+        <v/>
+      </c>
+      <c r="N9" t="str">
+        <v/>
+      </c>
+      <c r="O9" t="str">
+        <v/>
+      </c>
+      <c r="P9" t="str">
+        <v/>
+      </c>
+      <c r="Q9" t="str">
+        <v/>
+      </c>
+      <c r="R9" t="str">
+        <v/>
+      </c>
+      <c r="S9" t="str">
+        <v/>
+      </c>
+      <c r="T9" t="str">
+        <v/>
+      </c>
+      <c r="U9" t="str">
+        <v/>
+      </c>
+      <c r="V9" t="str">
+        <v/>
+      </c>
+      <c r="W9" t="str">
+        <v/>
+      </c>
+      <c r="X9" t="str">
+        <v/>
+      </c>
+      <c r="Y9" t="str">
+        <v/>
+      </c>
+      <c r="Z9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>19/08/2026</v>
+      </c>
+      <c r="B10" t="str">
+        <v>OM4-DE-IS-0001-007</v>
+      </c>
+      <c r="C10" t="str">
+        <v>HRSG Embeded Material (Anchor Bolt/Nut/Washer) (1 PKG); Square Washer 130X160X20T (40 EA); Square Washer 130X130X20T (160 EA); Square Washer 100X100X15T (16 EA); Square Washer 120X120X16T (72 EA); Anchor Plate 130X130X20T (40 EA); Anchor Plate 130X130X20T (160 EA); Anchor Plate 100X100X12T (16 EA); Anchor Plate 120X120X16T (72 EA); Bot. Plate 100X100X10T (40 EA); Bot. Plate 100X100X10T (160 EA); Bot. Plate 100X100X10T (16 EA)</v>
+      </c>
+      <c r="D10" t="str">
+        <v>OM4-DE-IS-0001</v>
+      </c>
+      <c r="E10" t="str">
+        <v>S3</v>
+      </c>
+      <c r="F10" t="str">
+        <v>Trong kho</v>
+      </c>
+      <c r="G10" t="str">
+        <v/>
+      </c>
+      <c r="H10" t="str">
+        <v>19/08/2026</v>
+      </c>
+      <c r="I10" t="str">
+        <v/>
+      </c>
+      <c r="J10" t="str">
+        <v/>
+      </c>
+      <c r="K10" t="str">
+        <v/>
+      </c>
+      <c r="L10" t="str">
+        <v/>
+      </c>
+      <c r="M10" t="str">
+        <v/>
+      </c>
+      <c r="N10" t="str">
+        <v/>
+      </c>
+      <c r="O10" t="str">
+        <v/>
+      </c>
+      <c r="P10" t="str">
+        <v/>
+      </c>
+      <c r="Q10" t="str">
+        <v/>
+      </c>
+      <c r="R10" t="str">
+        <v/>
+      </c>
+      <c r="S10" t="str">
+        <v/>
+      </c>
+      <c r="T10" t="str">
+        <v/>
+      </c>
+      <c r="U10" t="str">
+        <v/>
+      </c>
+      <c r="V10" t="str">
+        <v/>
+      </c>
+      <c r="W10" t="str">
+        <v/>
+      </c>
+      <c r="X10" t="str">
+        <v/>
+      </c>
+      <c r="Y10" t="str">
+        <v/>
+      </c>
+      <c r="Z10" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>19/08/2026</v>
+      </c>
+      <c r="B11" t="str">
+        <v>OM4-DE-IS-0001-008</v>
+      </c>
+      <c r="C11" t="str">
+        <v>HRSG Embeded Material (Anchor Bolt/Nut/Washer) (1 PKG); Sleeve 3"XSTD-982L (40 EA); Sleeve 3"XSTD-1,062L (160 EA); Sleeve 2-1/2"XSTD-752L (16 EA); Cap Plate Ø100XØ61X10T (40 EA); Cap Plate Ø100XØ65X10T (160 EA); Cap Plate Ø100XØ47X10T (16 EA)</v>
+      </c>
+      <c r="D11" t="str">
+        <v>OM4-DE-IS-0001</v>
+      </c>
+      <c r="E11" t="str">
+        <v>S3</v>
+      </c>
+      <c r="F11" t="str">
+        <v>Trong kho</v>
+      </c>
+      <c r="G11" t="str">
+        <v/>
+      </c>
+      <c r="H11" t="str">
+        <v>19/08/2026</v>
+      </c>
+      <c r="I11" t="str">
+        <v/>
+      </c>
+      <c r="J11" t="str">
+        <v/>
+      </c>
+      <c r="K11" t="str">
+        <v/>
+      </c>
+      <c r="L11" t="str">
+        <v/>
+      </c>
+      <c r="M11" t="str">
+        <v/>
+      </c>
+      <c r="N11" t="str">
+        <v/>
+      </c>
+      <c r="O11" t="str">
+        <v/>
+      </c>
+      <c r="P11" t="str">
+        <v/>
+      </c>
+      <c r="Q11" t="str">
+        <v/>
+      </c>
+      <c r="R11" t="str">
+        <v/>
+      </c>
+      <c r="S11" t="str">
+        <v/>
+      </c>
+      <c r="T11" t="str">
+        <v/>
+      </c>
+      <c r="U11" t="str">
+        <v/>
+      </c>
+      <c r="V11" t="str">
+        <v/>
+      </c>
+      <c r="W11" t="str">
+        <v/>
+      </c>
+      <c r="X11" t="str">
+        <v/>
+      </c>
+      <c r="Y11" t="str">
+        <v/>
+      </c>
+      <c r="Z11" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>19/08/2026</v>
+      </c>
+      <c r="B12" t="str">
+        <v>OM4-DE-IS-0001-009</v>
+      </c>
+      <c r="C12" t="str">
+        <v>HRSG Embeded Material (Spare) (1 PKG); Nut M56 (8 EA); Nut M60 (32 EA); Nut M42 (5 EA); Nut M48 (14 EA); Square Washer 130X160X20T (5 EA); Square Washer 130X130X20T (8 EA); Square Washer 100X100X15T (5 EA); Square Washer 120X120X16T (5 EA)</v>
+      </c>
+      <c r="D12" t="str">
+        <v>OM4-DE-IS-0001</v>
+      </c>
+      <c r="E12" t="str">
+        <v>S3</v>
+      </c>
+      <c r="F12" t="str">
+        <v>Trong kho</v>
+      </c>
+      <c r="G12" t="str">
+        <v/>
+      </c>
+      <c r="H12" t="str">
+        <v>19/08/2026</v>
+      </c>
+      <c r="I12" t="str">
+        <v/>
+      </c>
+      <c r="J12" t="str">
+        <v/>
+      </c>
+      <c r="K12" t="str">
+        <v/>
+      </c>
+      <c r="L12" t="str">
+        <v/>
+      </c>
+      <c r="M12" t="str">
+        <v/>
+      </c>
+      <c r="N12" t="str">
+        <v/>
+      </c>
+      <c r="O12" t="str">
+        <v/>
+      </c>
+      <c r="P12" t="str">
+        <v/>
+      </c>
+      <c r="Q12" t="str">
+        <v/>
+      </c>
+      <c r="R12" t="str">
+        <v/>
+      </c>
+      <c r="S12" t="str">
+        <v/>
+      </c>
+      <c r="T12" t="str">
+        <v/>
+      </c>
+      <c r="U12" t="str">
+        <v/>
+      </c>
+      <c r="V12" t="str">
+        <v/>
+      </c>
+      <c r="W12" t="str">
+        <v/>
+      </c>
+      <c r="X12" t="str">
+        <v/>
+      </c>
+      <c r="Y12" t="str">
+        <v/>
+      </c>
+      <c r="Z12" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>19/08/2026</v>
+      </c>
+      <c r="B13" t="str">
+        <v>S1</v>
+      </c>
+      <c r="C13" t="str">
+        <v>HRSG Embeded Material (Template)</v>
+      </c>
+      <c r="D13" t="str">
+        <v>OM4-DE-IS-0001</v>
+      </c>
+      <c r="E13" t="str">
+        <v>S3</v>
+      </c>
+      <c r="F13" t="str">
+        <v>Trong kho</v>
+      </c>
+      <c r="G13" t="str">
+        <v/>
+      </c>
+      <c r="H13" t="str">
+        <v>19/08/2026</v>
+      </c>
+      <c r="I13" t="str">
+        <v/>
+      </c>
+      <c r="J13" t="str">
+        <v/>
+      </c>
+      <c r="K13" t="str">
+        <v/>
+      </c>
+      <c r="L13" t="str">
+        <v/>
+      </c>
+      <c r="M13" t="str">
+        <v/>
+      </c>
+      <c r="N13" t="str">
+        <v/>
+      </c>
+      <c r="O13" t="str">
+        <v/>
+      </c>
+      <c r="P13" t="str">
+        <v/>
+      </c>
+      <c r="Q13" t="str">
+        <v/>
+      </c>
+      <c r="R13" t="str">
+        <v/>
+      </c>
+      <c r="S13" t="str">
+        <v/>
+      </c>
+      <c r="T13" t="str">
+        <v/>
+      </c>
+      <c r="U13" t="str">
+        <v/>
+      </c>
+      <c r="V13" t="str">
+        <v/>
+      </c>
+      <c r="W13" t="str">
+        <v/>
+      </c>
+      <c r="X13" t="str">
+        <v/>
+      </c>
+      <c r="Y13" t="str">
+        <v/>
+      </c>
+      <c r="Z13" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:Z5"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:Z13"/>
   </ignoredErrors>
 </worksheet>
 </file>